--- a/S_tables/Table_S4_subsystem_comparisons.xlsx
+++ b/S_tables/Table_S4_subsystem_comparisons.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subsystem enrichment" sheetId="1" r:id="Rb5bc2edee2d841b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transport reaction sets" sheetId="2" r:id="R6daa5258889647e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subsystem enrichment" sheetId="1" r:id="Rf1bb7d9087034089"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transport reaction sets" sheetId="2" r:id="R74e12f3cabeb4f04"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -416,7 +416,7 @@
         <x:v>MAR00605;MAR00670;MAR07588</x:v>
       </x:c>
       <x:c r="L3" s="2" t="n">
-        <x:v>0.7105715733201576</x:v>
+        <x:v>0.7184961633571855</x:v>
       </x:c>
       <x:c r="M3" s="3" t="b">
         <x:v>0</x:v>
@@ -576,7 +576,7 @@
         <x:v>MAR05130;MAR05131;MAR05132;MAR05133;MAR05134;MAR05135;MAR05136;MAR05137;MAR05138;MAR05139;MAR05140;MAR05141;MAR05142;MAR05143;MAR05145;MAR05146;MAR05147;MAR05148;MAR05149;MAR05150</x:v>
       </x:c>
       <x:c r="L7" s="2" t="n">
-        <x:v>1.8665273739175843e-22</x:v>
+        <x:v>1.7697444730477836e-22</x:v>
       </x:c>
       <x:c r="M7" s="3" t="b">
         <x:v>1</x:v>
@@ -734,7 +734,7 @@
         <x:v>MAR00021;MAR00022;MAR00023;MAR00033;MAR00034;MAR04413</x:v>
       </x:c>
       <x:c r="L11" s="2" t="n">
-        <x:v>0.009210954041276505</x:v>
+        <x:v>0.009154543999028968</x:v>
       </x:c>
       <x:c r="M11" s="3" t="b">
         <x:v>1</x:v>
@@ -972,7 +972,7 @@
         <x:v>MAR03107;MAR03108;MAR03109;MAR03110;MAR03111;MAR03112;MAR03113;MAR03114;MAR03115;MAR03116;MAR03117;MAR03118;MAR03122;MAR03123;MAR03125;MAR03129;MAR03130;MAR03132;MAR03136;MAR03137;MAR03139;MAR03150;MAR03151;MAR03153;MAR03408;MAR03411;MAR03414;MAR03416;MAR03422;MAR03423;MAR03424;MAR03425;MAR03430;MAR03431;MAR03432;MAR03433</x:v>
       </x:c>
       <x:c r="L17" s="2" t="n">
-        <x:v>1.463778566118276e-25</x:v>
+        <x:v>1.3734218645060366e-25</x:v>
       </x:c>
       <x:c r="M17" s="3" t="b">
         <x:v>1</x:v>
@@ -1052,7 +1052,7 @@
         <x:v>MAR03170;MAR03171;MAR03172;MAR03173;MAR03174;MAR03175;MAR03176;MAR03177;MAR03396;MAR03397</x:v>
       </x:c>
       <x:c r="L19" s="2" t="n">
-        <x:v>0.002198625082138094</x:v>
+        <x:v>0.0021234584126632876</x:v>
       </x:c>
       <x:c r="M19" s="3" t="b">
         <x:v>1</x:v>
@@ -1210,7 +1210,7 @@
         <x:v>MAR03240;MAR03241;MAR03242;MAR03243;MAR03244;MAR03245;MAR03246;MAR03247;MAR03250;MAR03252;MAR03254;MAR03256;MAR03258;MAR03260;MAR03262;MAR03264;MAR03272</x:v>
       </x:c>
       <x:c r="L23" s="2" t="n">
-        <x:v>4.69787227986379e-19</x:v>
+        <x:v>4.384680794539536e-19</x:v>
       </x:c>
       <x:c r="M23" s="3" t="b">
         <x:v>1</x:v>
@@ -1290,7 +1290,7 @@
         <x:v>MAR03218;MAR03219;MAR03220;MAR03221;MAR03222;MAR03223;MAR03224;MAR03225;MAR03226;MAR03227;MAR03228;MAR03229;MAR03230;MAR03231;MAR03232;MAR03233;MAR03234;MAR03235;MAR03236;MAR03237;MAR03239</x:v>
       </x:c>
       <x:c r="L25" s="2" t="n">
-        <x:v>1.4289549214935926e-23</x:v>
+        <x:v>1.3678884718571144e-23</x:v>
       </x:c>
       <x:c r="M25" s="3" t="b">
         <x:v>1</x:v>
@@ -1684,7 +1684,7 @@
         <x:v>MAR02591;MAR02594;MAR02599;MAR02602;MAR02605;MAR02611;MAR02614;MAR02620;MAR02623;MAR02626;MAR02633;MAR02636;MAR02642;MAR02648;MAR02651;MAR02654;MAR02657;MAR02660;MAR02666;MAR02669;MAR02672;MAR02675;MAR02678;MAR02681;MAR02684;MAR02687;MAR02693;MAR02699;MAR02702;MAR02705;MAR02708;MAR02730;MAR02733;MAR02736;MAR02739;MAR02759;MAR02762;MAR02768;MAR02771;MAR02774;MAR02877</x:v>
       </x:c>
       <x:c r="L35" s="2" t="n">
-        <x:v>2.313297620296776e-33</x:v>
+        <x:v>2.0562645513749117e-33</x:v>
       </x:c>
       <x:c r="M35" s="3" t="b">
         <x:v>1</x:v>
@@ -1766,7 +1766,7 @@
         <x:v>MAR02606;MAR02607;MAR02616;MAR02618;MAR02621;MAR02622;MAR02624;MAR02625;MAR02644;MAR02646;MAR02649;MAR02650;MAR02652;MAR02653;MAR02661;MAR02662;MAR02670;MAR02671;MAR02676;MAR02677;MAR02679;MAR02680;MAR02682;MAR02683;MAR02685;MAR02686;MAR02688;MAR02689;MAR02695;MAR02697;MAR02700;MAR02701;MAR02703;MAR02704;MAR02706;MAR02707;MAR02709;MAR02710;MAR02732;MAR02734;MAR02735;MAR02737;MAR02738;MAR02740;MAR02741;MAR02764;MAR02766;MAR02769;MAR02770;MAR02772;MAR02773;MAR02775;MAR02776;MAR08418</x:v>
       </x:c>
       <x:c r="L37" s="2" t="n">
-        <x:v>2.7746774611630334e-31</x:v>
+        <x:v>2.4663799654782515e-31</x:v>
       </x:c>
       <x:c r="M37" s="3" t="b">
         <x:v>1</x:v>
@@ -1807,7 +1807,7 @@
         <x:v>MAR03029;MAR03030</x:v>
       </x:c>
       <x:c r="L38" s="2" t="n">
-        <x:v>0.5183252187306376</x:v>
+        <x:v>0.5310149133511617</x:v>
       </x:c>
       <x:c r="M38" s="3" t="b">
         <x:v>0</x:v>
@@ -2320,7 +2320,7 @@
         <x:v>MAR07598;MAR07614;MAR10061</x:v>
       </x:c>
       <x:c r="L51" s="2" t="n">
-        <x:v>0.49152992164635545</x:v>
+        <x:v>0.5056008898060522</x:v>
       </x:c>
       <x:c r="M51" s="3" t="b">
         <x:v>0</x:v>
@@ -2521,7 +2521,7 @@
         <x:v>MAR00145;MAR00152;MAR00181;MAR00186;MAR00218;MAR00743;MAR00745;MAR00747;MAR00749;MAR01031;MAR02150;MAR02151</x:v>
       </x:c>
       <x:c r="L56" s="2" t="n">
-        <x:v>0.023631428977906824</x:v>
+        <x:v>0.02337255573401739</x:v>
       </x:c>
       <x:c r="M56" s="3" t="b">
         <x:v>1</x:v>
@@ -2562,7 +2562,7 @@
         <x:v>MAR02152;MAR02153;MAR02154;MAR02155;MAR02156;MAR02157;MAR02158;MAR02159;MAR02160;MAR02161;MAR02162;MAR02163</x:v>
       </x:c>
       <x:c r="L57" s="2" t="n">
-        <x:v>0.000010632897430180171</x:v>
+        <x:v>0.000010321993996549172</x:v>
       </x:c>
       <x:c r="M57" s="3" t="b">
         <x:v>1</x:v>
@@ -2919,7 +2919,7 @@
         <x:v>MAR00108;MAR00112;MAR00286;MAR00452;MAR00974;MAR00977;MAR00978;MAR00982;MAR01001;MAR02028;MAR02148;MAR02149;MAR02183;MAR02187;MAR02207;MAR03437;MAR03438;MAR03442;MAR03479;MAR03507;MAR03535;MAR04719;MAR04967;MAR05030;MAR05110;MAR05185;MAR05343;MAR05449;MAR05988;MAR06279;MAR06319;MAR06347</x:v>
       </x:c>
       <x:c r="L66" s="2" t="n">
-        <x:v>0.800881478903451</x:v>
+        <x:v>0.8080264069390861</x:v>
       </x:c>
       <x:c r="M66" s="3" t="b">
         <x:v>0</x:v>
@@ -2960,7 +2960,7 @@
         <x:v>MAR03972;MAR04332;MAR04335;MAR04655;MAR04656</x:v>
       </x:c>
       <x:c r="L67" s="2" t="n">
-        <x:v>0.7746430671886777</x:v>
+        <x:v>0.7822376070630764</x:v>
       </x:c>
       <x:c r="M67" s="3" t="b">
         <x:v>0</x:v>
@@ -3237,7 +3237,7 @@
         <x:v>MAR00129;MAR00579;MAR00580;MAR00581;MAR00598;MAR00632;MAR00643;MAR00651;MAR07594;MAR07597;MAR07601</x:v>
       </x:c>
       <x:c r="L74" s="2" t="n">
-        <x:v>0.22880923624279947</x:v>
+        <x:v>0.2300071903592539</x:v>
       </x:c>
       <x:c r="M74" s="3" t="b">
         <x:v>0</x:v>
@@ -3555,7 +3555,7 @@
         <x:v>MAR03984</x:v>
       </x:c>
       <x:c r="L82" s="2" t="n">
-        <x:v>0.8691446847561564</x:v>
+        <x:v>0.8765192457177237</x:v>
       </x:c>
       <x:c r="M82" s="3" t="b">
         <x:v>0</x:v>
@@ -3635,7 +3635,7 @@
         <x:v>MAR11321</x:v>
       </x:c>
       <x:c r="L84" s="2" t="n">
-        <x:v>0.6452190886893258</x:v>
+        <x:v>0.6574037267278154</x:v>
       </x:c>
       <x:c r="M84" s="3" t="b">
         <x:v>0</x:v>
@@ -4109,7 +4109,7 @@
         <x:v>MAR06402;MAR06403</x:v>
       </x:c>
       <x:c r="L96" s="2" t="n">
-        <x:v>0.1786529783690284</x:v>
+        <x:v>0.18009462251477476</x:v>
       </x:c>
       <x:c r="M96" s="3" t="b">
         <x:v>0</x:v>
@@ -4310,7 +4310,7 @@
         <x:v>MAR00061;MAR00578;MAR02127;MAR02141;MAR02377;MAR02379;MAR03789;MAR03946;MAR03952;MAR04756;MAR04852;MAR04874;MAR04898;MAR04905;MAR04914;MAR04963;MAR05006;MAR05033;MAR05043;MAR05115;MAR05126;MAR05227;MAR05304;MAR05361;MAR05420;MAR06328;MAR06438;MAR06454;MAR06469;MAR06481;MAR06513;MAR07638;MAR08009;MAR08614;MAR08891;MAR08987;MAR08998;MAR10049;MAR11443;MAR13080;MAR20137;MAR20139;MAR20149;MAR20161;MAR20163</x:v>
       </x:c>
       <x:c r="L101" s="2" t="n">
-        <x:v>0.14241943139580449</x:v>
+        <x:v>0.14362245453300101</x:v>
       </x:c>
       <x:c r="M101" s="3" t="b">
         <x:v>0</x:v>
@@ -4390,7 +4390,7 @@
         <x:v>MAR01542;MAR04265;MAR04269;MAR08791</x:v>
       </x:c>
       <x:c r="L103" s="2" t="n">
-        <x:v>0.650101905530899</x:v>
+        <x:v>0.6620460350288421</x:v>
       </x:c>
       <x:c r="M103" s="3" t="b">
         <x:v>0</x:v>
@@ -4431,7 +4431,7 @@
         <x:v>MAR01095;MAR05422;MAR05423;MAR07765;MAR07767;MAR07786;MAR07792;MAR07796;MAR07857;MAR07860;MAR07861;MAR07862;MAR13086</x:v>
       </x:c>
       <x:c r="L104" s="2" t="n">
-        <x:v>0.09298460228648582</x:v>
+        <x:v>0.09385112546191543</x:v>
       </x:c>
       <x:c r="M104" s="3" t="b">
         <x:v>0</x:v>
@@ -4472,7 +4472,7 @@
         <x:v>MAR03967;MAR03968;MAR04024;MAR04344;MAR04680;MAR07160;MAR07161;MAR07871;MAR08452;MAR08465;MAR08471;MAR08482;MAR08486</x:v>
       </x:c>
       <x:c r="L105" s="2" t="n">
-        <x:v>0.20620935608558832</x:v>
+        <x:v>0.2070698492835726</x:v>
       </x:c>
       <x:c r="M105" s="3" t="b">
         <x:v>0</x:v>
@@ -4671,7 +4671,7 @@
         <x:v>MAR03977;MAR06911;MAR06912;MAR06914;MAR06916;MAR06918</x:v>
       </x:c>
       <x:c r="L110" s="2" t="n">
-        <x:v>0.00023823670348439304</x:v>
+        <x:v>0.0002327098446733998</x:v>
       </x:c>
       <x:c r="M110" s="3" t="b">
         <x:v>1</x:v>
@@ -4790,7 +4790,7 @@
         <x:v>MAR04350;MAR04354;MAR04398;MAR04710</x:v>
       </x:c>
       <x:c r="L113" s="2" t="n">
-        <x:v>0.4802764624491124</x:v>
+        <x:v>0.4958310065742705</x:v>
       </x:c>
       <x:c r="M113" s="3" t="b">
         <x:v>0</x:v>
@@ -4870,7 +4870,7 @@
         <x:v>MAR00063;MAR00075;MAR01462;MAR02407;MAR02412;MAR02509;MAR02514;MAR03019;MAR03024;MAR03025;MAR03106;MAR04890;MAR04900;MAR07590;MAR07596;MAR07777;MAR07779;MAR08414;MAR08980;MAR09680;MAR10039;MAR10040</x:v>
       </x:c>
       <x:c r="L115" s="2" t="n">
-        <x:v>0.012790195693840456</x:v>
+        <x:v>0.012651287971183877</x:v>
       </x:c>
       <x:c r="M115" s="3" t="b">
         <x:v>1</x:v>
@@ -5073,7 +5073,7 @@
         <x:v>MAR01044;MAR04750;MAR04752;MAR04762;MAR04769;MAR04770;MAR11316;MAR11406</x:v>
       </x:c>
       <x:c r="L120" s="2" t="n">
-        <x:v>0.0005894055210522944</x:v>
+        <x:v>0.0005740781907176012</x:v>
       </x:c>
       <x:c r="M120" s="3" t="b">
         <x:v>1</x:v>
@@ -5311,7 +5311,7 @@
         <x:v>MAR04002;MAR04004;MAR04010;MAR04020;MAR04080;MAR04135;MAR04453;MAR04611;MAR04614;MAR04663;MAR06603</x:v>
       </x:c>
       <x:c r="L126" s="2" t="n">
-        <x:v>0.5411598833010876</x:v>
+        <x:v>0.5540990084995664</x:v>
       </x:c>
       <x:c r="M126" s="3" t="b">
         <x:v>0</x:v>
@@ -5352,7 +5352,7 @@
         <x:v>MAR03931;MAR04008;MAR04032;MAR04050;MAR04056;MAR04484;MAR04485;MAR04575;MAR04608;MAR04637;MAR04644;MAR04670;MAR04673;MAR06621;MAR06627;MAR08274</x:v>
       </x:c>
       <x:c r="L127" s="2" t="n">
-        <x:v>0.00018342473464764113</x:v>
+        <x:v>0.0001797191844527393</x:v>
       </x:c>
       <x:c r="M127" s="3" t="b">
         <x:v>1</x:v>
@@ -5432,7 +5432,7 @@
         <x:v>MAR03980;MAR04767;MAR08415</x:v>
       </x:c>
       <x:c r="L129" s="2" t="n">
-        <x:v>0.1836611351330739</x:v>
+        <x:v>0.18478238748431366</x:v>
       </x:c>
       <x:c r="M129" s="3" t="b">
         <x:v>0</x:v>
@@ -5473,7 +5473,7 @@
         <x:v>MAR06632;MAR06634;MAR06638;MAR06641;MAR06642;MAR06644;MAR06649;MAR06651;MAR06652;MAR06654;MAR06655;MAR06656;MAR06657;MAR06658;MAR06660;MAR06664;MAR06665;MAR06668;MAR06669;MAR06673;MAR06677;MAR06678;MAR06682;MAR06687;MAR06690;MAR06691;MAR06692;MAR06693;MAR06700;MAR06701;MAR06702;MAR06703;MAR08698;MAR08699;MAR08702;MAR08709;MAR08711</x:v>
       </x:c>
       <x:c r="L130" s="2" t="n">
-        <x:v>6.30365260710404e-20</x:v>
+        <x:v>5.923432291119988e-20</x:v>
       </x:c>
       <x:c r="M130" s="3" t="b">
         <x:v>1</x:v>
@@ -5908,7 +5908,7 @@
         <x:v>MAR04139;MAR04147;MAR04152;MAR04410;MAR04652;MAR08981</x:v>
       </x:c>
       <x:c r="L141" s="2" t="n">
-        <x:v>0.09654003657306906</x:v>
+        <x:v>0.09700641356134475</x:v>
       </x:c>
       <x:c r="M141" s="3" t="b">
         <x:v>0</x:v>
@@ -6187,7 +6187,7 @@
         <x:v>MAR02960;MAR02993</x:v>
       </x:c>
       <x:c r="L148" s="2" t="n">
-        <x:v>0.6102098945636854</x:v>
+        <x:v>0.6236603150916299</x:v>
       </x:c>
       <x:c r="M148" s="3" t="b">
         <x:v>0</x:v>
@@ -6228,7 +6228,7 @@
         <x:v>MAR08613;MAR08615;MAR08616</x:v>
       </x:c>
       <x:c r="L149" s="2" t="n">
-        <x:v>0.011714919284563998</x:v>
+        <x:v>0.011596586766538101</x:v>
       </x:c>
       <x:c r="M149" s="3" t="b">
         <x:v>1</x:v>
@@ -6386,7 +6386,7 @@
         <x:v>MAR02129;MAR02130;MAR02131;MAR02132;MAR02133;MAR02134;MAR02135;MAR02136;MAR02137;MAR02139;MAR02142;MAR02143;MAR02144;MAR02145</x:v>
       </x:c>
       <x:c r="L153" s="2" t="n">
-        <x:v>3.503722745492831e-7</x:v>
+        <x:v>3.3539910042324533e-7</x:v>
       </x:c>
       <x:c r="M153" s="3" t="b">
         <x:v>1</x:v>
@@ -6427,7 +6427,7 @@
         <x:v>MAR06436;MAR06453;MAR06465;MAR06467;MAR06470;MAR06471;MAR06472;MAR06473;MAR06476;MAR06478;MAR06482;MAR06484;MAR06486;MAR06488;MAR06492</x:v>
       </x:c>
       <x:c r="L154" s="2" t="n">
-        <x:v>3.3724362946441165e-7</x:v>
+        <x:v>3.235635527841974e-7</x:v>
       </x:c>
       <x:c r="M154" s="3" t="b">
         <x:v>1</x:v>
@@ -6548,7 +6548,7 @@
         <x:v>MAR02591;MAR02594;MAR02599;MAR02602;MAR02605;MAR02606;MAR02607;MAR02611;MAR02614;MAR02616;MAR02618;MAR02620;MAR02621;MAR02622;MAR02623;MAR02624;MAR02625;MAR02626;MAR02633;MAR02636;MAR02642;MAR02644;MAR02646;MAR02648;MAR02649;MAR02650;MAR02651;MAR02652;MAR02653;MAR02654;MAR02657;MAR02660;MAR02661;MAR02662;MAR02666;MAR02669;MAR02670;MAR02671;MAR02672;MAR02675;MAR02676;MAR02677;MAR02678;MAR02679;MAR02680;MAR02681;MAR02682;MAR02683;MAR02684;MAR02685;MAR02686;MAR02687;MAR02688;MAR02689;MAR02693;MAR02695;MAR02697;MAR02699;MAR02700;MAR02701;MAR02702;MAR02703;MAR02704;MAR02705;MAR02706;MAR02707;MAR02708;MAR02709;MAR02710;MAR02730;MAR02732;MAR02733;MAR02734;MAR02735;MAR02736;MAR02737;MAR02738;MAR02739;MAR02740;MAR02741;MAR02759;MAR02762;MAR02764;MAR02766;MAR02768;MAR02769;MAR02770;MAR02771;MAR02772;MAR02773;MAR02774;MAR02775;MAR02776;MAR02869;MAR02870;MAR02877;MAR02878;MAR02879;MAR02896;MAR02897;MAR02924;MAR02925;MAR02926;MAR03029;MAR03030;MAR08418</x:v>
       </x:c>
       <x:c r="L157" s="2" t="n">
-        <x:v>5.59423379446617e-45</x:v>
+        <x:v>4.9726522617477064e-45</x:v>
       </x:c>
       <x:c r="M157" s="3" t="b">
         <x:v>1</x:v>
@@ -6589,7 +6589,7 @@
         <x:v>MAR03107;MAR03108;MAR03109;MAR03110;MAR03111;MAR03112;MAR03113;MAR03114;MAR03115;MAR03116;MAR03117;MAR03118;MAR03122;MAR03123;MAR03125;MAR03129;MAR03130;MAR03132;MAR03136;MAR03137;MAR03139;MAR03150;MAR03151;MAR03153;MAR03170;MAR03171;MAR03172;MAR03173;MAR03174;MAR03175;MAR03176;MAR03177;MAR03218;MAR03219;MAR03220;MAR03221;MAR03222;MAR03223;MAR03224;MAR03225;MAR03226;MAR03227;MAR03228;MAR03229;MAR03230;MAR03231;MAR03232;MAR03233;MAR03234;MAR03235;MAR03236;MAR03237;MAR03239;MAR03240;MAR03241;MAR03242;MAR03243;MAR03244;MAR03245;MAR03246;MAR03247;MAR03250;MAR03252;MAR03254;MAR03256;MAR03258;MAR03260;MAR03262;MAR03264;MAR03272;MAR03396;MAR03397;MAR03408;MAR03411;MAR03414;MAR03416;MAR03422;MAR03423;MAR03424;MAR03425;MAR03430;MAR03431;MAR03432;MAR03433</x:v>
       </x:c>
       <x:c r="L158" s="2" t="n">
-        <x:v>6.121316068875755e-26</x:v>
+        <x:v>5.829824827500719e-26</x:v>
       </x:c>
       <x:c r="M158" s="3" t="b">
         <x:v>1</x:v>
@@ -6671,7 +6671,7 @@
         <x:v>MAR00605;MAR00669;MAR00670;MAR00680</x:v>
       </x:c>
       <x:c r="L160" s="2" t="n">
-        <x:v>0.332000491446845</x:v>
+        <x:v>0.34051332456086664</x:v>
       </x:c>
       <x:c r="M160" s="3" t="b">
         <x:v>0</x:v>
@@ -6831,7 +6831,7 @@
         <x:v>MAR05130;MAR05131;MAR05132;MAR05133;MAR05134;MAR05135;MAR05136;MAR05137;MAR05138;MAR05139;MAR05140;MAR05141;MAR05142;MAR05143;MAR05145;MAR05146;MAR05147;MAR05148;MAR05149;MAR05150</x:v>
       </x:c>
       <x:c r="L164" s="2" t="n">
-        <x:v>9.172581325138887e-22</x:v>
+        <x:v>8.67943179152927e-22</x:v>
       </x:c>
       <x:c r="M164" s="3" t="b">
         <x:v>1</x:v>
@@ -6991,7 +6991,7 @@
         <x:v>MAR00021;MAR00022;MAR00023;MAR00033;MAR00034;MAR04413</x:v>
       </x:c>
       <x:c r="L168" s="2" t="n">
-        <x:v>0.013374658372022365</x:v>
+        <x:v>0.013219396997886119</x:v>
       </x:c>
       <x:c r="M168" s="3" t="b">
         <x:v>1</x:v>
@@ -7151,7 +7151,7 @@
         <x:v>MAR03281;MAR03282;MAR03283;MAR03285;MAR03286;MAR03287;MAR03288;MAR03290;MAR03292;MAR03293;MAR03296;MAR03298</x:v>
       </x:c>
       <x:c r="L172" s="2" t="n">
-        <x:v>1.8832867402874133e-8</x:v>
+        <x:v>1.8234998596433684e-8</x:v>
       </x:c>
       <x:c r="M172" s="3" t="b">
         <x:v>1</x:v>
@@ -7231,7 +7231,7 @@
         <x:v>MAR03107;MAR03108;MAR03109;MAR03110;MAR03111;MAR03112;MAR03113;MAR03114;MAR03115;MAR03116;MAR03117;MAR03118;MAR03122;MAR03123;MAR03125;MAR03129;MAR03130;MAR03132;MAR03136;MAR03137;MAR03139;MAR03150;MAR03151;MAR03153;MAR03407;MAR03408;MAR03409;MAR03411;MAR03414;MAR03416;MAR03422;MAR03423;MAR03424;MAR03425;MAR03428;MAR03430;MAR03431;MAR03432;MAR03433;MAR09719</x:v>
       </x:c>
       <x:c r="L174" s="2" t="n">
-        <x:v>1.251123005284396e-29</x:v>
+        <x:v>1.1121093380305743e-29</x:v>
       </x:c>
       <x:c r="M174" s="3" t="b">
         <x:v>1</x:v>
@@ -7311,7 +7311,7 @@
         <x:v>MAR03170;MAR03171;MAR03172;MAR03173;MAR03174;MAR03175;MAR03176;MAR03177;MAR03396;MAR03397</x:v>
       </x:c>
       <x:c r="L176" s="2" t="n">
-        <x:v>0.003946685610086423</x:v>
+        <x:v>0.0038589814854178357</x:v>
       </x:c>
       <x:c r="M176" s="3" t="b">
         <x:v>1</x:v>
@@ -7469,7 +7469,7 @@
         <x:v>MAR03240;MAR03241;MAR03242;MAR03243;MAR03244;MAR03245;MAR03246;MAR03247;MAR03250;MAR03252;MAR03254;MAR03256;MAR03258;MAR03260;MAR03262;MAR03264;MAR03272</x:v>
       </x:c>
       <x:c r="L180" s="2" t="n">
-        <x:v>1.8184488159733523e-18</x:v>
+        <x:v>1.6952476766797642e-18</x:v>
       </x:c>
       <x:c r="M180" s="3" t="b">
         <x:v>1</x:v>
@@ -7549,7 +7549,7 @@
         <x:v>MAR03218;MAR03219;MAR03220;MAR03221;MAR03222;MAR03223;MAR03224;MAR03225;MAR03226;MAR03227;MAR03228;MAR03229;MAR03230;MAR03231;MAR03232;MAR03233;MAR03234;MAR03235;MAR03236;MAR03237;MAR03239</x:v>
       </x:c>
       <x:c r="L182" s="2" t="n">
-        <x:v>7.590781567736402e-23</x:v>
+        <x:v>7.247165941213354e-23</x:v>
       </x:c>
       <x:c r="M182" s="3" t="b">
         <x:v>1</x:v>
@@ -7904,7 +7904,7 @@
         <x:v>MAR08667;MAR08668</x:v>
       </x:c>
       <x:c r="L191" s="2" t="n">
-        <x:v>0.5796894582014015</x:v>
+        <x:v>0.5940619241072214</x:v>
       </x:c>
       <x:c r="M191" s="3" t="b">
         <x:v>0</x:v>
@@ -7945,7 +7945,7 @@
         <x:v>MAR02591;MAR02594;MAR02599;MAR02602;MAR02605;MAR02611;MAR02614;MAR02620;MAR02623;MAR02626;MAR02633;MAR02648;MAR02651;MAR02657;MAR02660;MAR02666;MAR02669;MAR02672;MAR02675;MAR02678;MAR02681;MAR02684;MAR02687;MAR02693;MAR02699;MAR02702;MAR02705;MAR02708;MAR02714;MAR02720;MAR02730;MAR02733;MAR02736;MAR02739;MAR02742;MAR02746;MAR02759;MAR02762;MAR02768;MAR02771;MAR02774;MAR02877;MAR03032</x:v>
       </x:c>
       <x:c r="L192" s="2" t="n">
-        <x:v>5.327842862934128e-35</x:v>
+        <x:v>4.7358603226081143e-35</x:v>
       </x:c>
       <x:c r="M192" s="3" t="b">
         <x:v>1</x:v>
@@ -8027,7 +8027,7 @@
         <x:v>MAR02593;MAR02603;MAR02604;MAR02606;MAR02607;MAR02616;MAR02618;MAR02621;MAR02622;MAR02624;MAR02625;MAR02634;MAR02635;MAR02649;MAR02650;MAR02652;MAR02653;MAR02661;MAR02662;MAR02668;MAR02670;MAR02671;MAR02673;MAR02674;MAR02676;MAR02677;MAR02679;MAR02680;MAR02682;MAR02683;MAR02685;MAR02686;MAR02688;MAR02689;MAR02695;MAR02697;MAR02700;MAR02701;MAR02703;MAR02704;MAR02706;MAR02707;MAR02709;MAR02710;MAR02715;MAR02716;MAR02722;MAR02724;MAR02731;MAR02732;MAR02734;MAR02735;MAR02737;MAR02738;MAR02740;MAR02741;MAR02748;MAR02750;MAR02764;MAR02766;MAR02769;MAR02770;MAR02772;MAR02773;MAR02775;MAR02776</x:v>
       </x:c>
       <x:c r="L194" s="2" t="n">
-        <x:v>2.700919779960906e-43</x:v>
+        <x:v>2.400817582187472e-43</x:v>
       </x:c>
       <x:c r="M194" s="3" t="b">
         <x:v>1</x:v>
@@ -8068,7 +8068,7 @@
         <x:v>MAR03029;MAR03030;MAR03033;MAR03034</x:v>
       </x:c>
       <x:c r="L195" s="2" t="n">
-        <x:v>0.01534234725603021</x:v>
+        <x:v>0.015119994397247165</x:v>
       </x:c>
       <x:c r="M195" s="3" t="b">
         <x:v>1</x:v>
@@ -8581,7 +8581,7 @@
         <x:v>MAR07598;MAR07600;MAR07614;MAR07615;MAR10061</x:v>
       </x:c>
       <x:c r="L208" s="2" t="n">
-        <x:v>0.042008480814817555</x:v>
+        <x:v>0.04267740309243088</x:v>
       </x:c>
       <x:c r="M208" s="3" t="b">
         <x:v>1</x:v>
@@ -8782,7 +8782,7 @@
         <x:v>MAR00144;MAR00145;MAR00146;MAR00148;MAR00152;MAR00181;MAR00186;MAR00218;MAR00747;MAR02150;MAR02151</x:v>
       </x:c>
       <x:c r="L213" s="2" t="n">
-        <x:v>0.1037499319382601</x:v>
+        <x:v>0.10388882073603554</x:v>
       </x:c>
       <x:c r="M213" s="3" t="b">
         <x:v>0</x:v>
@@ -8823,7 +8823,7 @@
         <x:v>MAR02152;MAR02153;MAR02154;MAR02155;MAR02156;MAR02157;MAR02158;MAR02159;MAR02160;MAR02161;MAR02162;MAR02163</x:v>
       </x:c>
       <x:c r="L214" s="2" t="n">
-        <x:v>0.00002417383981184238</x:v>
+        <x:v>0.000023391844993737772</x:v>
       </x:c>
       <x:c r="M214" s="3" t="b">
         <x:v>1</x:v>
@@ -8981,7 +8981,7 @@
         <x:v>MAR02282;MAR02365</x:v>
       </x:c>
       <x:c r="L218" s="2" t="n">
-        <x:v>0.9952843561633469</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M218" s="3" t="b">
         <x:v>0</x:v>
@@ -9022,7 +9022,7 @@
         <x:v>MAR02288</x:v>
       </x:c>
       <x:c r="L219" s="2" t="n">
-        <x:v>0.6715728215577712</x:v>
+        <x:v>0.6806175733632631</x:v>
       </x:c>
       <x:c r="M219" s="3" t="b">
         <x:v>0</x:v>
@@ -9182,7 +9182,7 @@
         <x:v>MAR00108;MAR00465;MAR00974;MAR00975;MAR00977;MAR00978;MAR00982;MAR01001;MAR01005;MAR02028;MAR02121;MAR02148;MAR02149;MAR02183;MAR02187;MAR02207;MAR03371;MAR03437;MAR03438;MAR03442;MAR03479;MAR03507;MAR03535;MAR04003;MAR04719;MAR04967;MAR05030;MAR05110;MAR05185;MAR05343;MAR05449;MAR05988;MAR06279;MAR06319;MAR06347</x:v>
       </x:c>
       <x:c r="L223" s="2" t="n">
-        <x:v>0.694254666370857</x:v>
+        <x:v>0.7023140074398387</x:v>
       </x:c>
       <x:c r="M223" s="3" t="b">
         <x:v>0</x:v>
@@ -9502,7 +9502,7 @@
         <x:v>MAR00129;MAR00579;MAR00580;MAR00581;MAR00598;MAR00599;MAR00614;MAR00615;MAR00616;MAR00632;MAR00642;MAR00643;MAR00644;MAR00648;MAR00651;MAR00660;MAR07591;MAR07594;MAR07597;MAR07601</x:v>
       </x:c>
       <x:c r="L231" s="2" t="n">
-        <x:v>0.00006427831414520372</x:v>
+        <x:v>0.00006178690662019582</x:v>
       </x:c>
       <x:c r="M231" s="3" t="b">
         <x:v>1</x:v>
@@ -9898,7 +9898,7 @@
         <x:v>MAR11321</x:v>
       </x:c>
       <x:c r="L241" s="2" t="n">
-        <x:v>0.6715728215577712</x:v>
+        <x:v>0.6806175733632631</x:v>
       </x:c>
       <x:c r="M241" s="3" t="b">
         <x:v>0</x:v>
@@ -10372,7 +10372,7 @@
         <x:v>MAR06402;MAR06403</x:v>
       </x:c>
       <x:c r="L253" s="2" t="n">
-        <x:v>0.20116701728542902</x:v>
+        <x:v>0.2018880460212191</x:v>
       </x:c>
       <x:c r="M253" s="3" t="b">
         <x:v>0</x:v>
@@ -10573,7 +10573,7 @@
         <x:v>MAR00060;MAR00061;MAR00229;MAR00578;MAR02127;MAR02141;MAR02225;MAR02377;MAR02379;MAR03789;MAR03946;MAR03949;MAR03952;MAR04760;MAR04852;MAR04855;MAR04874;MAR04888;MAR04898;MAR04905;MAR04914;MAR04926;MAR04957;MAR04963;MAR05006;MAR05043;MAR05126;MAR05227;MAR05304;MAR05361;MAR06286;MAR06295;MAR06298;MAR06328;MAR06438;MAR06454;MAR06469;MAR06481;MAR06513;MAR07638;MAR08009;MAR08428;MAR08430;MAR08614;MAR08891;MAR08987;MAR08998;MAR10049;MAR13080;MAR20137;MAR20138;MAR20139;MAR20149;MAR20152;MAR20155;MAR20160;MAR20164</x:v>
       </x:c>
       <x:c r="L258" s="2" t="n">
-        <x:v>0.00319972646596661</x:v>
+        <x:v>0.0031125221807306223</x:v>
       </x:c>
       <x:c r="M258" s="3" t="b">
         <x:v>1</x:v>
@@ -10653,7 +10653,7 @@
         <x:v>MAR00712;MAR01542;MAR04265;MAR04269;MAR08791</x:v>
       </x:c>
       <x:c r="L260" s="2" t="n">
-        <x:v>0.3515317807816641</x:v>
+        <x:v>0.3603154031616419</x:v>
       </x:c>
       <x:c r="M260" s="3" t="b">
         <x:v>0</x:v>
@@ -10694,7 +10694,7 @@
         <x:v>MAR01095;MAR05422;MAR05423;MAR07765;MAR07767;MAR07786;MAR07792;MAR07796;MAR07857;MAR07860;MAR07861;MAR07862;MAR13086</x:v>
       </x:c>
       <x:c r="L261" s="2" t="n">
-        <x:v>0.15334240700223517</x:v>
+        <x:v>0.1544257509181148</x:v>
       </x:c>
       <x:c r="M261" s="3" t="b">
         <x:v>0</x:v>
@@ -10735,7 +10735,7 @@
         <x:v>MAR03967;MAR03968;MAR04024;MAR07160;MAR07161;MAR07863;MAR07886;MAR08456;MAR08467;MAR08471;MAR08482;MAR08486</x:v>
       </x:c>
       <x:c r="L262" s="2" t="n">
-        <x:v>0.5156704469078927</x:v>
+        <x:v>0.5285926850573576</x:v>
       </x:c>
       <x:c r="M262" s="3" t="b">
         <x:v>0</x:v>
@@ -10895,7 +10895,7 @@
         <x:v>MAR03452;MAR03453;MAR03454;MAR03455;MAR03456;MAR03457;MAR03458</x:v>
       </x:c>
       <x:c r="L266" s="2" t="n">
-        <x:v>0.682599604386712</x:v>
+        <x:v>0.6914719682173148</x:v>
       </x:c>
       <x:c r="M266" s="3" t="b">
         <x:v>0</x:v>
@@ -10936,7 +10936,7 @@
         <x:v>MAR03977;MAR06911;MAR06912;MAR06914;MAR06916;MAR06918;MAR06921</x:v>
       </x:c>
       <x:c r="L267" s="2" t="n">
-        <x:v>0.00001994599827198092</x:v>
+        <x:v>0.000019320910007047044</x:v>
       </x:c>
       <x:c r="M267" s="3" t="b">
         <x:v>1</x:v>
@@ -11055,7 +11055,7 @@
         <x:v>MAR04350;MAR04354;MAR04398;MAR04710</x:v>
       </x:c>
       <x:c r="L270" s="2" t="n">
-        <x:v>0.5626441331322158</x:v>
+        <x:v>0.5772312032504585</x:v>
       </x:c>
       <x:c r="M270" s="3" t="b">
         <x:v>0</x:v>
@@ -11135,7 +11135,7 @@
         <x:v>MAR00063;MAR00075;MAR00127;MAR00713;MAR01462;MAR01561;MAR01562;MAR01633;MAR02278;MAR02407;MAR02412;MAR02509;MAR02514;MAR03019;MAR03020;MAR03022;MAR03024;MAR03025;MAR03106;MAR03947;MAR04900;MAR04924;MAR07590;MAR07596;MAR07777;MAR07779;MAR08980;MAR09680;MAR10039;MAR10040</x:v>
       </x:c>
       <x:c r="L272" s="2" t="n">
-        <x:v>0.00003137598904665884</x:v>
+        <x:v>0.00003027060189867357</x:v>
       </x:c>
       <x:c r="M272" s="3" t="b">
         <x:v>1</x:v>
@@ -11572,7 +11572,7 @@
         <x:v>MAR04002;MAR04004;MAR04010;MAR04135;MAR04453;MAR04482;MAR04574;MAR04603;MAR04611;MAR04614;MAR04695</x:v>
       </x:c>
       <x:c r="L283" s="2" t="n">
-        <x:v>0.716620173690155</x:v>
+        <x:v>0.7242877146432184</x:v>
       </x:c>
       <x:c r="M283" s="3" t="b">
         <x:v>0</x:v>
@@ -11613,7 +11613,7 @@
         <x:v>MAR03931;MAR03970;MAR04008;MAR04028;MAR04030;MAR04032;MAR04579;MAR04644;MAR04673;MAR06621;MAR08274</x:v>
       </x:c>
       <x:c r="L284" s="2" t="n">
-        <x:v>0.09620174651807363</x:v>
+        <x:v>0.09680678894900491</x:v>
       </x:c>
       <x:c r="M284" s="3" t="b">
         <x:v>0</x:v>
@@ -11695,7 +11695,7 @@
         <x:v>MAR03960;MAR03980;MAR04767</x:v>
       </x:c>
       <x:c r="L286" s="2" t="n">
-        <x:v>0.2170898317891889</x:v>
+        <x:v>0.21835936296924263</x:v>
       </x:c>
       <x:c r="M286" s="3" t="b">
         <x:v>0</x:v>
@@ -11736,7 +11736,7 @@
         <x:v>MAR06632;MAR06634;MAR06638;MAR06641;MAR06642;MAR06644;MAR06648;MAR06649;MAR06651;MAR06652;MAR06654;MAR06655;MAR06656;MAR06657;MAR06658;MAR06660;MAR06664;MAR06665;MAR06668;MAR06669;MAR06673;MAR06677;MAR06678;MAR06682;MAR06687;MAR06690;MAR06691;MAR06692;MAR06693;MAR06700;MAR06701;MAR06702;MAR06703;MAR08698;MAR08699;MAR08702;MAR08709;MAR08711</x:v>
       </x:c>
       <x:c r="L287" s="2" t="n">
-        <x:v>8.906508958881402e-20</x:v>
+        <x:v>8.344837222735727e-20</x:v>
       </x:c>
       <x:c r="M287" s="3" t="b">
         <x:v>1</x:v>
@@ -12173,7 +12173,7 @@
         <x:v>MAR00710;MAR03957;MAR04139;MAR04141;MAR04145;MAR04147;MAR04152;MAR04408;MAR04410;MAR04458;MAR04589;MAR04652;MAR08981</x:v>
       </x:c>
       <x:c r="L298" s="2" t="n">
-        <x:v>8.35753527541428e-7</x:v>
+        <x:v>7.98331727800767e-7</x:v>
       </x:c>
       <x:c r="M298" s="3" t="b">
         <x:v>1</x:v>
@@ -12333,7 +12333,7 @@
         <x:v>ASCTm;MAR15020m</x:v>
       </x:c>
       <x:c r="L302" s="2" t="n">
-        <x:v>0.48624945097331995</x:v>
+        <x:v>0.5007679123092831</x:v>
       </x:c>
       <x:c r="M302" s="3" t="b">
         <x:v>0</x:v>
@@ -12495,7 +12495,7 @@
         <x:v>MAR08613;MAR08615;MAR08616</x:v>
       </x:c>
       <x:c r="L306" s="2" t="n">
-        <x:v>0.014446567123614605</x:v>
+        <x:v>0.01425772310892683</x:v>
       </x:c>
       <x:c r="M306" s="3" t="b">
         <x:v>1</x:v>
@@ -12653,7 +12653,7 @@
         <x:v>MAR02129;MAR02130;MAR02131;MAR02132;MAR02133;MAR02134;MAR02135;MAR02136;MAR02137;MAR02139;MAR02142;MAR02143;MAR02144;MAR02145</x:v>
       </x:c>
       <x:c r="L310" s="2" t="n">
-        <x:v>9.051479440584814e-7</x:v>
+        <x:v>8.620456610080775e-7</x:v>
       </x:c>
       <x:c r="M310" s="3" t="b">
         <x:v>1</x:v>
@@ -12694,7 +12694,7 @@
         <x:v>MAR06436;MAR06453;MAR06465;MAR06467;MAR06470;MAR06471;MAR06472;MAR06473;MAR06476;MAR06478;MAR06482;MAR06484;MAR06486;MAR06488;MAR06492</x:v>
       </x:c>
       <x:c r="L311" s="2" t="n">
-        <x:v>9.051479440584814e-7</x:v>
+        <x:v>8.620456610080775e-7</x:v>
       </x:c>
       <x:c r="M311" s="3" t="b">
         <x:v>1</x:v>
@@ -12815,7 +12815,7 @@
         <x:v>MAR02591;MAR02593;MAR02594;MAR02599;MAR02602;MAR02603;MAR02604;MAR02605;MAR02606;MAR02607;MAR02611;MAR02614;MAR02616;MAR02618;MAR02620;MAR02621;MAR02622;MAR02623;MAR02624;MAR02625;MAR02626;MAR02633;MAR02634;MAR02635;MAR02648;MAR02649;MAR02650;MAR02651;MAR02652;MAR02653;MAR02657;MAR02660;MAR02661;MAR02662;MAR02666;MAR02668;MAR02669;MAR02670;MAR02671;MAR02672;MAR02673;MAR02674;MAR02675;MAR02676;MAR02677;MAR02678;MAR02679;MAR02680;MAR02681;MAR02682;MAR02683;MAR02684;MAR02685;MAR02686;MAR02687;MAR02688;MAR02689;MAR02693;MAR02695;MAR02697;MAR02699;MAR02700;MAR02701;MAR02702;MAR02703;MAR02704;MAR02705;MAR02706;MAR02707;MAR02708;MAR02709;MAR02710;MAR02714;MAR02715;MAR02716;MAR02720;MAR02722;MAR02724;MAR02730;MAR02731;MAR02732;MAR02733;MAR02734;MAR02735;MAR02736;MAR02737;MAR02738;MAR02739;MAR02740;MAR02741;MAR02742;MAR02746;MAR02748;MAR02750;MAR02759;MAR02762;MAR02764;MAR02766;MAR02768;MAR02769;MAR02770;MAR02771;MAR02772;MAR02773;MAR02774;MAR02775;MAR02776;MAR02869;MAR02870;MAR02877;MAR02878;MAR02879;MAR02896;MAR02897;MAR02924;MAR02925;MAR02926;MAR03029;MAR03030;MAR03032;MAR03033;MAR03034</x:v>
       </x:c>
       <x:c r="L314" s="2" t="n">
-        <x:v>8.640021484156079e-56</x:v>
+        <x:v>7.680019097027626e-56</x:v>
       </x:c>
       <x:c r="M314" s="3" t="b">
         <x:v>1</x:v>
@@ -12856,7 +12856,7 @@
         <x:v>MAR03107;MAR03108;MAR03109;MAR03110;MAR03111;MAR03112;MAR03113;MAR03114;MAR03115;MAR03116;MAR03117;MAR03118;MAR03122;MAR03123;MAR03125;MAR03129;MAR03130;MAR03132;MAR03136;MAR03137;MAR03139;MAR03150;MAR03151;MAR03153;MAR03170;MAR03171;MAR03172;MAR03173;MAR03174;MAR03175;MAR03176;MAR03177;MAR03218;MAR03219;MAR03220;MAR03221;MAR03222;MAR03223;MAR03224;MAR03225;MAR03226;MAR03227;MAR03228;MAR03229;MAR03230;MAR03231;MAR03232;MAR03233;MAR03234;MAR03235;MAR03236;MAR03237;MAR03239;MAR03240;MAR03241;MAR03242;MAR03243;MAR03244;MAR03245;MAR03246;MAR03247;MAR03250;MAR03252;MAR03254;MAR03256;MAR03258;MAR03260;MAR03262;MAR03264;MAR03272;MAR03281;MAR03282;MAR03283;MAR03285;MAR03286;MAR03287;MAR03288;MAR03290;MAR03292;MAR03293;MAR03296;MAR03298;MAR03396;MAR03397;MAR03407;MAR03408;MAR03409;MAR03411;MAR03414;MAR03416;MAR03422;MAR03423;MAR03424;MAR03425;MAR03428;MAR03430;MAR03431;MAR03432;MAR03433;MAR09719</x:v>
       </x:c>
       <x:c r="L315" s="2" t="n">
-        <x:v>5.327842862934128e-35</x:v>
+        <x:v>4.7358603226081143e-35</x:v>
       </x:c>
       <x:c r="M315" s="3" t="b">
         <x:v>1</x:v>
@@ -12936,7 +12936,7 @@
         <x:v>MAR00604;MAR00605;MAR00668;MAR00670;MAR00683;MAR07588</x:v>
       </x:c>
       <x:c r="L317" s="2" t="n">
-        <x:v>0.0045065664054656845</x:v>
+        <x:v>0.004385700639801854</x:v>
       </x:c>
       <x:c r="M317" s="3" t="b">
         <x:v>1</x:v>
@@ -12977,7 +12977,7 @@
         <x:v>MAR03804;MAR03827;MAR03829;MAR03899;MAR04172</x:v>
       </x:c>
       <x:c r="L318" s="2" t="n">
-        <x:v>0.1037499319382601</x:v>
+        <x:v>0.10388882073603554</x:v>
       </x:c>
       <x:c r="M318" s="3" t="b">
         <x:v>0</x:v>
@@ -13096,7 +13096,7 @@
         <x:v>MAR05130;MAR05131;MAR05132;MAR05133;MAR05134;MAR05135;MAR05136;MAR05137;MAR05138;MAR05139;MAR05140;MAR05141;MAR05142;MAR05143;MAR05145;MAR05146;MAR05147;MAR05148;MAR05149;MAR05150</x:v>
       </x:c>
       <x:c r="L321" s="2" t="n">
-        <x:v>1.0074978203477702e-24</x:v>
+        <x:v>9.362606007272209e-25</x:v>
       </x:c>
       <x:c r="M321" s="3" t="b">
         <x:v>1</x:v>
@@ -13256,7 +13256,7 @@
         <x:v>MAR00021;MAR00022;MAR00023;MAR00033;MAR00034;MAR04413</x:v>
       </x:c>
       <x:c r="L325" s="2" t="n">
-        <x:v>0.0026296245124973385</x:v>
+        <x:v>0.002537796354918066</x:v>
       </x:c>
       <x:c r="M325" s="3" t="b">
         <x:v>1</x:v>
@@ -13336,7 +13336,7 @@
         <x:v>MAR06396;MAR08619</x:v>
       </x:c>
       <x:c r="L327" s="2" t="n">
-        <x:v>0.7500660081818816</x:v>
+        <x:v>0.7577542616482805</x:v>
       </x:c>
       <x:c r="M327" s="3" t="b">
         <x:v>0</x:v>
@@ -13494,7 +13494,7 @@
         <x:v>MAR03136;MAR03137;MAR03139;MAR03150;MAR03151;MAR03153</x:v>
       </x:c>
       <x:c r="L331" s="2" t="n">
-        <x:v>0.4715558089657251</x:v>
+        <x:v>0.4874402932295278</x:v>
       </x:c>
       <x:c r="M331" s="3" t="b">
         <x:v>0</x:v>
@@ -13730,7 +13730,7 @@
         <x:v>MAR03250;MAR03252;MAR03254;MAR03256;MAR03258;MAR03260;MAR03262;MAR03264;MAR03272</x:v>
       </x:c>
       <x:c r="L337" s="2" t="n">
-        <x:v>8.676703053292227e-7</x:v>
+        <x:v>8.279729710984739e-7</x:v>
       </x:c>
       <x:c r="M337" s="3" t="b">
         <x:v>1</x:v>
@@ -14163,7 +14163,7 @@
         <x:v>MAR08662;MAR08663;MAR08667;MAR08668</x:v>
       </x:c>
       <x:c r="L348" s="2" t="n">
-        <x:v>0.0047040342078416815</x:v>
+        <x:v>0.00456787635495364</x:v>
       </x:c>
       <x:c r="M348" s="3" t="b">
         <x:v>1</x:v>
@@ -14838,7 +14838,7 @@
         <x:v>MAR07598;MAR07614;MAR10061</x:v>
       </x:c>
       <x:c r="L365" s="2" t="n">
-        <x:v>0.2894817866971283</x:v>
+        <x:v>0.2966118799655305</x:v>
       </x:c>
       <x:c r="M365" s="3" t="b">
         <x:v>0</x:v>
@@ -14879,7 +14879,7 @@
         <x:v>MAR00569;MAR00574;MAR00628;MAR00656;MAR00658;MAR00661;MAR00714;MAR01871;MAR01922;MAR01939;MAR04110;MAR04146;MAR04181;MAR04341;MAR04349;MAR04384;MAR04392;MAR04859;MAR04886;MAR04899;MAR08966;MAR09026;MAR09038;MAR09039;MAR09040;MAR09041;MAR09042;MAR09044;MAR09045;MAR09046;MAR09047;MAR09062;MAR09063;MAR09064;MAR09066;MAR09067;MAR09069;MAR09071;MAR09072;MAR09075;MAR09076;MAR09079;MAR09103;MAR09107;MAR09108;MAR09109;MAR09143;MAR09151;MAR09153;MAR09172;MAR09215;MAR09242;MAR09253;MAR09255;MAR09259;MAR09269;MAR09271;MAR09273;MAR09285;MAR09292;MAR09295;MAR09298;MAR09300;MAR09310;MAR09354;MAR09378;MAR09383;MAR09404;MAR09406;MAR09438;MAR09440;MAR09702;MAR09729;MAR09847;MAR09849;MAR09858;MAR09860;MAR09861;MAR09862;MAR09864;MAR09868;MAR09920;MAR09921;MAR09925;MAR10024;MAR10047;MAR10188;MAR10193;MAR10197;MAR10243;MAR10250;MAR10438;MAR10496;MAR11400;MAR11424;MAR11428;MAR11895;MAR11897;MAR11929;MAR11947;MAR11953;MAR11959;MAR11965;MAR12127</x:v>
       </x:c>
       <x:c r="L366" s="2" t="n">
-        <x:v>0.1632634002760863</x:v>
+        <x:v>0.16502560840605038</x:v>
       </x:c>
       <x:c r="M366" s="3" t="b">
         <x:v>0</x:v>
@@ -15080,7 +15080,7 @@
         <x:v>MAR02152;MAR02153;MAR02154;MAR02155;MAR02156;MAR02157;MAR02158;MAR02159;MAR02160;MAR02161;MAR02162;MAR02163</x:v>
       </x:c>
       <x:c r="L371" s="2" t="n">
-        <x:v>6.231421897342697e-7</x:v>
+        <x:v>5.95866605671827e-7</x:v>
       </x:c>
       <x:c r="M371" s="3" t="b">
         <x:v>1</x:v>
@@ -15755,7 +15755,7 @@
         <x:v>MAR00129;MAR00579;MAR00580;MAR00581;MAR00589;MAR00592;MAR00597;MAR00598;MAR00600;MAR00614;MAR00632;MAR00642;MAR00643;MAR00648;MAR00651;MAR07591;MAR07594;MAR07597;MAR07601</x:v>
       </x:c>
       <x:c r="L388" s="2" t="n">
-        <x:v>0.0000014290646139893526</x:v>
+        <x:v>0.000001393779067964924</x:v>
       </x:c>
       <x:c r="M388" s="3" t="b">
         <x:v>1</x:v>
@@ -16623,7 +16623,7 @@
         <x:v>MAR06402;MAR06403</x:v>
       </x:c>
       <x:c r="L410" s="2" t="n">
-        <x:v>0.11227760579475277</x:v>
+        <x:v>0.1127943337635649</x:v>
       </x:c>
       <x:c r="M410" s="3" t="b">
         <x:v>0</x:v>
@@ -16824,7 +16824,7 @@
         <x:v>MAR00061;MAR00182;MAR00578;MAR01694;MAR01774;MAR02127;MAR02141;MAR02379;MAR02413;MAR02416;MAR03789;MAR03825;MAR03946;MAR04756;MAR04855;MAR04874;MAR04888;MAR04898;MAR04905;MAR04914;MAR04922;MAR04957;MAR05043;MAR05116;MAR05126;MAR05227;MAR05304;MAR05361;MAR05420;MAR06286;MAR06287;MAR06291;MAR06294;MAR06295;MAR06298;MAR06328;MAR06438;MAR06454;MAR06469;MAR06481;MAR06513;MAR07638;MAR08009;MAR08614;MAR08891;MAR08987;MAR08998;MAR10049;MAR11443;MAR13080;MAR20132;MAR20137;MAR20139;MAR20147;MAR20151;MAR20152;MAR20160;MAR20162;MAR20163</x:v>
       </x:c>
       <x:c r="L415" s="2" t="n">
-        <x:v>1.2713087898924648e-8</x:v>
+        <x:v>1.1916914717375831e-8</x:v>
       </x:c>
       <x:c r="M415" s="3" t="b">
         <x:v>1</x:v>
@@ -16904,7 +16904,7 @@
         <x:v>MAR01542;MAR04265;MAR04269;MAR08791</x:v>
       </x:c>
       <x:c r="L417" s="2" t="n">
-        <x:v>0.36089731518367674</x:v>
+        <x:v>0.36968105936275036</x:v>
       </x:c>
       <x:c r="M417" s="3" t="b">
         <x:v>0</x:v>
@@ -16945,7 +16945,7 @@
         <x:v>MAR01095;MAR05422;MAR05423;MAR07765;MAR07767;MAR07786;MAR07792;MAR07796;MAR07857;MAR07860;MAR07861;MAR07862;MAR13086</x:v>
       </x:c>
       <x:c r="L418" s="2" t="n">
-        <x:v>0.011042153918890492</x:v>
+        <x:v>0.010939131278425865</x:v>
       </x:c>
       <x:c r="M418" s="3" t="b">
         <x:v>1</x:v>
@@ -16986,7 +16986,7 @@
         <x:v>MAR03968;MAR04024;MAR04344;MAR04640;MAR04680;MAR07160;MAR07161;MAR07863;MAR07871;MAR07883;MAR07886;MAR08456;MAR08465;MAR08467;MAR08482;MAR08486</x:v>
       </x:c>
       <x:c r="L419" s="2" t="n">
-        <x:v>0.0016307518882236155</x:v>
+        <x:v>0.0015787257003704968</x:v>
       </x:c>
       <x:c r="M419" s="3" t="b">
         <x:v>1</x:v>
@@ -17183,7 +17183,7 @@
         <x:v>MAR03977;MAR06911;MAR06912;MAR06914;MAR06916;MAR06918;MAR06921</x:v>
       </x:c>
       <x:c r="L424" s="2" t="n">
-        <x:v>0.0000018706964722682471</x:v>
+        <x:v>0.0000018222918451319303</x:v>
       </x:c>
       <x:c r="M424" s="3" t="b">
         <x:v>1</x:v>
@@ -17302,7 +17302,7 @@
         <x:v>MAR04350;MAR04354;MAR04398;MAR04710</x:v>
       </x:c>
       <x:c r="L427" s="2" t="n">
-        <x:v>0.2463505282352108</x:v>
+        <x:v>0.2492983123337518</x:v>
       </x:c>
       <x:c r="M427" s="3" t="b">
         <x:v>0</x:v>
@@ -17585,7 +17585,7 @@
         <x:v>MAR01044;MAR04750;MAR04752;MAR04762;MAR04769;MAR04770;MAR11316;MAR11406</x:v>
       </x:c>
       <x:c r="L434" s="2" t="n">
-        <x:v>0.00008622803130841069</x:v>
+        <x:v>0.00008369515171697589</x:v>
       </x:c>
       <x:c r="M434" s="3" t="b">
         <x:v>1</x:v>
@@ -17823,7 +17823,7 @@
         <x:v>MAR04002;MAR04004;MAR04010;MAR04135;MAR04453;MAR04518;MAR04603;MAR04611;MAR04614;MAR04663;MAR06603</x:v>
       </x:c>
       <x:c r="L440" s="2" t="n">
-        <x:v>0.15021644632120157</x:v>
+        <x:v>0.1513809148973349</x:v>
       </x:c>
       <x:c r="M440" s="3" t="b">
         <x:v>0</x:v>
@@ -17864,7 +17864,7 @@
         <x:v>MAR03931;MAR04008;MAR04030;MAR04635;MAR04637;MAR04644;MAR04673;MAR04675;MAR04676;MAR06621;MAR08274</x:v>
       </x:c>
       <x:c r="L441" s="2" t="n">
-        <x:v>0.008293217493292905</x:v>
+        <x:v>0.00826344054325633</x:v>
       </x:c>
       <x:c r="M441" s="3" t="b">
         <x:v>1</x:v>
@@ -17946,7 +17946,7 @@
         <x:v>MAR03960;MAR03980;MAR04767</x:v>
       </x:c>
       <x:c r="L443" s="2" t="n">
-        <x:v>0.09921196732556468</x:v>
+        <x:v>0.09962024702649294</x:v>
       </x:c>
       <x:c r="M443" s="3" t="b">
         <x:v>0</x:v>
@@ -17987,7 +17987,7 @@
         <x:v>MAR06632;MAR06634;MAR06638;MAR06641;MAR06642;MAR06644;MAR06648;MAR06649;MAR06651;MAR06652;MAR06653;MAR06654;MAR06655;MAR06656;MAR06657;MAR06658;MAR06660;MAR06664;MAR06665;MAR06668;MAR06669;MAR06673;MAR06677;MAR06678;MAR06682;MAR06687;MAR06690;MAR06691;MAR06692;MAR06693;MAR06700;MAR06701;MAR06702;MAR06703;MAR08698;MAR08699;MAR08702;MAR08709;MAR08711</x:v>
       </x:c>
       <x:c r="L444" s="2" t="n">
-        <x:v>4.3971787428161e-26</x:v>
+        <x:v>4.209265121328232e-26</x:v>
       </x:c>
       <x:c r="M444" s="3" t="b">
         <x:v>1</x:v>
@@ -18422,7 +18422,7 @@
         <x:v>MAR04139;MAR04141;MAR04145;MAR04147;MAR04152;MAR04408;MAR04410;MAR04458;MAR04589;MAR04652</x:v>
       </x:c>
       <x:c r="L455" s="2" t="n">
-        <x:v>0.00001886478816250074</x:v>
+        <x:v>0.000018293127915152228</x:v>
       </x:c>
       <x:c r="M455" s="3" t="b">
         <x:v>1</x:v>
@@ -18580,7 +18580,7 @@
         <x:v>ASCTm;MAR15020m</x:v>
       </x:c>
       <x:c r="L459" s="2" t="n">
-        <x:v>0.2894817866971283</x:v>
+        <x:v>0.2966118799655305</x:v>
       </x:c>
       <x:c r="M459" s="3" t="b">
         <x:v>0</x:v>
@@ -18740,7 +18740,7 @@
         <x:v>MAR08613;MAR08615;MAR08616</x:v>
       </x:c>
       <x:c r="L463" s="2" t="n">
-        <x:v>0.005804698176998718</x:v>
+        <x:v>0.005628798232241181</x:v>
       </x:c>
       <x:c r="M463" s="3" t="b">
         <x:v>1</x:v>
@@ -18898,7 +18898,7 @@
         <x:v>MAR02129;MAR02131;MAR02133;MAR02134;MAR02135;MAR02136;MAR02137;MAR02138;MAR02139;MAR02142;MAR02143;MAR02144;MAR02145;MAR02767</x:v>
       </x:c>
       <x:c r="L467" s="2" t="n">
-        <x:v>1.2405538134669782e-8</x:v>
+        <x:v>1.1639764175739548e-8</x:v>
       </x:c>
       <x:c r="M467" s="3" t="b">
         <x:v>1</x:v>
@@ -18939,7 +18939,7 @@
         <x:v>MAR06436;MAR06453;MAR06465;MAR06467;MAR06470;MAR06471;MAR06472;MAR06473;MAR06476;MAR06478;MAR06482;MAR06484;MAR06486;MAR06488;MAR06492</x:v>
       </x:c>
       <x:c r="L468" s="2" t="n">
-        <x:v>9.541800696296479e-9</x:v>
+        <x:v>8.961691220001724e-9</x:v>
       </x:c>
       <x:c r="M468" s="3" t="b">
         <x:v>1</x:v>
@@ -19019,7 +19019,7 @@
         <x:v>MAR00018;MAR00019;MAR00061;MAR00089;MAR00142;MAR00182;MAR00569;MAR00574;MAR00578;MAR00628;MAR00656;MAR00658;MAR00661;MAR00714;MAR01095;MAR01461;MAR01462;MAR01499;MAR01525;MAR01528;MAR01529;MAR01601;MAR01607;MAR01633;MAR01669;MAR01694;MAR01774;MAR01827;MAR01871;MAR01922;MAR01939;MAR02127;MAR02141;MAR02278;MAR02351;MAR02379;MAR02382;MAR02413;MAR02416;MAR03597;MAR03789;MAR03825;MAR03946;MAR03959;MAR04110;MAR04146;MAR04181;MAR04341;MAR04349;MAR04384;MAR04392;MAR04756;MAR04765;MAR04847;MAR04855;MAR04859;MAR04874;MAR04883;MAR04885;MAR04886;MAR04888;MAR04894;MAR04898;MAR04899;MAR04905;MAR04914;MAR04922;MAR04947;MAR04948;MAR04957;MAR04958;MAR04969;MAR04990;MAR05003;MAR05008;MAR05043;MAR05068;MAR05070;MAR05071;MAR05116;MAR05126;MAR05206;MAR05227;MAR05303;MAR05304;MAR05308;MAR05320;MAR05361;MAR05420;MAR05422;MAR05423;MAR05547;MAR05987;MAR06059;MAR06061;MAR06071;MAR06089;MAR06090;MAR06109;MAR06250;MAR06286;MAR06287;MAR06291;MAR06294;MAR06295;MAR06298;MAR06328;MAR06366;MAR06438;MAR06454;MAR06462;MAR06463;MAR06468;MAR06469;MAR06474;MAR06481;MAR06505;MAR06512;MAR06513;MAR06629;MAR07590;MAR07596;MAR07609;MAR07638;MAR07735;MAR07765;MAR07767;MAR07772;MAR07776;MAR07777;MAR07778;MAR07779;MAR07780;MAR07781;MAR07786;MAR07792;MAR07796;MAR07819;MAR07857;MAR07860;MAR07861;MAR07862;MAR08009;MAR08010;MAR08408;MAR08612;MAR08614;MAR08676;MAR08716;MAR08721;MAR08722;MAR08891;MAR08966;MAR08987;MAR08998;MAR09006;MAR09026;MAR09038;MAR09039;MAR09040;MAR09041;MAR09042;MAR09044;MAR09045;MAR09046;MAR09047;MAR09062;MAR09063;MAR09064;MAR09066;MAR09067;MAR09069;MAR09071;MAR09072;MAR09075;MAR09076;MAR09079;MAR09103;MAR09107;MAR09108;MAR09109;MAR09112;MAR09143;MAR09151;MAR09153;MAR09172;MAR09215;MAR09242;MAR09253;MAR09255;MAR09259;MAR09269;MAR09271;MAR09273;MAR09285;MAR09292;MAR09295;MAR09298;MAR09300;MAR09310;MAR09354;MAR09378;MAR09383;MAR09404;MAR09406;MAR09438;MAR09440;MAR09609;MAR09637;MAR09641;MAR09650;MAR09702;MAR09728;MAR09729;MAR09824;MAR09825;MAR09827;MAR09828;MAR09830;MAR09833;MAR09834;MAR09835;MAR09836;MAR09837;MAR09839;MAR09847;MAR09849;MAR09858;MAR09860;MAR09861;MAR09862;MAR09864;MAR09868;MAR09872;MAR09888;MAR09891;MAR09892;MAR09895;MAR09898;MAR09904;MAR09907;MAR09908;MAR09909;MAR09913;MAR09920;MAR09921;MAR09925;MAR09973;MAR09974;MAR09983;MAR09996;MAR10023;MAR10024;MAR10039;MAR10040;MAR10046;MAR10047;MAR10049;MAR10188;MAR10193;MAR10197;MAR10243;MAR10250;MAR10366;MAR10375;MAR10392;MAR10438;MAR10489;MAR10496;MAR11250;MAR11252;MAR11256;MAR11261;MAR11276;MAR11311;MAR11318;MAR11400;MAR11424;MAR11428;MAR11433;MAR11443;MAR11583;MAR11787;MAR11815;MAR11894;MAR11895;MAR11896;MAR11897;MAR11928;MAR11929;MAR11947;MAR11953;MAR11958;MAR11959;MAR11965;MAR12127;MAR13080;MAR13086;MAR20132;MAR20137;MAR20139;MAR20147;MAR20151;MAR20152;MAR20160;MAR20162;MAR20163</x:v>
       </x:c>
       <x:c r="L470" s="2" t="n">
-        <x:v>0.544396932125347</x:v>
+        <x:v>0.5567983499189975</x:v>
       </x:c>
       <x:c r="M470" s="3" t="b">
         <x:v>0</x:v>
@@ -19183,7 +19183,7 @@
         <x:v>MAR00604;MAR00605;MAR00670;MAR07588</x:v>
       </x:c>
       <x:c r="L474" s="2" t="n">
-        <x:v>0.2567837403161312</x:v>
+        <x:v>0.2605303044284878</x:v>
       </x:c>
       <x:c r="M474" s="3" t="b">
         <x:v>0</x:v>
@@ -19224,7 +19224,7 @@
         <x:v>MAR03802;MAR03804;MAR03899;MAR15017</x:v>
       </x:c>
       <x:c r="L475" s="2" t="n">
-        <x:v>0.5796894582014015</x:v>
+        <x:v>0.5940619241072214</x:v>
       </x:c>
       <x:c r="M475" s="3" t="b">
         <x:v>0</x:v>
@@ -19343,7 +19343,7 @@
         <x:v>MAR05130;MAR05131;MAR05132;MAR05133;MAR05134;MAR05135;MAR05136;MAR05137;MAR05138;MAR05139;MAR05140;MAR05141;MAR05142;MAR05143;MAR05145;MAR05146;MAR05147;MAR05148;MAR05149;MAR05150</x:v>
       </x:c>
       <x:c r="L478" s="2" t="n">
-        <x:v>1.2253661760684098e-22</x:v>
+        <x:v>1.1643326117431635e-22</x:v>
       </x:c>
       <x:c r="M478" s="3" t="b">
         <x:v>1</x:v>
@@ -19501,7 +19501,7 @@
         <x:v>MAR00021;MAR00022;MAR00023;MAR00033;MAR00034;MAR04413</x:v>
       </x:c>
       <x:c r="L482" s="2" t="n">
-        <x:v>0.008300330902824437</x:v>
+        <x:v>0.00826344054325633</x:v>
       </x:c>
       <x:c r="M482" s="3" t="b">
         <x:v>1</x:v>
@@ -19741,7 +19741,7 @@
         <x:v>MAR03107;MAR03108;MAR03109;MAR03110;MAR03111;MAR03112;MAR03113;MAR03114;MAR03115;MAR03116;MAR03117;MAR03118;MAR03122;MAR03123;MAR03125;MAR03129;MAR03130;MAR03132;MAR03136;MAR03137;MAR03139;MAR03150;MAR03151;MAR03153;MAR03408;MAR03409;MAR03411;MAR03413;MAR03414;MAR03416;MAR03422;MAR03423;MAR03424;MAR03425;MAR03426;MAR03430;MAR03431;MAR03432;MAR03433;MAR09719</x:v>
       </x:c>
       <x:c r="L488" s="2" t="n">
-        <x:v>2.594441129022564e-31</x:v>
+        <x:v>2.306169892464501e-31</x:v>
       </x:c>
       <x:c r="M488" s="3" t="b">
         <x:v>1</x:v>
@@ -19821,7 +19821,7 @@
         <x:v>MAR03170;MAR03171;MAR03172;MAR03173;MAR03174;MAR03175;MAR03176;MAR03177;MAR03396;MAR03397</x:v>
       </x:c>
       <x:c r="L490" s="2" t="n">
-        <x:v>0.0018446698634320528</x:v>
+        <x:v>0.0017829818744715417</x:v>
       </x:c>
       <x:c r="M490" s="3" t="b">
         <x:v>1</x:v>
@@ -19979,7 +19979,7 @@
         <x:v>MAR03240;MAR03241;MAR03242;MAR03243;MAR03244;MAR03245;MAR03246;MAR03247;MAR03258;MAR03260;MAR03262;MAR03264;MAR03272</x:v>
       </x:c>
       <x:c r="L494" s="2" t="n">
-        <x:v>2.687341344468246e-11</x:v>
+        <x:v>2.490396706930384e-11</x:v>
       </x:c>
       <x:c r="M494" s="3" t="b">
         <x:v>1</x:v>
@@ -20059,7 +20059,7 @@
         <x:v>MAR03218;MAR03219;MAR03220;MAR03221;MAR03222;MAR03223;MAR03224;MAR03225;MAR03226;MAR03227;MAR03228;MAR03234;MAR03235;MAR03236;MAR03237;MAR03239</x:v>
       </x:c>
       <x:c r="L496" s="2" t="n">
-        <x:v>6.712139571668694e-14</x:v>
+        <x:v>6.243850764342971e-14</x:v>
       </x:c>
       <x:c r="M496" s="3" t="b">
         <x:v>1</x:v>
@@ -20453,7 +20453,7 @@
         <x:v>MAR00159;MAR02591;MAR02594;MAR02599;MAR02602;MAR02605;MAR02611;MAR02614;MAR02620;MAR02623;MAR02633;MAR02648;MAR02651;MAR02657;MAR02660;MAR02666;MAR02669;MAR02672;MAR02675;MAR02678;MAR02681;MAR02684;MAR02687;MAR02690;MAR02693;MAR02699;MAR02702;MAR02705;MAR02708;MAR02711;MAR02714;MAR02730;MAR02733;MAR02736;MAR02739;MAR02742;MAR02759;MAR02762;MAR02768;MAR02771;MAR02774;MAR02877</x:v>
       </x:c>
       <x:c r="L506" s="2" t="n">
-        <x:v>3.6052064144084185e-35</x:v>
+        <x:v>3.2046279239185943e-35</x:v>
       </x:c>
       <x:c r="M506" s="3" t="b">
         <x:v>1</x:v>
@@ -20535,7 +20535,7 @@
         <x:v>MAR02606;MAR02607;MAR02616;MAR02618;MAR02621;MAR02622;MAR02624;MAR02625;MAR02649;MAR02650;MAR02652;MAR02653;MAR02661;MAR02662;MAR02670;MAR02671;MAR02673;MAR02674;MAR02676;MAR02677;MAR02679;MAR02680;MAR02682;MAR02683;MAR02685;MAR02686;MAR02688;MAR02689;MAR02691;MAR02692;MAR02695;MAR02697;MAR02700;MAR02701;MAR02703;MAR02704;MAR02706;MAR02707;MAR02709;MAR02710;MAR02712;MAR02713;MAR02715;MAR02716;MAR02732;MAR02734;MAR02735;MAR02737;MAR02738;MAR02740;MAR02741;MAR02764;MAR02766;MAR02769;MAR02770;MAR02772;MAR02773;MAR02775;MAR02776</x:v>
       </x:c>
       <x:c r="L508" s="2" t="n">
-        <x:v>2.367214274987097e-37</x:v>
+        <x:v>2.104190466655197e-37</x:v>
       </x:c>
       <x:c r="M508" s="3" t="b">
         <x:v>1</x:v>
@@ -20576,7 +20576,7 @@
         <x:v>MAR03029;MAR03030</x:v>
       </x:c>
       <x:c r="L509" s="2" t="n">
-        <x:v>0.5023946189594026</x:v>
+        <x:v>0.515276532266054</x:v>
       </x:c>
       <x:c r="M509" s="3" t="b">
         <x:v>0</x:v>
@@ -20656,7 +20656,7 @@
         <x:v>MAR01565</x:v>
       </x:c>
       <x:c r="L511" s="2" t="n">
-        <x:v>0.6336315549401373</x:v>
+        <x:v>0.6459242306091699</x:v>
       </x:c>
       <x:c r="M511" s="3" t="b">
         <x:v>0</x:v>
@@ -21091,7 +21091,7 @@
         <x:v>MAR07598;MAR07614;MAR10061</x:v>
       </x:c>
       <x:c r="L522" s="2" t="n">
-        <x:v>0.47912572022199773</x:v>
+        <x:v>0.49495269596506675</x:v>
       </x:c>
       <x:c r="M522" s="3" t="b">
         <x:v>0</x:v>
@@ -21292,7 +21292,7 @@
         <x:v>MAR00144;MAR00146;MAR00148;MAR00181;MAR00186;MAR00205;MAR00218;MAR00743;MAR00745;MAR00747;MAR00749;MAR02150;MAR02151</x:v>
       </x:c>
       <x:c r="L527" s="2" t="n">
-        <x:v>0.0070289819038961265</x:v>
+        <x:v>0.006913752692356846</x:v>
       </x:c>
       <x:c r="M527" s="3" t="b">
         <x:v>1</x:v>
@@ -21333,7 +21333,7 @@
         <x:v>MAR02152;MAR02153;MAR02154;MAR02155;MAR02156;MAR02157;MAR02158;MAR02159;MAR02160;MAR02161;MAR02162;MAR02163</x:v>
       </x:c>
       <x:c r="L528" s="2" t="n">
-        <x:v>0.000008461415460486971</x:v>
+        <x:v>0.000008223242284562153</x:v>
       </x:c>
       <x:c r="M528" s="3" t="b">
         <x:v>1</x:v>
@@ -21532,7 +21532,7 @@
         <x:v>MAR02289</x:v>
       </x:c>
       <x:c r="L533" s="2" t="n">
-        <x:v>0.6336315549401373</x:v>
+        <x:v>0.6459242306091699</x:v>
       </x:c>
       <x:c r="M533" s="3" t="b">
         <x:v>0</x:v>
@@ -21692,7 +21692,7 @@
         <x:v>MAR00108;MAR00112;MAR00977;MAR00978;MAR00982;MAR01001;MAR02028;MAR02148;MAR02149;MAR02183;MAR02187;MAR02207;MAR02381;MAR03437;MAR03438;MAR03442;MAR03479;MAR03507;MAR03535;MAR04719;MAR04967;MAR05030;MAR05044;MAR05110;MAR05111;MAR05185;MAR05188;MAR05343;MAR05449;MAR05988;MAR06279;MAR06319;MAR06347</x:v>
       </x:c>
       <x:c r="L537" s="2" t="n">
-        <x:v>0.544396932125347</x:v>
+        <x:v>0.5567983499189975</x:v>
       </x:c>
       <x:c r="M537" s="3" t="b">
         <x:v>0</x:v>
@@ -22010,7 +22010,7 @@
         <x:v>MAR00129;MAR00579;MAR00580;MAR00581;MAR00598;MAR00632;MAR00643;MAR00651;MAR07594;MAR07597;MAR07601</x:v>
       </x:c>
       <x:c r="L545" s="2" t="n">
-        <x:v>0.20355436848695932</x:v>
+        <x:v>0.20415910517289798</x:v>
       </x:c>
       <x:c r="M545" s="3" t="b">
         <x:v>0</x:v>
@@ -22092,7 +22092,7 @@
         <x:v>MAR04368;MAR04373;MAR04391;MAR06412;MAR20069</x:v>
       </x:c>
       <x:c r="L547" s="2" t="n">
-        <x:v>0.48624945097331995</x:v>
+        <x:v>0.5007679123092831</x:v>
       </x:c>
       <x:c r="M547" s="3" t="b">
         <x:v>0</x:v>
@@ -22406,7 +22406,7 @@
         <x:v>MAR11321</x:v>
       </x:c>
       <x:c r="L555" s="2" t="n">
-        <x:v>0.6336315549401373</x:v>
+        <x:v>0.6459242306091699</x:v>
       </x:c>
       <x:c r="M555" s="3" t="b">
         <x:v>0</x:v>
@@ -22880,7 +22880,7 @@
         <x:v>MAR06397;MAR06402;MAR06403</x:v>
       </x:c>
       <x:c r="L567" s="2" t="n">
-        <x:v>0.011042153918890492</x:v>
+        <x:v>0.010939131278425865</x:v>
       </x:c>
       <x:c r="M567" s="3" t="b">
         <x:v>1</x:v>
@@ -23081,7 +23081,7 @@
         <x:v>MAR00061;MAR00158;MAR00229;MAR00578;MAR02127;MAR02141;MAR02377;MAR02379;MAR03789;MAR03946;MAR03949;MAR03952;MAR04756;MAR04855;MAR04898;MAR04905;MAR04914;MAR04922;MAR04926;MAR05227;MAR05304;MAR05361;MAR05420;MAR06295;MAR06298;MAR06328;MAR06438;MAR06454;MAR06469;MAR06481;MAR06513;MAR07638;MAR07719;MAR08009;MAR08614;MAR08891;MAR08987;MAR08998;MAR10049;MAR20137;MAR20139;MAR20148;MAR20156;MAR20161;MAR20164</x:v>
       </x:c>
       <x:c r="L572" s="2" t="n">
-        <x:v>0.1037499319382601</x:v>
+        <x:v>0.10388882073603554</x:v>
       </x:c>
       <x:c r="M572" s="3" t="b">
         <x:v>0</x:v>
@@ -23161,7 +23161,7 @@
         <x:v>MAR01542;MAR04265;MAR04269;MAR08791</x:v>
       </x:c>
       <x:c r="L574" s="2" t="n">
-        <x:v>0.6253007767335249</x:v>
+        <x:v>0.6387481052654287</x:v>
       </x:c>
       <x:c r="M574" s="3" t="b">
         <x:v>0</x:v>
@@ -23202,7 +23202,7 @@
         <x:v>MAR01095;MAR05422;MAR05423;MAR07765;MAR07767;MAR07786;MAR07792;MAR07796;MAR07857;MAR07860;MAR07861;MAR07862;MAR13086</x:v>
       </x:c>
       <x:c r="L575" s="2" t="n">
-        <x:v>0.07981358298394318</x:v>
+        <x:v>0.08081198689176292</x:v>
       </x:c>
       <x:c r="M575" s="3" t="b">
         <x:v>0</x:v>
@@ -23243,7 +23243,7 @@
         <x:v>MAR03967;MAR03968;MAR04024;MAR07160;MAR07161;MAR07717;MAR07863;MAR07867;MAR07869;MAR07871;MAR08456;MAR08467;MAR08486</x:v>
       </x:c>
       <x:c r="L576" s="2" t="n">
-        <x:v>0.18314448829805452</x:v>
+        <x:v>0.18438119141117826</x:v>
       </x:c>
       <x:c r="M576" s="3" t="b">
         <x:v>0</x:v>
@@ -23442,7 +23442,7 @@
         <x:v>MAR03977;MAR06911;MAR06912;MAR06914;MAR06916;MAR06918</x:v>
       </x:c>
       <x:c r="L581" s="2" t="n">
-        <x:v>0.00021150028423168245</x:v>
+        <x:v>0.00020680027791542284</x:v>
       </x:c>
       <x:c r="M581" s="3" t="b">
         <x:v>1</x:v>
@@ -23561,7 +23561,7 @@
         <x:v>MAR04350;MAR04354;MAR04398;MAR04710</x:v>
       </x:c>
       <x:c r="L584" s="2" t="n">
-        <x:v>0.4629359447079332</x:v>
+        <x:v>0.47567730098429833</x:v>
       </x:c>
       <x:c r="M584" s="3" t="b">
         <x:v>0</x:v>
@@ -23641,7 +23641,7 @@
         <x:v>MAR00063;MAR01462;MAR02407;MAR02412;MAR02509;MAR02514;MAR03024;MAR03025;MAR03106;MAR03947;MAR04900;MAR07590;MAR07596;MAR07777;MAR07779;MAR08980;MAR09680;MAR10039;MAR10040</x:v>
       </x:c>
       <x:c r="L586" s="2" t="n">
-        <x:v>0.08726774932254744</x:v>
+        <x:v>0.08828842475322052</x:v>
       </x:c>
       <x:c r="M586" s="3" t="b">
         <x:v>0</x:v>
@@ -23840,7 +23840,7 @@
         <x:v>MAR01044;MAR04750;MAR04752;MAR04762;MAR04769;MAR11316;MAR11406</x:v>
       </x:c>
       <x:c r="L591" s="2" t="n">
-        <x:v>0.003532463527525122</x:v>
+        <x:v>0.003456845042226419</x:v>
       </x:c>
       <x:c r="M591" s="3" t="b">
         <x:v>1</x:v>
@@ -24078,7 +24078,7 @@
         <x:v>MAR04002;MAR04004;MAR04010;MAR04020;MAR04135;MAR04453;MAR04612;MAR04614;MAR04621;MAR06603;MAR09797</x:v>
       </x:c>
       <x:c r="L597" s="2" t="n">
-        <x:v>0.493257571818339</x:v>
+        <x:v>0.5064867020969918</x:v>
       </x:c>
       <x:c r="M597" s="3" t="b">
         <x:v>0</x:v>
@@ -24119,7 +24119,7 @@
         <x:v>MAR03931;MAR04008;MAR04032;MAR04485;MAR04579;MAR04644;MAR06627;MAR08274</x:v>
       </x:c>
       <x:c r="L598" s="2" t="n">
-        <x:v>0.48592980027541827</x:v>
+        <x:v>0.5007679123092831</x:v>
       </x:c>
       <x:c r="M598" s="3" t="b">
         <x:v>0</x:v>
@@ -24201,7 +24201,7 @@
         <x:v>MAR03980;MAR04767</x:v>
       </x:c>
       <x:c r="L600" s="2" t="n">
-        <x:v>0.670167172742874</x:v>
+        <x:v>0.6801526350868503</x:v>
       </x:c>
       <x:c r="M600" s="3" t="b">
         <x:v>0</x:v>
@@ -24242,7 +24242,7 @@
         <x:v>MAR06632;MAR06634;MAR06638;MAR06641;MAR06642;MAR06644;MAR06647;MAR06649;MAR06651;MAR06652;MAR06654;MAR06655;MAR06656;MAR06657;MAR06658;MAR06660;MAR06664;MAR06665;MAR06668;MAR06669;MAR06673;MAR06675;MAR06677;MAR06678;MAR06682;MAR06687;MAR06690;MAR06691;MAR06692;MAR06693;MAR06700;MAR06701;MAR06702;MAR06703;MAR08698;MAR08702;MAR08709;MAR08711</x:v>
       </x:c>
       <x:c r="L601" s="2" t="n">
-        <x:v>2.6853027815169362e-21</x:v>
+        <x:v>2.536119293654884e-21</x:v>
       </x:c>
       <x:c r="M601" s="3" t="b">
         <x:v>1</x:v>
@@ -24679,7 +24679,7 @@
         <x:v>MAR04139;MAR04141;MAR04147;MAR04152;MAR04652;MAR08981</x:v>
       </x:c>
       <x:c r="L612" s="2" t="n">
-        <x:v>0.0908844391560719</x:v>
+        <x:v>0.09187446572639947</x:v>
       </x:c>
       <x:c r="M612" s="3" t="b">
         <x:v>0</x:v>
@@ -24958,7 +24958,7 @@
         <x:v>MAR02960;MAR02993</x:v>
       </x:c>
       <x:c r="L619" s="2" t="n">
-        <x:v>0.5939550051489226</x:v>
+        <x:v>0.6080195134675674</x:v>
       </x:c>
       <x:c r="M619" s="3" t="b">
         <x:v>0</x:v>
@@ -24999,7 +24999,7 @@
         <x:v>MAR08613;MAR08615;MAR08616</x:v>
       </x:c>
       <x:c r="L620" s="2" t="n">
-        <x:v>0.011042153918890492</x:v>
+        <x:v>0.010939131278425865</x:v>
       </x:c>
       <x:c r="M620" s="3" t="b">
         <x:v>1</x:v>
@@ -25157,7 +25157,7 @@
         <x:v>MAR02129;MAR02130;MAR02131;MAR02132;MAR02133;MAR02134;MAR02135;MAR02136;MAR02137;MAR02139;MAR02142;MAR02143;MAR02144;MAR02145</x:v>
       </x:c>
       <x:c r="L624" s="2" t="n">
-        <x:v>2.7512600275390464e-7</x:v>
+        <x:v>2.6427874099658224e-7</x:v>
       </x:c>
       <x:c r="M624" s="3" t="b">
         <x:v>1</x:v>
@@ -25198,7 +25198,7 @@
         <x:v>MAR06436;MAR06453;MAR06465;MAR06467;MAR06470;MAR06471;MAR06472;MAR06473;MAR06476;MAR06478;MAR06482;MAR06484;MAR06486;MAR06488;MAR06492</x:v>
       </x:c>
       <x:c r="L625" s="2" t="n">
-        <x:v>2.6080355238255436e-7</x:v>
+        <x:v>2.511441615535709e-7</x:v>
       </x:c>
       <x:c r="M625" s="3" t="b">
         <x:v>1</x:v>
@@ -25319,7 +25319,7 @@
         <x:v>MAR00159;MAR02591;MAR02594;MAR02599;MAR02602;MAR02605;MAR02606;MAR02607;MAR02611;MAR02614;MAR02616;MAR02618;MAR02620;MAR02621;MAR02622;MAR02623;MAR02624;MAR02625;MAR02633;MAR02648;MAR02649;MAR02650;MAR02651;MAR02652;MAR02653;MAR02657;MAR02660;MAR02661;MAR02662;MAR02666;MAR02669;MAR02670;MAR02671;MAR02672;MAR02673;MAR02674;MAR02675;MAR02676;MAR02677;MAR02678;MAR02679;MAR02680;MAR02681;MAR02682;MAR02683;MAR02684;MAR02685;MAR02686;MAR02687;MAR02688;MAR02689;MAR02690;MAR02691;MAR02692;MAR02693;MAR02695;MAR02697;MAR02699;MAR02700;MAR02701;MAR02702;MAR02703;MAR02704;MAR02705;MAR02706;MAR02707;MAR02708;MAR02709;MAR02710;MAR02711;MAR02712;MAR02713;MAR02714;MAR02715;MAR02716;MAR02730;MAR02732;MAR02733;MAR02734;MAR02735;MAR02736;MAR02737;MAR02738;MAR02739;MAR02740;MAR02741;MAR02742;MAR02759;MAR02762;MAR02764;MAR02766;MAR02768;MAR02769;MAR02770;MAR02771;MAR02772;MAR02773;MAR02774;MAR02775;MAR02776;MAR02869;MAR02870;MAR02877;MAR02878;MAR02879;MAR02896;MAR02897;MAR02924;MAR02925;MAR02926;MAR03029;MAR03030</x:v>
       </x:c>
       <x:c r="L628" s="2" t="n">
-        <x:v>2.115870301685154e-51</x:v>
+        <x:v>1.880773601497915e-51</x:v>
       </x:c>
       <x:c r="M628" s="3" t="b">
         <x:v>1</x:v>
@@ -25360,7 +25360,7 @@
         <x:v>MAR03107;MAR03108;MAR03109;MAR03110;MAR03111;MAR03112;MAR03113;MAR03114;MAR03115;MAR03116;MAR03117;MAR03118;MAR03122;MAR03123;MAR03125;MAR03129;MAR03130;MAR03132;MAR03136;MAR03137;MAR03139;MAR03150;MAR03151;MAR03153;MAR03170;MAR03171;MAR03172;MAR03173;MAR03174;MAR03175;MAR03176;MAR03177;MAR03218;MAR03219;MAR03220;MAR03221;MAR03222;MAR03223;MAR03224;MAR03225;MAR03226;MAR03227;MAR03228;MAR03234;MAR03235;MAR03236;MAR03237;MAR03239;MAR03240;MAR03241;MAR03242;MAR03243;MAR03244;MAR03245;MAR03246;MAR03247;MAR03258;MAR03260;MAR03262;MAR03264;MAR03272;MAR03298;MAR03396;MAR03397;MAR03408;MAR03409;MAR03411;MAR03413;MAR03414;MAR03416;MAR03422;MAR03423;MAR03424;MAR03425;MAR03426;MAR03430;MAR03431;MAR03432;MAR03433;MAR09719</x:v>
       </x:c>
       <x:c r="L629" s="2" t="n">
-        <x:v>5.325772886372335e-24</x:v>
+        <x:v>5.1285220387289156e-24</x:v>
       </x:c>
       <x:c r="M629" s="3" t="b">
         <x:v>1</x:v>
@@ -25440,7 +25440,7 @@
         <x:v>MAR00604;MAR00605;MAR00670;MAR07588</x:v>
       </x:c>
       <x:c r="L631" s="2" t="n">
-        <x:v>0.09654003657306906</x:v>
+        <x:v>0.09700641356134475</x:v>
       </x:c>
       <x:c r="M631" s="3" t="b">
         <x:v>0</x:v>
@@ -25481,7 +25481,7 @@
         <x:v>MAR03802;MAR03804;MAR03899</x:v>
       </x:c>
       <x:c r="L632" s="2" t="n">
-        <x:v>0.6646504534671596</x:v>
+        <x:v>0.6748758450589619</x:v>
       </x:c>
       <x:c r="M632" s="3" t="b">
         <x:v>0</x:v>
@@ -25600,7 +25600,7 @@
         <x:v>MAR05130;MAR05131;MAR05132;MAR05133;MAR05134;MAR05135;MAR05136;MAR05137;MAR05138;MAR05139;MAR05140;MAR05141;MAR05142;MAR05143;MAR05145;MAR05146;MAR05147;MAR05148;MAR05149;MAR05150</x:v>
       </x:c>
       <x:c r="L635" s="2" t="n">
-        <x:v>1.3770180791063512e-25</x:v>
+        <x:v>1.3005170747115538e-25</x:v>
       </x:c>
       <x:c r="M635" s="3" t="b">
         <x:v>1</x:v>
@@ -25760,7 +25760,7 @@
         <x:v>MAR00021;MAR00022;MAR00023;MAR00033;MAR00034;MAR04413</x:v>
       </x:c>
       <x:c r="L639" s="2" t="n">
-        <x:v>0.0014927129336760625</x:v>
+        <x:v>0.0014474792084131515</x:v>
       </x:c>
       <x:c r="M639" s="3" t="b">
         <x:v>1</x:v>
@@ -25840,7 +25840,7 @@
         <x:v>MAR06396;MAR08619</x:v>
       </x:c>
       <x:c r="L641" s="2" t="n">
-        <x:v>0.6572856712938208</x:v>
+        <x:v>0.668696880864894</x:v>
       </x:c>
       <x:c r="M641" s="3" t="b">
         <x:v>0</x:v>
@@ -25998,7 +25998,7 @@
         <x:v>MAR03136;MAR03137;MAR03139;MAR03150;MAR03151;MAR03153</x:v>
       </x:c>
       <x:c r="L645" s="2" t="n">
-        <x:v>0.32942819572561904</x:v>
+        <x:v>0.33809270543606207</x:v>
       </x:c>
       <x:c r="M645" s="3" t="b">
         <x:v>0</x:v>
@@ -26234,7 +26234,7 @@
         <x:v>MAR03250;MAR03252;MAR03254;MAR03256;MAR03258;MAR03260;MAR03262;MAR03264;MAR03272</x:v>
       </x:c>
       <x:c r="L651" s="2" t="n">
-        <x:v>3.445311140426511e-7</x:v>
+        <x:v>3.3017565095754063e-7</x:v>
       </x:c>
       <x:c r="M651" s="3" t="b">
         <x:v>1</x:v>
@@ -26667,7 +26667,7 @@
         <x:v>MAR08662;MAR08663</x:v>
       </x:c>
       <x:c r="L662" s="2" t="n">
-        <x:v>0.29995066685556215</x:v>
+        <x:v>0.3067456657810927</x:v>
       </x:c>
       <x:c r="M662" s="3" t="b">
         <x:v>0</x:v>
@@ -26905,7 +26905,7 @@
         <x:v>MAR01565</x:v>
       </x:c>
       <x:c r="L668" s="2" t="n">
-        <x:v>0.4869868260921511</x:v>
+        <x:v>0.5012262069720386</x:v>
       </x:c>
       <x:c r="M668" s="3" t="b">
         <x:v>0</x:v>
@@ -27340,7 +27340,7 @@
         <x:v>MAR07598;MAR07614;MAR10061</x:v>
       </x:c>
       <x:c r="L679" s="2" t="n">
-        <x:v>0.23193132053150717</x:v>
+        <x:v>0.23286598906560077</x:v>
       </x:c>
       <x:c r="M679" s="3" t="b">
         <x:v>0</x:v>
@@ -27381,7 +27381,7 @@
         <x:v>MAR00569;MAR00574;MAR00628;MAR00656;MAR00658;MAR00661;MAR00714;MAR01871;MAR01922;MAR01939;MAR04110;MAR04146;MAR04181;MAR04384;MAR04859;MAR04886;MAR04899;MAR08966;MAR09038;MAR09039;MAR09040;MAR09041;MAR09042;MAR09043;MAR09044;MAR09045;MAR09046;MAR09047;MAR09048;MAR09058;MAR09062;MAR09063;MAR09064;MAR09066;MAR09067;MAR09068;MAR09069;MAR09070;MAR09072;MAR09076;MAR09079;MAR09108;MAR09109;MAR09143;MAR09146;MAR09151;MAR09153;MAR09172;MAR09209;MAR09215;MAR09255;MAR09259;MAR09269;MAR09271;MAR09273;MAR09292;MAR09298;MAR09354;MAR09360;MAR09363;MAR09378;MAR09383;MAR09404;MAR09406;MAR09440;MAR09702;MAR09729;MAR09847;MAR09849;MAR09860;MAR09861;MAR09862;MAR09864;MAR09868;MAR09920;MAR09921;MAR09925;MAR10024;MAR10047;MAR10188;MAR10193;MAR10195;MAR10197;MAR10202;MAR10222;MAR10243;MAR10250;MAR10496;MAR11400;MAR11424;MAR11428;MAR11895;MAR11897;MAR11947;MAR11953;MAR11974;MAR12127</x:v>
       </x:c>
       <x:c r="L680" s="2" t="n">
-        <x:v>0.0754208905038683</x:v>
+        <x:v>0.07648949372502675</x:v>
       </x:c>
       <x:c r="M680" s="3" t="b">
         <x:v>0</x:v>
@@ -27582,7 +27582,7 @@
         <x:v>MAR02152;MAR02153;MAR02154;MAR02155;MAR02156;MAR02157;MAR02158;MAR02159;MAR02160;MAR02161;MAR02162;MAR02163</x:v>
       </x:c>
       <x:c r="L685" s="2" t="n">
-        <x:v>1.9942621165671444e-7</x:v>
+        <x:v>1.925494457375174e-7</x:v>
       </x:c>
       <x:c r="M685" s="3" t="b">
         <x:v>1</x:v>
@@ -27978,7 +27978,7 @@
         <x:v>MAR04333;MAR04335;MAR04655;MAR04656</x:v>
       </x:c>
       <x:c r="L695" s="2" t="n">
-        <x:v>0.6618817009721645</x:v>
+        <x:v>0.6723877597177544</x:v>
       </x:c>
       <x:c r="M695" s="3" t="b">
         <x:v>0</x:v>
@@ -28255,7 +28255,7 @@
         <x:v>MAR00129;MAR00579;MAR00580;MAR00581;MAR00598;MAR00632;MAR00643;MAR00651;MAR07594;MAR07597;MAR07601</x:v>
       </x:c>
       <x:c r="L702" s="2" t="n">
-        <x:v>0.02067981716352217</x:v>
+        <x:v>0.020482866523869575</x:v>
       </x:c>
       <x:c r="M702" s="3" t="b">
         <x:v>1</x:v>
@@ -28337,10 +28337,10 @@
         <x:v>MAR04368;MAR04373;MAR04375;MAR04391;MAR06412;MAR20069</x:v>
       </x:c>
       <x:c r="L704" s="2" t="n">
-        <x:v>0.04966919164564351</x:v>
+        <x:v>0.05050079150576844</x:v>
       </x:c>
       <x:c r="M704" s="3" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="705" ht="18" customHeight="1">
@@ -29123,7 +29123,7 @@
         <x:v>MAR06402;MAR06403</x:v>
       </x:c>
       <x:c r="L724" s="2" t="n">
-        <x:v>0.09620174651807363</x:v>
+        <x:v>0.09680678894900491</x:v>
       </x:c>
       <x:c r="M724" s="3" t="b">
         <x:v>0</x:v>
@@ -29324,7 +29324,7 @@
         <x:v>MAR00061;MAR00182;MAR00578;MAR02225;MAR02379;MAR03789;MAR03952;MAR04756;MAR04852;MAR04855;MAR04874;MAR04898;MAR04905;MAR04914;MAR04922;MAR04963;MAR05006;MAR05043;MAR05115;MAR05126;MAR05227;MAR05304;MAR05361;MAR05420;MAR06328;MAR06438;MAR06454;MAR06469;MAR06481;MAR06513;MAR07638;MAR08009;MAR08428;MAR08430;MAR08614;MAR08891;MAR08987;MAR08998;MAR10049;MAR11443;MAR13080;MAR20137;MAR20139;MAR20156;MAR20160;MAR20164</x:v>
       </x:c>
       <x:c r="L729" s="2" t="n">
-        <x:v>0.00003754091279213906</x:v>
+        <x:v>0.000036117793222240984</x:v>
       </x:c>
       <x:c r="M729" s="3" t="b">
         <x:v>1</x:v>
@@ -29404,7 +29404,7 @@
         <x:v>MAR01542;MAR04265;MAR04269;MAR08791</x:v>
       </x:c>
       <x:c r="L731" s="2" t="n">
-        <x:v>0.26981247811861797</x:v>
+        <x:v>0.27580831096569836</x:v>
       </x:c>
       <x:c r="M731" s="3" t="b">
         <x:v>0</x:v>
@@ -29445,7 +29445,7 @@
         <x:v>MAR01095;MAR05422;MAR05423;MAR07765;MAR07767;MAR07786;MAR07792;MAR07796;MAR07857;MAR07860;MAR07861;MAR07862;MAR13086</x:v>
       </x:c>
       <x:c r="L732" s="2" t="n">
-        <x:v>0.004444286870493834</x:v>
+        <x:v>0.004328348952133125</x:v>
       </x:c>
       <x:c r="M732" s="3" t="b">
         <x:v>1</x:v>
@@ -29486,7 +29486,7 @@
         <x:v>MAR03967;MAR03968;MAR04024;MAR04344;MAR07160;MAR07161;MAR07865;MAR07869;MAR07871;MAR07886;MAR08456;MAR08463</x:v>
       </x:c>
       <x:c r="L733" s="2" t="n">
-        <x:v>0.03537518397025375</x:v>
+        <x:v>0.03562256287913664</x:v>
       </x:c>
       <x:c r="M733" s="3" t="b">
         <x:v>1</x:v>
@@ -29683,7 +29683,7 @@
         <x:v>MAR03977;MAR06911;MAR06912;MAR06914;MAR06916;MAR06918</x:v>
       </x:c>
       <x:c r="L738" s="2" t="n">
-        <x:v>0.00002855309835965097</x:v>
+        <x:v>0.000027573911173106006</x:v>
       </x:c>
       <x:c r="M738" s="3" t="b">
         <x:v>1</x:v>
@@ -30085,7 +30085,7 @@
         <x:v>MAR01044;MAR04752;MAR04762;MAR04770;MAR11316</x:v>
       </x:c>
       <x:c r="L748" s="2" t="n">
-        <x:v>0.021172421883744474</x:v>
+        <x:v>0.020955525520869232</x:v>
       </x:c>
       <x:c r="M748" s="3" t="b">
         <x:v>1</x:v>
@@ -30323,7 +30323,7 @@
         <x:v>MAR04002;MAR04004;MAR04020;MAR04080;MAR04135;MAR04453;MAR04612;MAR04614;MAR04621;MAR04663</x:v>
       </x:c>
       <x:c r="L754" s="2" t="n">
-        <x:v>0.16993770688376722</x:v>
+        <x:v>0.17142280544579766</x:v>
       </x:c>
       <x:c r="M754" s="3" t="b">
         <x:v>0</x:v>
@@ -30364,7 +30364,7 @@
         <x:v>MAR03931;MAR03970;MAR04008;MAR04032;MAR04579;MAR04644;MAR08274</x:v>
       </x:c>
       <x:c r="L755" s="2" t="n">
-        <x:v>0.2567837403161312</x:v>
+        <x:v>0.2605303044284878</x:v>
       </x:c>
       <x:c r="M755" s="3" t="b">
         <x:v>0</x:v>
@@ -30446,7 +30446,7 @@
         <x:v>MAR03980;MAR03982;MAR04767</x:v>
       </x:c>
       <x:c r="L757" s="2" t="n">
-        <x:v>0.07795110828360427</x:v>
+        <x:v>0.07899045639405233</x:v>
       </x:c>
       <x:c r="M757" s="3" t="b">
         <x:v>0</x:v>
@@ -30487,7 +30487,7 @@
         <x:v>MAR06634;MAR06638;MAR06641;MAR06642;MAR06644;MAR06649;MAR06651;MAR06652;MAR06654;MAR06655;MAR06656;MAR06657;MAR06658;MAR06660;MAR06664;MAR06665;MAR06668;MAR06669;MAR06673;MAR06674;MAR06677;MAR06678;MAR06682;MAR06687;MAR06690;MAR06691;MAR06692;MAR06693;MAR06700;MAR06701;MAR06702;MAR06703;MAR08698;MAR08699;MAR08702;MAR08709;MAR08711</x:v>
       </x:c>
       <x:c r="L758" s="2" t="n">
-        <x:v>1.463778566118276e-25</x:v>
+        <x:v>1.3734218645060366e-25</x:v>
       </x:c>
       <x:c r="M758" s="3" t="b">
         <x:v>1</x:v>
@@ -30805,7 +30805,7 @@
         <x:v>MAR08746</x:v>
       </x:c>
       <x:c r="L766" s="2" t="n">
-        <x:v>0.7917760471885523</x:v>
+        <x:v>0.7991878701781073</x:v>
       </x:c>
       <x:c r="M766" s="3" t="b">
         <x:v>0</x:v>
@@ -30924,7 +30924,7 @@
         <x:v>MAR04139;MAR04141;MAR04147;MAR04152;MAR04408;MAR04410;MAR04652</x:v>
       </x:c>
       <x:c r="L769" s="2" t="n">
-        <x:v>0.003461732673846001</x:v>
+        <x:v>0.0033905036064829147</x:v>
       </x:c>
       <x:c r="M769" s="3" t="b">
         <x:v>1</x:v>
@@ -31203,7 +31203,7 @@
         <x:v>MAR02960;MAR02993</x:v>
       </x:c>
       <x:c r="L776" s="2" t="n">
-        <x:v>0.36327362986552025</x:v>
+        <x:v>0.3716510091705951</x:v>
       </x:c>
       <x:c r="M776" s="3" t="b">
         <x:v>0</x:v>
@@ -31244,7 +31244,7 @@
         <x:v>MAR08613;MAR08615;MAR08616</x:v>
       </x:c>
       <x:c r="L777" s="2" t="n">
-        <x:v>0.004387078790813399</x:v>
+        <x:v>0.004275905254204093</x:v>
       </x:c>
       <x:c r="M777" s="3" t="b">
         <x:v>1</x:v>
@@ -31402,7 +31402,7 @@
         <x:v>MAR02129;MAR02130;MAR02131;MAR02132;MAR02133;MAR02134;MAR02135;MAR02136;MAR02137;MAR02138;MAR02139;MAR02142;MAR02143;MAR02144;MAR02145;MAR08006</x:v>
       </x:c>
       <x:c r="L781" s="2" t="n">
-        <x:v>1.2046111522254447e-11</x:v>
+        <x:v>1.1183550450290549e-11</x:v>
       </x:c>
       <x:c r="M781" s="3" t="b">
         <x:v>1</x:v>
@@ -31443,7 +31443,7 @@
         <x:v>MAR06436;MAR06453;MAR06465;MAR06467;MAR06470;MAR06471;MAR06472;MAR06473;MAR06476;MAR06478;MAR06482;MAR06484;MAR06486;MAR06488;MAR06492</x:v>
       </x:c>
       <x:c r="L782" s="2" t="n">
-        <x:v>2.1141472439295967e-9</x:v>
+        <x:v>1.994297626926785e-9</x:v>
       </x:c>
       <x:c r="M782" s="3" t="b">
         <x:v>1</x:v>
@@ -31523,7 +31523,7 @@
         <x:v>MAR00019;MAR00061;MAR00089;MAR00142;MAR00182;MAR00569;MAR00574;MAR00578;MAR00628;MAR00656;MAR00658;MAR00661;MAR00714;MAR01095;MAR01461;MAR01462;MAR01499;MAR01534;MAR01601;MAR01607;MAR01633;MAR01669;MAR01827;MAR01871;MAR01922;MAR01939;MAR02225;MAR02278;MAR02351;MAR02379;MAR02382;MAR03597;MAR03789;MAR03951;MAR03952;MAR03959;MAR04110;MAR04146;MAR04181;MAR04384;MAR04756;MAR04765;MAR04852;MAR04855;MAR04859;MAR04874;MAR04883;MAR04886;MAR04894;MAR04896;MAR04898;MAR04899;MAR04905;MAR04914;MAR04919;MAR04922;MAR04947;MAR04958;MAR04963;MAR04969;MAR05006;MAR05023;MAR05043;MAR05068;MAR05071;MAR05076;MAR05080;MAR05082;MAR05085;MAR05089;MAR05091;MAR05115;MAR05126;MAR05206;MAR05227;MAR05303;MAR05304;MAR05361;MAR05420;MAR05422;MAR05423;MAR05448;MAR05471;MAR05498;MAR05510;MAR05521;MAR05548;MAR05566;MAR05570;MAR05577;MAR05969;MAR05987;MAR06072;MAR06090;MAR06095;MAR06250;MAR06328;MAR06383;MAR06438;MAR06454;MAR06462;MAR06463;MAR06468;MAR06469;MAR06474;MAR06481;MAR06505;MAR06512;MAR06513;MAR06629;MAR07590;MAR07596;MAR07609;MAR07638;MAR07765;MAR07767;MAR07772;MAR07776;MAR07777;MAR07778;MAR07779;MAR07780;MAR07781;MAR07786;MAR07792;MAR07796;MAR07811;MAR07819;MAR07857;MAR07860;MAR07861;MAR07862;MAR08009;MAR08010;MAR08408;MAR08428;MAR08430;MAR08612;MAR08614;MAR08676;MAR08687;MAR08716;MAR08720;MAR08721;MAR08722;MAR08891;MAR08966;MAR08987;MAR08998;MAR09038;MAR09039;MAR09040;MAR09041;MAR09042;MAR09043;MAR09044;MAR09045;MAR09046;MAR09047;MAR09048;MAR09058;MAR09062;MAR09063;MAR09064;MAR09066;MAR09067;MAR09068;MAR09069;MAR09070;MAR09072;MAR09076;MAR09079;MAR09108;MAR09109;MAR09143;MAR09146;MAR09151;MAR09153;MAR09172;MAR09209;MAR09215;MAR09255;MAR09259;MAR09269;MAR09271;MAR09273;MAR09292;MAR09298;MAR09354;MAR09360;MAR09363;MAR09378;MAR09383;MAR09404;MAR09406;MAR09440;MAR09609;MAR09637;MAR09641;MAR09650;MAR09702;MAR09728;MAR09729;MAR09824;MAR09825;MAR09827;MAR09828;MAR09830;MAR09833;MAR09834;MAR09835;MAR09836;MAR09837;MAR09838;MAR09839;MAR09847;MAR09849;MAR09860;MAR09861;MAR09862;MAR09864;MAR09868;MAR09883;MAR09884;MAR09913;MAR09920;MAR09921;MAR09925;MAR09975;MAR09983;MAR09989;MAR09996;MAR10004;MAR10023;MAR10024;MAR10039;MAR10040;MAR10046;MAR10047;MAR10049;MAR10159;MAR10188;MAR10193;MAR10195;MAR10197;MAR10202;MAR10222;MAR10243;MAR10250;MAR10363;MAR10364;MAR10366;MAR10375;MAR10489;MAR10496;MAR11250;MAR11252;MAR11256;MAR11261;MAR11276;MAR11400;MAR11424;MAR11428;MAR11443;MAR11583;MAR11787;MAR11894;MAR11895;MAR11896;MAR11897;MAR11947;MAR11953;MAR11973;MAR11974;MAR12127;MAR13080;MAR13086;MAR20137;MAR20139;MAR20156;MAR20160;MAR20164</x:v>
       </x:c>
       <x:c r="L784" s="2" t="n">
-        <x:v>0.213669475921185</x:v>
+        <x:v>0.21505123032161594</x:v>
       </x:c>
       <x:c r="M784" s="3" t="b">
         <x:v>0</x:v>
@@ -31685,7 +31685,7 @@
         <x:v>MAR00604;MAR00605;MAR00670</x:v>
       </x:c>
       <x:c r="L788" s="2" t="n">
-        <x:v>0.389445018463027</x:v>
+        <x:v>0.399555221434549</x:v>
       </x:c>
       <x:c r="M788" s="3" t="b">
         <x:v>0</x:v>
@@ -31726,7 +31726,7 @@
         <x:v>MAR03802;MAR03804;MAR03899</x:v>
       </x:c>
       <x:c r="L789" s="2" t="n">
-        <x:v>0.692628766773793</x:v>
+        <x:v>0.7010045374837169</x:v>
       </x:c>
       <x:c r="M789" s="3" t="b">
         <x:v>0</x:v>
@@ -31845,7 +31845,7 @@
         <x:v>MAR05130;MAR05131;MAR05132;MAR05133;MAR05134;MAR05135;MAR05136;MAR05137;MAR05138;MAR05139;MAR05140;MAR05141;MAR05142;MAR05143;MAR05145;MAR05146;MAR05147;MAR05148;MAR05149;MAR05150</x:v>
       </x:c>
       <x:c r="L792" s="2" t="n">
-        <x:v>2.0912067966327574e-25</x:v>
+        <x:v>1.9566847219955624e-25</x:v>
       </x:c>
       <x:c r="M792" s="3" t="b">
         <x:v>1</x:v>
@@ -32005,7 +32005,7 @@
         <x:v>MAR00021;MAR00022;MAR00023;MAR00033;MAR00034;MAR04413</x:v>
       </x:c>
       <x:c r="L796" s="2" t="n">
-        <x:v>0.0017002839614651483</x:v>
+        <x:v>0.0016447191261231501</x:v>
       </x:c>
       <x:c r="M796" s="3" t="b">
         <x:v>1</x:v>
@@ -32085,7 +32085,7 @@
         <x:v>MAR06394;MAR08619</x:v>
       </x:c>
       <x:c r="L798" s="2" t="n">
-        <x:v>0.6715728215577712</x:v>
+        <x:v>0.6806175733632631</x:v>
       </x:c>
       <x:c r="M798" s="3" t="b">
         <x:v>0</x:v>
@@ -32165,7 +32165,7 @@
         <x:v>MAR03281;MAR03282;MAR03283;MAR03285;MAR03286;MAR03287;MAR03288;MAR03290;MAR03292;MAR03293;MAR03298</x:v>
       </x:c>
       <x:c r="L800" s="2" t="n">
-        <x:v>3.810913851934425e-9</x:v>
+        <x:v>3.5829104590836472e-9</x:v>
       </x:c>
       <x:c r="M800" s="3" t="b">
         <x:v>1</x:v>
@@ -32951,7 +32951,7 @@
         <x:v>MAR00159;MAR02591;MAR02594;MAR02599;MAR02626;MAR02730;MAR02742;MAR02746;MAR02759</x:v>
       </x:c>
       <x:c r="L820" s="2" t="n">
-        <x:v>0.01352290796453474</x:v>
+        <x:v>0.0133559584834911</x:v>
       </x:c>
       <x:c r="M820" s="3" t="b">
         <x:v>1</x:v>
@@ -33152,7 +33152,7 @@
         <x:v>MAR01565</x:v>
       </x:c>
       <x:c r="L825" s="2" t="n">
-        <x:v>0.493257571818339</x:v>
+        <x:v>0.5064867020969918</x:v>
       </x:c>
       <x:c r="M825" s="3" t="b">
         <x:v>0</x:v>
@@ -33587,7 +33587,7 @@
         <x:v>MAR07598;MAR07614;MAR10061</x:v>
       </x:c>
       <x:c r="L836" s="2" t="n">
-        <x:v>0.24599141523458315</x:v>
+        <x:v>0.2490909634219605</x:v>
       </x:c>
       <x:c r="M836" s="3" t="b">
         <x:v>0</x:v>
@@ -33628,7 +33628,7 @@
         <x:v>MAR00569;MAR00574;MAR00628;MAR00656;MAR00658;MAR00661;MAR00714;MAR01871;MAR01939;MAR04110;MAR04146;MAR04181;MAR04384;MAR04859;MAR04886;MAR04889;MAR04899;MAR08966;MAR09038;MAR09039;MAR09040;MAR09041;MAR09042;MAR09043;MAR09044;MAR09045;MAR09046;MAR09047;MAR09058;MAR09062;MAR09063;MAR09064;MAR09066;MAR09067;MAR09068;MAR09069;MAR09070;MAR09072;MAR09076;MAR09079;MAR09103;MAR09107;MAR09108;MAR09109;MAR09143;MAR09151;MAR09153;MAR09172;MAR09209;MAR09215;MAR09242;MAR09253;MAR09254;MAR09259;MAR09269;MAR09271;MAR09273;MAR09292;MAR09298;MAR09300;MAR09353;MAR09354;MAR09360;MAR09378;MAR09383;MAR09404;MAR09406;MAR09437;MAR09440;MAR09702;MAR09729;MAR09847;MAR09849;MAR09858;MAR09860;MAR09862;MAR09864;MAR09868;MAR09920;MAR09921;MAR10024;MAR10047;MAR10188;MAR10195;MAR10197;MAR10202;MAR10243;MAR10250;MAR10254;MAR10496;MAR11400;MAR11424;MAR11895;MAR11897;MAR11947;MAR11953;MAR12127</x:v>
       </x:c>
       <x:c r="L837" s="2" t="n">
-        <x:v>0.1406308177256291</x:v>
+        <x:v>0.14191763566560217</x:v>
       </x:c>
       <x:c r="M837" s="3" t="b">
         <x:v>0</x:v>
@@ -33788,7 +33788,7 @@
         <x:v>MAR00148;MAR00152;MAR00181;MAR00743;MAR00747;MAR02150;MAR02151</x:v>
       </x:c>
       <x:c r="L841" s="2" t="n">
-        <x:v>0.29826387232985146</x:v>
+        <x:v>0.3052152796524442</x:v>
       </x:c>
       <x:c r="M841" s="3" t="b">
         <x:v>0</x:v>
@@ -33829,7 +33829,7 @@
         <x:v>MAR02152;MAR02153;MAR02154;MAR02155;MAR02156;MAR02157;MAR02158;MAR02159;MAR02160;MAR02161;MAR02162;MAR02163</x:v>
       </x:c>
       <x:c r="L842" s="2" t="n">
-        <x:v>2.6209451056508293e-7</x:v>
+        <x:v>2.520690374833584e-7</x:v>
       </x:c>
       <x:c r="M842" s="3" t="b">
         <x:v>1</x:v>
@@ -34502,7 +34502,7 @@
         <x:v>MAR00129;MAR00579;MAR00580;MAR00581;MAR00598;MAR00632;MAR00643;MAR00651;MAR07591;MAR07594;MAR07597;MAR07601</x:v>
       </x:c>
       <x:c r="L859" s="2" t="n">
-        <x:v>0.008660595735217056</x:v>
+        <x:v>0.008614772477358765</x:v>
       </x:c>
       <x:c r="M859" s="3" t="b">
         <x:v>1</x:v>
@@ -35370,7 +35370,7 @@
         <x:v>MAR06397;MAR06402;MAR06403</x:v>
       </x:c>
       <x:c r="L881" s="2" t="n">
-        <x:v>0.004626669676274646</x:v>
+        <x:v>0.004495972792764062</x:v>
       </x:c>
       <x:c r="M881" s="3" t="b">
         <x:v>1</x:v>
@@ -35571,7 +35571,7 @@
         <x:v>MAR00061;MAR00158;MAR00182;MAR00578;MAR03789;MAR03946;MAR04756;MAR04852;MAR04855;MAR04874;MAR04898;MAR04905;MAR04914;MAR04963;MAR05043;MAR05116;MAR05126;MAR05227;MAR05304;MAR05361;MAR05420;MAR06328;MAR06438;MAR06454;MAR06469;MAR06481;MAR06513;MAR07638;MAR08009;MAR08428;MAR08430;MAR08614;MAR08891;MAR08987;MAR08998;MAR10049;MAR11443;MAR20137;MAR20139;MAR20149;MAR20160;MAR20164</x:v>
       </x:c>
       <x:c r="L886" s="2" t="n">
-        <x:v>0.0014927129336760625</x:v>
+        <x:v>0.0014474792084131515</x:v>
       </x:c>
       <x:c r="M886" s="3" t="b">
         <x:v>1</x:v>
@@ -35651,7 +35651,7 @@
         <x:v>MAR01542;MAR04265;MAR04269;MAR08791</x:v>
       </x:c>
       <x:c r="L888" s="2" t="n">
-        <x:v>0.2894817866971283</x:v>
+        <x:v>0.2966118799655305</x:v>
       </x:c>
       <x:c r="M888" s="3" t="b">
         <x:v>0</x:v>
@@ -35692,7 +35692,7 @@
         <x:v>MAR01095;MAR05422;MAR05423;MAR07765;MAR07767;MAR07786;MAR07792;MAR07796;MAR07857;MAR07860;MAR07861;MAR07862;MAR13086</x:v>
       </x:c>
       <x:c r="L889" s="2" t="n">
-        <x:v>0.005605341070307366</x:v>
+        <x:v>0.0054392568904464075</x:v>
       </x:c>
       <x:c r="M889" s="3" t="b">
         <x:v>1</x:v>
@@ -35733,7 +35733,7 @@
         <x:v>MAR03967;MAR03968;MAR04024;MAR07160;MAR07161;MAR07863;MAR07886;MAR08452;MAR08456;MAR08482;MAR08486</x:v>
       </x:c>
       <x:c r="L890" s="2" t="n">
-        <x:v>0.10288929108953244</x:v>
+        <x:v>0.1032399703365997</x:v>
       </x:c>
       <x:c r="M890" s="3" t="b">
         <x:v>0</x:v>
@@ -35891,7 +35891,7 @@
         <x:v>MAR03452;MAR03453;MAR03454;MAR03455;MAR03456;MAR03457;MAR03458</x:v>
       </x:c>
       <x:c r="L894" s="2" t="n">
-        <x:v>0.1573169767245146</x:v>
+        <x:v>0.1591252178362906</x:v>
       </x:c>
       <x:c r="M894" s="3" t="b">
         <x:v>0</x:v>
@@ -35932,7 +35932,7 @@
         <x:v>MAR03977;MAR06911;MAR06912;MAR06914;MAR06916;MAR06918</x:v>
       </x:c>
       <x:c r="L895" s="2" t="n">
-        <x:v>0.000032726480551613474</x:v>
+        <x:v>0.000031514388679331494</x:v>
       </x:c>
       <x:c r="M895" s="3" t="b">
         <x:v>1</x:v>
@@ -36051,7 +36051,7 @@
         <x:v>MAR04350;MAR04354;MAR04398;MAR04710</x:v>
       </x:c>
       <x:c r="L898" s="2" t="n">
-        <x:v>0.20038150745727032</x:v>
+        <x:v>0.20122395223336692</x:v>
       </x:c>
       <x:c r="M898" s="3" t="b">
         <x:v>0</x:v>
@@ -36334,7 +36334,7 @@
         <x:v>MAR01044;MAR04752;MAR04762;MAR04770;MAR11316;MAR11406</x:v>
       </x:c>
       <x:c r="L905" s="2" t="n">
-        <x:v>0.003998058529769108</x:v>
+        <x:v>0.00390601113619084</x:v>
       </x:c>
       <x:c r="M905" s="3" t="b">
         <x:v>1</x:v>
@@ -36572,7 +36572,7 @@
         <x:v>MAR04002;MAR04004;MAR04010;MAR04020;MAR04080;MAR04135;MAR04453;MAR04603;MAR04611;MAR04614</x:v>
       </x:c>
       <x:c r="L911" s="2" t="n">
-        <x:v>0.19590815770822512</x:v>
+        <x:v>0.1968545739290378</x:v>
       </x:c>
       <x:c r="M911" s="3" t="b">
         <x:v>0</x:v>
@@ -36613,7 +36613,7 @@
         <x:v>MAR03931;MAR03970;MAR04008;MAR04032;MAR04512;MAR04579;MAR04644;MAR04673;MAR06621;MAR08274</x:v>
       </x:c>
       <x:c r="L912" s="2" t="n">
-        <x:v>0.0145267241009587</x:v>
+        <x:v>0.014326436745146618</x:v>
       </x:c>
       <x:c r="M912" s="3" t="b">
         <x:v>1</x:v>
@@ -36693,7 +36693,7 @@
         <x:v>MAR03980;MAR04767</x:v>
       </x:c>
       <x:c r="L914" s="2" t="n">
-        <x:v>0.4500556634815929</x:v>
+        <x:v>0.46273004212546776</x:v>
       </x:c>
       <x:c r="M914" s="3" t="b">
         <x:v>0</x:v>
@@ -36734,7 +36734,7 @@
         <x:v>MAR06633;MAR06634;MAR06638;MAR06641;MAR06642;MAR06644;MAR06649;MAR06651;MAR06652;MAR06654;MAR06655;MAR06656;MAR06657;MAR06658;MAR06660;MAR06664;MAR06665;MAR06668;MAR06669;MAR06672;MAR06674;MAR06675;MAR06677;MAR06678;MAR06682;MAR06687;MAR06690;MAR06691;MAR06692;MAR06693;MAR06700;MAR06701;MAR06702;MAR06703;MAR08702;MAR08709;MAR08711</x:v>
       </x:c>
       <x:c r="L915" s="2" t="n">
-        <x:v>3.695083041922627e-25</x:v>
+        <x:v>3.4487441724611177e-25</x:v>
       </x:c>
       <x:c r="M915" s="3" t="b">
         <x:v>1</x:v>
@@ -37169,7 +37169,7 @@
         <x:v>MAR04147;MAR04152;MAR04408;MAR04410;MAR04652</x:v>
       </x:c>
       <x:c r="L926" s="2" t="n">
-        <x:v>0.09160076949830923</x:v>
+        <x:v>0.09252602979627193</x:v>
       </x:c>
       <x:c r="M926" s="3" t="b">
         <x:v>0</x:v>
@@ -37448,7 +37448,7 @@
         <x:v>MAR02960;MAR02993</x:v>
       </x:c>
       <x:c r="L933" s="2" t="n">
-        <x:v>0.3806318560716889</x:v>
+        <x:v>0.38916976416302046</x:v>
       </x:c>
       <x:c r="M933" s="3" t="b">
         <x:v>0</x:v>
@@ -37489,7 +37489,7 @@
         <x:v>MAR08613;MAR08615;MAR08616</x:v>
       </x:c>
       <x:c r="L934" s="2" t="n">
-        <x:v>0.004626669676274646</x:v>
+        <x:v>0.004495972792764062</x:v>
       </x:c>
       <x:c r="M934" s="3" t="b">
         <x:v>1</x:v>
@@ -37647,7 +37647,7 @@
         <x:v>MAR02129;MAR02130;MAR02131;MAR02132;MAR02133;MAR02134;MAR02135;MAR02136;MAR02137;MAR02138;MAR02139;MAR02142;MAR02143;MAR02144;MAR02145;MAR08006</x:v>
       </x:c>
       <x:c r="L938" s="2" t="n">
-        <x:v>1.829123902079068e-11</x:v>
+        <x:v>1.6965786917834833e-11</x:v>
       </x:c>
       <x:c r="M938" s="3" t="b">
         <x:v>1</x:v>
@@ -37688,7 +37688,7 @@
         <x:v>MAR06436;MAR06453;MAR06465;MAR06467;MAR06470;MAR06471;MAR06472;MAR06473;MAR06476;MAR06478;MAR06482;MAR06484;MAR06486;MAR06488;MAR06492</x:v>
       </x:c>
       <x:c r="L939" s="2" t="n">
-        <x:v>3.042149397102721e-9</x:v>
+        <x:v>2.8631994325672666e-9</x:v>
       </x:c>
       <x:c r="M939" s="3" t="b">
         <x:v>1</x:v>
@@ -37768,7 +37768,7 @@
         <x:v>MAR00019;MAR00061;MAR00089;MAR00142;MAR00158;MAR00182;MAR00569;MAR00574;MAR00578;MAR00628;MAR00656;MAR00658;MAR00661;MAR00714;MAR01095;MAR01462;MAR01499;MAR01525;MAR01534;MAR01601;MAR01607;MAR01633;MAR01669;MAR01827;MAR01871;MAR01939;MAR02278;MAR02351;MAR02382;MAR03597;MAR03789;MAR03946;MAR03951;MAR03959;MAR04110;MAR04146;MAR04181;MAR04384;MAR04756;MAR04765;MAR04847;MAR04852;MAR04855;MAR04859;MAR04874;MAR04882;MAR04883;MAR04886;MAR04889;MAR04894;MAR04898;MAR04899;MAR04905;MAR04914;MAR04919;MAR04947;MAR04948;MAR04958;MAR04963;MAR04969;MAR04985;MAR04990;MAR05023;MAR05032;MAR05043;MAR05068;MAR05071;MAR05074;MAR05076;MAR05080;MAR05082;MAR05085;MAR05088;MAR05089;MAR05116;MAR05126;MAR05206;MAR05227;MAR05303;MAR05304;MAR05361;MAR05420;MAR05422;MAR05423;MAR05498;MAR05510;MAR05521;MAR05548;MAR05566;MAR05575;MAR05577;MAR05969;MAR05987;MAR06058;MAR06072;MAR06090;MAR06095;MAR06250;MAR06328;MAR06366;MAR06383;MAR06438;MAR06454;MAR06462;MAR06463;MAR06468;MAR06469;MAR06474;MAR06481;MAR06505;MAR06512;MAR06513;MAR06629;MAR07590;MAR07596;MAR07609;MAR07638;MAR07735;MAR07765;MAR07767;MAR07772;MAR07776;MAR07777;MAR07778;MAR07779;MAR07780;MAR07786;MAR07792;MAR07796;MAR07811;MAR07819;MAR07857;MAR07860;MAR07861;MAR07862;MAR08009;MAR08010;MAR08408;MAR08428;MAR08430;MAR08612;MAR08614;MAR08676;MAR08716;MAR08720;MAR08721;MAR08722;MAR08891;MAR08966;MAR08987;MAR08998;MAR09038;MAR09039;MAR09040;MAR09041;MAR09042;MAR09043;MAR09044;MAR09045;MAR09046;MAR09047;MAR09058;MAR09062;MAR09063;MAR09064;MAR09066;MAR09067;MAR09068;MAR09069;MAR09070;MAR09072;MAR09076;MAR09079;MAR09103;MAR09107;MAR09108;MAR09109;MAR09112;MAR09143;MAR09151;MAR09153;MAR09172;MAR09209;MAR09215;MAR09242;MAR09253;MAR09254;MAR09259;MAR09269;MAR09271;MAR09273;MAR09292;MAR09298;MAR09300;MAR09353;MAR09354;MAR09360;MAR09378;MAR09383;MAR09404;MAR09406;MAR09437;MAR09440;MAR09609;MAR09637;MAR09641;MAR09650;MAR09702;MAR09728;MAR09729;MAR09824;MAR09827;MAR09828;MAR09830;MAR09834;MAR09836;MAR09837;MAR09838;MAR09839;MAR09847;MAR09849;MAR09858;MAR09860;MAR09862;MAR09864;MAR09868;MAR09883;MAR09884;MAR09913;MAR09920;MAR09921;MAR09975;MAR09989;MAR09996;MAR10004;MAR10023;MAR10024;MAR10039;MAR10040;MAR10046;MAR10047;MAR10049;MAR10188;MAR10195;MAR10197;MAR10202;MAR10243;MAR10250;MAR10254;MAR10363;MAR10364;MAR10366;MAR10375;MAR10383;MAR10489;MAR10496;MAR11250;MAR11252;MAR11256;MAR11257;MAR11261;MAR11400;MAR11424;MAR11443;MAR11583;MAR11787;MAR11894;MAR11895;MAR11896;MAR11897;MAR11947;MAR11953;MAR12127;MAR12306;MAR12307;MAR13086;MAR20137;MAR20139;MAR20149;MAR20160;MAR20164</x:v>
       </x:c>
       <x:c r="L941" s="2" t="n">
-        <x:v>0.6613060402309279</x:v>
+        <x:v>0.672128447435396</x:v>
       </x:c>
       <x:c r="M941" s="3" t="b">
         <x:v>0</x:v>
@@ -37891,7 +37891,7 @@
         <x:v>MAR00193;MAR00214;MAR00238;MAR00242;MAR00246;MAR00272;MAR00280;MAR00310;MAR00328;MAR00332;MAR00338;MAR00342;MAR00346;MAR00370;MAR00374;MAR00394;MAR00418;MAR00422</x:v>
       </x:c>
       <x:c r="L944" s="2" t="n">
-        <x:v>0.0000013055285331639876</x:v>
+        <x:v>0.0000012748823234653023</x:v>
       </x:c>
       <x:c r="M944" s="3" t="b">
         <x:v>1</x:v>
@@ -37932,7 +37932,7 @@
         <x:v>MAR00604;MAR00605;MAR00670;MAR07588</x:v>
       </x:c>
       <x:c r="L945" s="2" t="n">
-        <x:v>0.24810373274684439</x:v>
+        <x:v>0.2509167002383052</x:v>
       </x:c>
       <x:c r="M945" s="3" t="b">
         <x:v>0</x:v>
@@ -38092,7 +38092,7 @@
         <x:v>MAR05130;MAR05131;MAR05132;MAR05133;MAR05134;MAR05135;MAR05136;MAR05137;MAR05138;MAR05139;MAR05140;MAR05141;MAR05142;MAR05143;MAR05145;MAR05146;MAR05147;MAR05148;MAR05149;MAR05150</x:v>
       </x:c>
       <x:c r="L949" s="2" t="n">
-        <x:v>9.310069853913091e-23</x:v>
+        <x:v>8.866733194202942e-23</x:v>
       </x:c>
       <x:c r="M949" s="3" t="b">
         <x:v>1</x:v>
@@ -38252,7 +38252,7 @@
         <x:v>MAR00021;MAR00022;MAR00023;MAR00033;MAR00034;MAR04413</x:v>
       </x:c>
       <x:c r="L953" s="2" t="n">
-        <x:v>0.007825488235073279</x:v>
+        <x:v>0.007747728189376977</x:v>
       </x:c>
       <x:c r="M953" s="3" t="b">
         <x:v>1</x:v>
@@ -38490,7 +38490,7 @@
         <x:v>MAR03107;MAR03108;MAR03109;MAR03110;MAR03111;MAR03112;MAR03113;MAR03114;MAR03115;MAR03116;MAR03117;MAR03118;MAR03122;MAR03123;MAR03125;MAR03129;MAR03130;MAR03132;MAR03136;MAR03137;MAR03139;MAR03150;MAR03151;MAR03153;MAR03411;MAR03413;MAR03414;MAR03416;MAR03422;MAR03424;MAR03425;MAR03430;MAR03431;MAR03432;MAR03433</x:v>
       </x:c>
       <x:c r="L959" s="2" t="n">
-        <x:v>7.2365594576843895e-25</x:v>
+        <x:v>6.7388066907537165e-25</x:v>
       </x:c>
       <x:c r="M959" s="3" t="b">
         <x:v>1</x:v>
@@ -38726,7 +38726,7 @@
         <x:v>MAR03240;MAR03241;MAR03242;MAR03243;MAR03244;MAR03245;MAR03246;MAR03247;MAR03250;MAR03252;MAR03254;MAR03256;MAR03258;MAR03260;MAR03262;MAR03264;MAR03272</x:v>
       </x:c>
       <x:c r="L965" s="2" t="n">
-        <x:v>2.5252794270857304e-19</x:v>
+        <x:v>2.3598052765929333e-19</x:v>
       </x:c>
       <x:c r="M965" s="3" t="b">
         <x:v>1</x:v>
@@ -38806,7 +38806,7 @@
         <x:v>MAR03218;MAR03219;MAR03220;MAR03221;MAR03222;MAR03223;MAR03224;MAR03225;MAR03226;MAR03227;MAR03228;MAR03229;MAR03230;MAR03231;MAR03232;MAR03233;MAR03234;MAR03235;MAR03236;MAR03237;MAR03239</x:v>
       </x:c>
       <x:c r="L967" s="2" t="n">
-        <x:v>6.667691600241475e-24</x:v>
+        <x:v>6.400983936231817e-24</x:v>
       </x:c>
       <x:c r="M967" s="3" t="b">
         <x:v>1</x:v>
@@ -39161,7 +39161,7 @@
         <x:v>MAR08667;MAR08668</x:v>
       </x:c>
       <x:c r="L976" s="2" t="n">
-        <x:v>0.493257571818339</x:v>
+        <x:v>0.5064867020969918</x:v>
       </x:c>
       <x:c r="M976" s="3" t="b">
         <x:v>0</x:v>
@@ -39202,7 +39202,7 @@
         <x:v>MAR02591;MAR02594;MAR02599;MAR02602;MAR02611;MAR02614;MAR02620;MAR02626;MAR02633;MAR02654;MAR02657;MAR02660;MAR02666;MAR02672;MAR02678;MAR02681;MAR02684;MAR02687;MAR02690;MAR02693;MAR02702;MAR02705;MAR02708;MAR02730;MAR02733;MAR02736;MAR02739;MAR02759;MAR02762;MAR02771;MAR02774</x:v>
       </x:c>
       <x:c r="L977" s="2" t="n">
-        <x:v>1.3917948745837238e-20</x:v>
+        <x:v>1.3121298480923996e-20</x:v>
       </x:c>
       <x:c r="M977" s="3" t="b">
         <x:v>1</x:v>
@@ -39284,7 +39284,7 @@
         <x:v>MAR02616;MAR02618;MAR02621;MAR02622;MAR02661;MAR02662;MAR02679;MAR02680;MAR02682;MAR02683;MAR02685;MAR02686;MAR02688;MAR02689;MAR02691;MAR02692;MAR02695;MAR02697;MAR02703;MAR02704;MAR02706;MAR02707;MAR02709;MAR02710;MAR02732;MAR02734;MAR02735;MAR02737;MAR02738;MAR02740;MAR02741;MAR02764;MAR02766;MAR02772;MAR02773;MAR02775;MAR02776</x:v>
       </x:c>
       <x:c r="L979" s="2" t="n">
-        <x:v>1.5171193042631856e-15</x:v>
+        <x:v>1.4127671828059293e-15</x:v>
       </x:c>
       <x:c r="M979" s="3" t="b">
         <x:v>1</x:v>
@@ -39403,7 +39403,7 @@
         <x:v>MAR01565</x:v>
       </x:c>
       <x:c r="L982" s="2" t="n">
-        <x:v>0.6309553602694533</x:v>
+        <x:v>0.6441882482358362</x:v>
       </x:c>
       <x:c r="M982" s="3" t="b">
         <x:v>0</x:v>
@@ -39840,7 +39840,7 @@
         <x:v>MAR07598;MAR07614;MAR10061</x:v>
       </x:c>
       <x:c r="L993" s="2" t="n">
-        <x:v>0.46774485757349105</x:v>
+        <x:v>0.4819189441666271</x:v>
       </x:c>
       <x:c r="M993" s="3" t="b">
         <x:v>0</x:v>
@@ -39881,7 +39881,7 @@
         <x:v>MAR00569;MAR00574;MAR00618;MAR00620;MAR00621;MAR00628;MAR00631;MAR00637;MAR00656;MAR00658;MAR00661;MAR00662;MAR00697;MAR00698;MAR00699;MAR00700;MAR00714;MAR01939;MAR04110;MAR04146;MAR04181;MAR04384;MAR04859;MAR04886;MAR04899;MAR04923;MAR08966;MAR08967;MAR09025;MAR09026;MAR09029;MAR09038;MAR09039;MAR09040;MAR09041;MAR09042;MAR09043;MAR09044;MAR09045;MAR09046;MAR09058;MAR09061;MAR09062;MAR09063;MAR09064;MAR09066;MAR09067;MAR09068;MAR09069;MAR09070;MAR09072;MAR09076;MAR09079;MAR09103;MAR09107;MAR09109;MAR09133;MAR09143;MAR09146;MAR09151;MAR09153;MAR09172;MAR09209;MAR09215;MAR09242;MAR09255;MAR09259;MAR09269;MAR09271;MAR09272;MAR09292;MAR09298;MAR09338;MAR09354;MAR09358;MAR09360;MAR09362;MAR09378;MAR09383;MAR09404;MAR09406;MAR09422;MAR09423;MAR09437;MAR09439;MAR09440;MAR09702;MAR09729;MAR09847;MAR09849;MAR09858;MAR09860;MAR09862;MAR09864;MAR09868;MAR09920;MAR09921;MAR09922;MAR09923;MAR09924;MAR09925;MAR10024;MAR10047;MAR10188;MAR10193;MAR10195;MAR10197;MAR10228;MAR10241;MAR10243;MAR10249;MAR10250;MAR10345;MAR10496;MAR11400;MAR11424;MAR11895;MAR11897;MAR11929;MAR11947;MAR11949;MAR11953;MAR11974;MAR12127;MAR13040;MAR13046;MAR13050;MAR13055;MAR13057;MAR13059;MAR13061;MAR13062;MAR13063</x:v>
       </x:c>
       <x:c r="L994" s="2" t="n">
-        <x:v>0.06828646660809791</x:v>
+        <x:v>0.0693703787764804</x:v>
       </x:c>
       <x:c r="M994" s="3" t="b">
         <x:v>0</x:v>
@@ -40041,10 +40041,10 @@
         <x:v>MAR00145;MAR00152;MAR00181;MAR00186;MAR00743;MAR00745;MAR00747;MAR00749;MAR01031;MAR02150;MAR02151</x:v>
       </x:c>
       <x:c r="L998" s="2" t="n">
-        <x:v>0.04966919164564351</x:v>
+        <x:v>0.05050079150576844</x:v>
       </x:c>
       <x:c r="M998" s="3" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="999" ht="18" customHeight="1">
@@ -40082,7 +40082,7 @@
         <x:v>MAR02152;MAR02153;MAR02154;MAR02155;MAR02156;MAR02157;MAR02158;MAR02159;MAR02160;MAR02161;MAR02162;MAR02163</x:v>
       </x:c>
       <x:c r="L999" s="2" t="n">
-        <x:v>0.000007271438469523459</x:v>
+        <x:v>0.000007074913105482285</x:v>
       </x:c>
       <x:c r="M999" s="3" t="b">
         <x:v>1</x:v>
@@ -40755,7 +40755,7 @@
         <x:v>MAR00129;MAR00579;MAR00580;MAR00581;MAR00598;MAR00632;MAR00643;MAR00651;MAR07594;MAR07597;MAR07601</x:v>
       </x:c>
       <x:c r="L1016" s="2" t="n">
-        <x:v>0.18836108900158904</x:v>
+        <x:v>0.18939038456990373</x:v>
       </x:c>
       <x:c r="M1016" s="3" t="b">
         <x:v>0</x:v>
@@ -40837,7 +40837,7 @@
         <x:v>MAR04368;MAR04373;MAR04375;MAR04391</x:v>
       </x:c>
       <x:c r="L1018" s="2" t="n">
-        <x:v>0.9496316253171754</x:v>
+        <x:v>0.9633944024956851</x:v>
       </x:c>
       <x:c r="M1018" s="3" t="b">
         <x:v>0</x:v>
@@ -41623,7 +41623,7 @@
         <x:v>MAR06402;MAR06403</x:v>
       </x:c>
       <x:c r="L1038" s="2" t="n">
-        <x:v>0.16795607676425867</x:v>
+        <x:v>0.16953758407842306</x:v>
       </x:c>
       <x:c r="M1038" s="3" t="b">
         <x:v>0</x:v>
@@ -41824,7 +41824,7 @@
         <x:v>MAR00061;MAR00182;MAR00578;MAR01788;MAR02225;MAR02379;MAR03789;MAR03818;MAR03946;MAR03952;MAR04756;MAR04852;MAR04855;MAR04874;MAR04898;MAR04905;MAR04914;MAR04922;MAR04963;MAR05006;MAR05043;MAR05115;MAR05126;MAR05227;MAR05304;MAR05361;MAR05420;MAR06328;MAR06438;MAR06454;MAR06469;MAR06481;MAR06513;MAR07638;MAR07719;MAR08009;MAR08428;MAR08430;MAR08614;MAR08745;MAR08891;MAR08987;MAR08997;MAR08998;MAR10049;MAR11443;MAR13027;MAR13077;MAR20137;MAR20138;MAR20139;MAR20148;MAR20156;MAR20161</x:v>
       </x:c>
       <x:c r="L1043" s="2" t="n">
-        <x:v>0.0010295038154099739</x:v>
+        <x:v>0.0010009064872041412</x:v>
       </x:c>
       <x:c r="M1043" s="3" t="b">
         <x:v>1</x:v>
@@ -41904,7 +41904,7 @@
         <x:v>MAR01542;MAR04265;MAR04269;MAR08791</x:v>
       </x:c>
       <x:c r="L1045" s="2" t="n">
-        <x:v>0.6044580707821695</x:v>
+        <x:v>0.6181088853888129</x:v>
       </x:c>
       <x:c r="M1045" s="3" t="b">
         <x:v>0</x:v>
@@ -41945,7 +41945,7 @@
         <x:v>MAR01095;MAR05422;MAR05423;MAR07765;MAR07767;MAR07786;MAR07792;MAR07796;MAR07857;MAR07860;MAR07861;MAR07862;MAR13086</x:v>
       </x:c>
       <x:c r="L1046" s="2" t="n">
-        <x:v>0.07198086276145212</x:v>
+        <x:v>0.07306165649660905</x:v>
       </x:c>
       <x:c r="M1046" s="3" t="b">
         <x:v>0</x:v>
@@ -41986,7 +41986,7 @@
         <x:v>MAR03967;MAR04024;MAR04344;MAR04507;MAR07160;MAR07161;MAR07717;MAR07865;MAR07871;MAR08456;MAR08463</x:v>
       </x:c>
       <x:c r="L1047" s="2" t="n">
-        <x:v>0.498616780223016</x:v>
+        <x:v>0.5116944735526611</x:v>
       </x:c>
       <x:c r="M1047" s="3" t="b">
         <x:v>0</x:v>
@@ -42185,7 +42185,7 @@
         <x:v>MAR03977;MAR06911;MAR06912;MAR06914;MAR06916;MAR06918</x:v>
       </x:c>
       <x:c r="L1052" s="2" t="n">
-        <x:v>0.00019570505385017455</x:v>
+        <x:v>0.00019155151338144424</x:v>
       </x:c>
       <x:c r="M1052" s="3" t="b">
         <x:v>1</x:v>
@@ -42304,7 +42304,7 @@
         <x:v>MAR04350;MAR04354;MAR04398;MAR04710</x:v>
       </x:c>
       <x:c r="L1055" s="2" t="n">
-        <x:v>0.4465918379273535</x:v>
+        <x:v>0.4594566233820509</x:v>
       </x:c>
       <x:c r="M1055" s="3" t="b">
         <x:v>0</x:v>
@@ -42587,7 +42587,7 @@
         <x:v>MAR01044;MAR04750;MAR04752;MAR04762;MAR04769;MAR04770;MAR11316;MAR11406</x:v>
       </x:c>
       <x:c r="L1062" s="2" t="n">
-        <x:v>0.0004539005921450539</x:v>
+        <x:v>0.0004425124052453572</x:v>
       </x:c>
       <x:c r="M1062" s="3" t="b">
         <x:v>1</x:v>
@@ -42946,7 +42946,7 @@
         <x:v>MAR03980;MAR04767</x:v>
       </x:c>
       <x:c r="L1071" s="2" t="n">
-        <x:v>0.6613060402309279</x:v>
+        <x:v>0.672128447435396</x:v>
       </x:c>
       <x:c r="M1071" s="3" t="b">
         <x:v>0</x:v>
@@ -42987,7 +42987,7 @@
         <x:v>MAR06634;MAR06638;MAR06641;MAR06642;MAR06644;MAR06649;MAR06651;MAR06652;MAR06654;MAR06655;MAR06656;MAR06657;MAR06658;MAR06660;MAR06664;MAR06665;MAR06668;MAR06669;MAR06672;MAR06673;MAR06674;MAR06675;MAR06677;MAR06678;MAR06682;MAR06687;MAR06690;MAR06691;MAR06692;MAR06693;MAR06700;MAR06701;MAR06702;MAR06703;MAR08702;MAR08711</x:v>
       </x:c>
       <x:c r="L1072" s="2" t="n">
-        <x:v>1.8201537828884839e-19</x:v>
+        <x:v>1.7030678670301604e-19</x:v>
       </x:c>
       <x:c r="M1072" s="3" t="b">
         <x:v>1</x:v>
@@ -43701,7 +43701,7 @@
         <x:v>MAR02960;MAR02993</x:v>
       </x:c>
       <x:c r="L1090" s="2" t="n">
-        <x:v>0.5809837878381451</x:v>
+        <x:v>0.5950634132407155</x:v>
       </x:c>
       <x:c r="M1090" s="3" t="b">
         <x:v>0</x:v>
@@ -43742,7 +43742,7 @@
         <x:v>MAR08613;MAR08615;MAR08616</x:v>
       </x:c>
       <x:c r="L1091" s="2" t="n">
-        <x:v>0.010779559477215178</x:v>
+        <x:v>0.010704701425290073</x:v>
       </x:c>
       <x:c r="M1091" s="3" t="b">
         <x:v>1</x:v>
@@ -43900,7 +43900,7 @@
         <x:v>MAR02129;MAR02130;MAR02131;MAR02132;MAR02133;MAR02134;MAR02135;MAR02136;MAR02137;MAR02138;MAR02139;MAR02142;MAR02143;MAR02144;MAR02145;MAR08006</x:v>
       </x:c>
       <x:c r="L1095" s="2" t="n">
-        <x:v>2.145855998425912e-9</x:v>
+        <x:v>2.0218732074057484e-9</x:v>
       </x:c>
       <x:c r="M1095" s="3" t="b">
         <x:v>1</x:v>
@@ -43941,7 +43941,7 @@
         <x:v>MAR06436;MAR06453;MAR06465;MAR06467;MAR06470;MAR06471;MAR06472;MAR06473;MAR06476;MAR06478;MAR06482;MAR06484;MAR06486;MAR06488;MAR06492</x:v>
       </x:c>
       <x:c r="L1096" s="2" t="n">
-        <x:v>2.1561393340882022e-7</x:v>
+        <x:v>2.078989339083163e-7</x:v>
       </x:c>
       <x:c r="M1096" s="3" t="b">
         <x:v>1</x:v>
@@ -44062,7 +44062,7 @@
         <x:v>MAR02591;MAR02594;MAR02599;MAR02602;MAR02611;MAR02614;MAR02616;MAR02618;MAR02620;MAR02621;MAR02622;MAR02626;MAR02633;MAR02654;MAR02657;MAR02660;MAR02661;MAR02662;MAR02666;MAR02672;MAR02678;MAR02679;MAR02680;MAR02681;MAR02682;MAR02683;MAR02684;MAR02685;MAR02686;MAR02687;MAR02688;MAR02689;MAR02690;MAR02691;MAR02692;MAR02693;MAR02695;MAR02697;MAR02702;MAR02703;MAR02704;MAR02705;MAR02706;MAR02707;MAR02708;MAR02709;MAR02710;MAR02730;MAR02732;MAR02733;MAR02734;MAR02735;MAR02736;MAR02737;MAR02738;MAR02739;MAR02740;MAR02741;MAR02759;MAR02762;MAR02764;MAR02766;MAR02771;MAR02772;MAR02773;MAR02774;MAR02775;MAR02776;MAR02869;MAR02870;MAR02896;MAR02897</x:v>
       </x:c>
       <x:c r="L1099" s="2" t="n">
-        <x:v>2.372118496815373e-20</x:v>
+        <x:v>2.2325821146497626e-20</x:v>
       </x:c>
       <x:c r="M1099" s="3" t="b">
         <x:v>1</x:v>
@@ -44103,7 +44103,7 @@
         <x:v>MAR03107;MAR03108;MAR03109;MAR03110;MAR03111;MAR03112;MAR03113;MAR03114;MAR03115;MAR03116;MAR03117;MAR03118;MAR03122;MAR03123;MAR03125;MAR03129;MAR03130;MAR03132;MAR03136;MAR03137;MAR03139;MAR03150;MAR03151;MAR03153;MAR03218;MAR03219;MAR03220;MAR03221;MAR03222;MAR03223;MAR03224;MAR03225;MAR03226;MAR03227;MAR03228;MAR03229;MAR03230;MAR03231;MAR03232;MAR03233;MAR03234;MAR03235;MAR03236;MAR03237;MAR03239;MAR03240;MAR03241;MAR03242;MAR03243;MAR03244;MAR03245;MAR03246;MAR03247;MAR03250;MAR03252;MAR03254;MAR03256;MAR03258;MAR03260;MAR03262;MAR03264;MAR03272;MAR03411;MAR03413;MAR03414;MAR03416;MAR03422;MAR03424;MAR03425;MAR03430;MAR03431;MAR03432;MAR03433</x:v>
       </x:c>
       <x:c r="L1100" s="2" t="n">
-        <x:v>7.892665862529278e-20</x:v>
+        <x:v>7.405464266076852e-20</x:v>
       </x:c>
       <x:c r="M1100" s="3" t="b">
         <x:v>1</x:v>
@@ -44183,7 +44183,7 @@
         <x:v>MAR00604;MAR00605;MAR00670;MAR07588</x:v>
       </x:c>
       <x:c r="L1102" s="2" t="n">
-        <x:v>0.09620174651807363</x:v>
+        <x:v>0.09680678894900491</x:v>
       </x:c>
       <x:c r="M1102" s="3" t="b">
         <x:v>0</x:v>
@@ -44343,7 +44343,7 @@
         <x:v>MAR05130;MAR05131;MAR05132;MAR05133;MAR05134;MAR05135;MAR05136;MAR05137;MAR05138;MAR05139;MAR05140;MAR05141;MAR05142;MAR05143;MAR05145;MAR05146;MAR05147;MAR05148;MAR05149;MAR05150</x:v>
       </x:c>
       <x:c r="L1106" s="2" t="n">
-        <x:v>1.3097431491235366e-25</x:v>
+        <x:v>1.241830541391205e-25</x:v>
       </x:c>
       <x:c r="M1106" s="3" t="b">
         <x:v>1</x:v>
@@ -44503,7 +44503,7 @@
         <x:v>MAR00021;MAR00022;MAR00023;MAR00033;MAR00034;MAR04413</x:v>
       </x:c>
       <x:c r="L1110" s="2" t="n">
-        <x:v>0.0014757710084685738</x:v>
+        <x:v>0.0014335095248354532</x:v>
       </x:c>
       <x:c r="M1110" s="3" t="b">
         <x:v>1</x:v>
@@ -44583,7 +44583,7 @@
         <x:v>MAR08619;MAR08620</x:v>
       </x:c>
       <x:c r="L1112" s="2" t="n">
-        <x:v>0.65369317408886</x:v>
+        <x:v>0.6653713527980727</x:v>
       </x:c>
       <x:c r="M1112" s="3" t="b">
         <x:v>0</x:v>
@@ -45564,7 +45564,7 @@
         <x:v>MAR03029;MAR03030</x:v>
       </x:c>
       <x:c r="L1137" s="2" t="n">
-        <x:v>0.29826387232985146</x:v>
+        <x:v>0.3052152796524442</x:v>
       </x:c>
       <x:c r="M1137" s="3" t="b">
         <x:v>0</x:v>
@@ -45644,7 +45644,7 @@
         <x:v>MAR01565</x:v>
       </x:c>
       <x:c r="L1139" s="2" t="n">
-        <x:v>0.48624945097331995</x:v>
+        <x:v>0.5007679123092831</x:v>
       </x:c>
       <x:c r="M1139" s="3" t="b">
         <x:v>0</x:v>
@@ -45841,7 +45841,7 @@
         <x:v>MAR03996;MAR04323;MAR08641;MAR08682</x:v>
       </x:c>
       <x:c r="L1144" s="2" t="n">
-        <x:v>0.6027498065698739</x:v>
+        <x:v>0.6166909585585649</x:v>
       </x:c>
       <x:c r="M1144" s="3" t="b">
         <x:v>0</x:v>
@@ -46079,7 +46079,7 @@
         <x:v>MAR07598;MAR07614;MAR10061</x:v>
       </x:c>
       <x:c r="L1150" s="2" t="n">
-        <x:v>0.22978972251535681</x:v>
+        <x:v>0.2308535638232983</x:v>
       </x:c>
       <x:c r="M1150" s="3" t="b">
         <x:v>0</x:v>
@@ -46120,7 +46120,7 @@
         <x:v>MAR00569;MAR00574;MAR00628;MAR00631;MAR00656;MAR00658;MAR00661;MAR00714;MAR01871;MAR01939;MAR04110;MAR04146;MAR04181;MAR04384;MAR04886;MAR04889;MAR04899;MAR08966;MAR08967;MAR09010;MAR09026;MAR09038;MAR09039;MAR09040;MAR09041;MAR09042;MAR09044;MAR09045;MAR09046;MAR09047;MAR09058;MAR09061;MAR09062;MAR09063;MAR09064;MAR09066;MAR09067;MAR09069;MAR09070;MAR09071;MAR09072;MAR09076;MAR09079;MAR09103;MAR09107;MAR09108;MAR09109;MAR09133;MAR09143;MAR09151;MAR09153;MAR09172;MAR09209;MAR09215;MAR09242;MAR09253;MAR09255;MAR09259;MAR09269;MAR09271;MAR09272;MAR09292;MAR09297;MAR09298;MAR09300;MAR09353;MAR09354;MAR09358;MAR09362;MAR09378;MAR09383;MAR09386;MAR09404;MAR09406;MAR09423;MAR09437;MAR09440;MAR09702;MAR09729;MAR09847;MAR09849;MAR09858;MAR09860;MAR09862;MAR09864;MAR09868;MAR09920;MAR09921;MAR10024;MAR10047;MAR10184;MAR10188;MAR10193;MAR10195;MAR10197;MAR10243;MAR10250;MAR10440;MAR10496;MAR11400;MAR11403;MAR11424;MAR11823;MAR11895;MAR11897;MAR11947;MAR11953;MAR11974;MAR12127</x:v>
       </x:c>
       <x:c r="L1151" s="2" t="n">
-        <x:v>0.000907820567550419</x:v>
+        <x:v>0.000883399663394092</x:v>
       </x:c>
       <x:c r="M1151" s="3" t="b">
         <x:v>1</x:v>
@@ -46321,7 +46321,7 @@
         <x:v>MAR02152;MAR02153;MAR02154;MAR02155;MAR02156;MAR02157;MAR02158;MAR02159;MAR02160;MAR02161;MAR02162;MAR02163</x:v>
       </x:c>
       <x:c r="L1156" s="2" t="n">
-        <x:v>1.9063471500003807e-7</x:v>
+        <x:v>1.8431738526319473e-7</x:v>
       </x:c>
       <x:c r="M1156" s="3" t="b">
         <x:v>1</x:v>
@@ -46990,7 +46990,7 @@
         <x:v>MAR00129;MAR00579;MAR00580;MAR00581;MAR00598;MAR00632;MAR00643;MAR00651;MAR07594;MAR07597;MAR07601</x:v>
       </x:c>
       <x:c r="L1173" s="2" t="n">
-        <x:v>0.01994726828660847</x:v>
+        <x:v>0.019771872642201847</x:v>
       </x:c>
       <x:c r="M1173" s="3" t="b">
         <x:v>1</x:v>
@@ -47072,7 +47072,7 @@
         <x:v>MAR04368;MAR04373;MAR04375;MAR04391</x:v>
       </x:c>
       <x:c r="L1175" s="2" t="n">
-        <x:v>0.46603300829707567</x:v>
+        <x:v>0.4785645909656424</x:v>
       </x:c>
       <x:c r="M1175" s="3" t="b">
         <x:v>0</x:v>
@@ -47858,7 +47858,7 @@
         <x:v>MAR06402;MAR06403</x:v>
       </x:c>
       <x:c r="L1195" s="2" t="n">
-        <x:v>0.09620174651807363</x:v>
+        <x:v>0.09680678894900491</x:v>
       </x:c>
       <x:c r="M1195" s="3" t="b">
         <x:v>0</x:v>
@@ -48059,7 +48059,7 @@
         <x:v>MAR00061;MAR00157;MAR00158;MAR00578;MAR01046;MAR02225;MAR03789;MAR03946;MAR04756;MAR04852;MAR04855;MAR04874;MAR04898;MAR04905;MAR04914;MAR04922;MAR04963;MAR05126;MAR05227;MAR05304;MAR06328;MAR06438;MAR06454;MAR06469;MAR06481;MAR06513;MAR06781;MAR07638;MAR07719;MAR08009;MAR08428;MAR08430;MAR08614;MAR08891;MAR08987;MAR08997;MAR08998;MAR10049;MAR11357;MAR20137;MAR20138;MAR20139;MAR20148;MAR20156;MAR20161;MAR20164</x:v>
       </x:c>
       <x:c r="L1200" s="2" t="n">
-        <x:v>0.000032726480551613474</x:v>
+        <x:v>0.000031514388679331494</x:v>
       </x:c>
       <x:c r="M1200" s="3" t="b">
         <x:v>1</x:v>
@@ -48139,7 +48139,7 @@
         <x:v>MAR01542;MAR04265;MAR04269;MAR08791</x:v>
       </x:c>
       <x:c r="L1202" s="2" t="n">
-        <x:v>0.2664776651905659</x:v>
+        <x:v>0.2725779355829798</x:v>
       </x:c>
       <x:c r="M1202" s="3" t="b">
         <x:v>0</x:v>
@@ -48180,7 +48180,7 @@
         <x:v>MAR01095;MAR05422;MAR05423;MAR07765;MAR07767;MAR07786;MAR07792;MAR07796;MAR07857;MAR07860;MAR07861;MAR07862;MAR13086</x:v>
       </x:c>
       <x:c r="L1203" s="2" t="n">
-        <x:v>0.004321826495207726</x:v>
+        <x:v>0.004218925864369447</x:v>
       </x:c>
       <x:c r="M1203" s="3" t="b">
         <x:v>1</x:v>
@@ -48221,7 +48221,7 @@
         <x:v>MAR03967;MAR04054;MAR04344;MAR04633;MAR07160;MAR07161;MAR07717;MAR07801;MAR07865;MAR07867;MAR07869;MAR08452;MAR08456;MAR08465;MAR08486</x:v>
       </x:c>
       <x:c r="L1204" s="2" t="n">
-        <x:v>0.0015153757433369096</x:v>
+        <x:v>0.0014682307202108725</x:v>
       </x:c>
       <x:c r="M1204" s="3" t="b">
         <x:v>1</x:v>
@@ -48418,7 +48418,7 @@
         <x:v>MAR03977;MAR06911;MAR06912;MAR06914;MAR06916;MAR06918</x:v>
       </x:c>
       <x:c r="L1209" s="2" t="n">
-        <x:v>0.000027974876587954886</x:v>
+        <x:v>0.00002704238070168972</x:v>
       </x:c>
       <x:c r="M1209" s="3" t="b">
         <x:v>1</x:v>
@@ -48537,7 +48537,7 @@
         <x:v>MAR04350;MAR04354;MAR04398;MAR04710</x:v>
       </x:c>
       <x:c r="L1212" s="2" t="n">
-        <x:v>0.18314448829805452</x:v>
+        <x:v>0.18438119141117826</x:v>
       </x:c>
       <x:c r="M1212" s="3" t="b">
         <x:v>0</x:v>
@@ -48820,7 +48820,7 @@
         <x:v>MAR01044;MAR04752;MAR04762;MAR04770;MAR11316;MAR11406</x:v>
       </x:c>
       <x:c r="L1219" s="2" t="n">
-        <x:v>0.0034405249151457885</x:v>
+        <x:v>0.0033726433228428083</x:v>
       </x:c>
       <x:c r="M1219" s="3" t="b">
         <x:v>1</x:v>
@@ -49058,7 +49058,7 @@
         <x:v>MAR04002;MAR04010;MAR04135;MAR04453;MAR04480;MAR04481;MAR04574;MAR04603;MAR04614;MAR04695</x:v>
       </x:c>
       <x:c r="L1225" s="2" t="n">
-        <x:v>0.16605300932046063</x:v>
+        <x:v>0.1677303124449097</x:v>
       </x:c>
       <x:c r="M1225" s="3" t="b">
         <x:v>0</x:v>
@@ -49099,7 +49099,7 @@
         <x:v>MAR03931;MAR03970;MAR04008;MAR04032;MAR04512;MAR04579;MAR06627;MAR08274</x:v>
       </x:c>
       <x:c r="L1226" s="2" t="n">
-        <x:v>0.1055287611275653</x:v>
+        <x:v>0.10559897321081717</x:v>
       </x:c>
       <x:c r="M1226" s="3" t="b">
         <x:v>0</x:v>
@@ -49179,7 +49179,7 @@
         <x:v>MAR03980;MAR04767</x:v>
       </x:c>
       <x:c r="L1228" s="2" t="n">
-        <x:v>0.42749319597064067</x:v>
+        <x:v>0.4400860187976828</x:v>
       </x:c>
       <x:c r="M1228" s="3" t="b">
         <x:v>0</x:v>
@@ -49220,7 +49220,7 @@
         <x:v>MAR06634;MAR06638;MAR06641;MAR06642;MAR06644;MAR06649;MAR06651;MAR06652;MAR06654;MAR06655;MAR06656;MAR06657;MAR06658;MAR06660;MAR06664;MAR06665;MAR06668;MAR06669;MAR06672;MAR06673;MAR06674;MAR06675;MAR06677;MAR06678;MAR06682;MAR06687;MAR06690;MAR06691;MAR06692;MAR06693;MAR06700;MAR06701;MAR06702;MAR06703;MAR08702;MAR08711</x:v>
       </x:c>
       <x:c r="L1229" s="2" t="n">
-        <x:v>1.6156644521672652e-24</x:v>
+        <x:v>1.498587317952246e-24</x:v>
       </x:c>
       <x:c r="M1229" s="3" t="b">
         <x:v>1</x:v>
@@ -49657,7 +49657,7 @@
         <x:v>MAR04147;MAR04152;MAR04652</x:v>
       </x:c>
       <x:c r="L1240" s="2" t="n">
-        <x:v>0.6926455195614194</x:v>
+        <x:v>0.7010045374837169</x:v>
       </x:c>
       <x:c r="M1240" s="3" t="b">
         <x:v>0</x:v>
@@ -49942,7 +49942,7 @@
         <x:v>MAR02960;MAR02993</x:v>
       </x:c>
       <x:c r="L1247" s="2" t="n">
-        <x:v>0.3612464832207184</x:v>
+        <x:v>0.3698068264250008</x:v>
       </x:c>
       <x:c r="M1247" s="3" t="b">
         <x:v>0</x:v>
@@ -49983,7 +49983,7 @@
         <x:v>MAR08613;MAR08615;MAR08616</x:v>
       </x:c>
       <x:c r="L1248" s="2" t="n">
-        <x:v>0.00435159855784798</x:v>
+        <x:v>0.004244627108540016</x:v>
       </x:c>
       <x:c r="M1248" s="3" t="b">
         <x:v>1</x:v>
@@ -50141,7 +50141,7 @@
         <x:v>MAR02129;MAR02130;MAR02131;MAR02132;MAR02133;MAR02134;MAR02135;MAR02136;MAR02137;MAR02138;MAR02139;MAR02142;MAR02143;MAR02144;MAR02145;MAR08006</x:v>
       </x:c>
       <x:c r="L1252" s="2" t="n">
-        <x:v>1.1318893845749194e-11</x:v>
+        <x:v>1.0518568018271979e-11</x:v>
       </x:c>
       <x:c r="M1252" s="3" t="b">
         <x:v>1</x:v>
@@ -50182,7 +50182,7 @@
         <x:v>MAR06436;MAR06453;MAR06465;MAR06467;MAR06470;MAR06471;MAR06472;MAR06473;MAR06476;MAR06478;MAR06482;MAR06484;MAR06486;MAR06488;MAR06492</x:v>
       </x:c>
       <x:c r="L1253" s="2" t="n">
-        <x:v>1.9963959498597687e-9</x:v>
+        <x:v>1.8854850637564482e-9</x:v>
       </x:c>
       <x:c r="M1253" s="3" t="b">
         <x:v>1</x:v>
@@ -50262,7 +50262,7 @@
         <x:v>MAR00019;MAR00061;MAR00089;MAR00090;MAR00142;MAR00157;MAR00158;MAR00569;MAR00574;MAR00578;MAR00628;MAR00631;MAR00656;MAR00658;MAR00661;MAR00714;MAR01046;MAR01095;MAR01461;MAR01462;MAR01499;MAR01514;MAR01525;MAR01601;MAR01607;MAR01669;MAR01827;MAR01871;MAR01939;MAR02225;MAR02351;MAR03106;MAR03597;MAR03789;MAR03946;MAR03951;MAR03959;MAR04110;MAR04146;MAR04181;MAR04384;MAR04756;MAR04847;MAR04848;MAR04852;MAR04855;MAR04874;MAR04875;MAR04882;MAR04883;MAR04886;MAR04889;MAR04894;MAR04898;MAR04899;MAR04905;MAR04914;MAR04919;MAR04922;MAR04947;MAR04948;MAR04958;MAR04963;MAR04969;MAR04985;MAR04990;MAR05034;MAR05042;MAR05068;MAR05071;MAR05126;MAR05206;MAR05227;MAR05303;MAR05304;MAR05305;MAR05308;MAR05314;MAR05315;MAR05316;MAR05318;MAR05320;MAR05322;MAR05422;MAR05423;MAR05530;MAR05531;MAR05987;MAR06061;MAR06067;MAR06250;MAR06258;MAR06328;MAR06366;MAR06367;MAR06375;MAR06383;MAR06438;MAR06454;MAR06462;MAR06463;MAR06468;MAR06469;MAR06474;MAR06481;MAR06505;MAR06512;MAR06513;MAR06629;MAR06781;MAR07590;MAR07596;MAR07609;MAR07638;MAR07719;MAR07735;MAR07765;MAR07767;MAR07772;MAR07776;MAR07777;MAR07778;MAR07779;MAR07780;MAR07781;MAR07786;MAR07792;MAR07796;MAR07811;MAR07819;MAR07857;MAR07860;MAR07861;MAR07862;MAR08009;MAR08010;MAR08408;MAR08428;MAR08430;MAR08612;MAR08614;MAR08676;MAR08716;MAR08720;MAR08721;MAR08722;MAR08891;MAR08966;MAR08967;MAR08987;MAR08991;MAR08997;MAR08998;MAR08999;MAR09006;MAR09010;MAR09026;MAR09031;MAR09038;MAR09039;MAR09040;MAR09041;MAR09042;MAR09044;MAR09045;MAR09046;MAR09047;MAR09058;MAR09061;MAR09062;MAR09063;MAR09064;MAR09066;MAR09067;MAR09069;MAR09070;MAR09071;MAR09072;MAR09076;MAR09079;MAR09103;MAR09107;MAR09108;MAR09109;MAR09112;MAR09133;MAR09143;MAR09151;MAR09153;MAR09172;MAR09209;MAR09215;MAR09242;MAR09253;MAR09255;MAR09259;MAR09269;MAR09271;MAR09272;MAR09292;MAR09297;MAR09298;MAR09300;MAR09353;MAR09354;MAR09358;MAR09362;MAR09378;MAR09383;MAR09386;MAR09404;MAR09406;MAR09423;MAR09437;MAR09440;MAR09593;MAR09609;MAR09637;MAR09641;MAR09650;MAR09702;MAR09728;MAR09729;MAR09824;MAR09827;MAR09828;MAR09830;MAR09834;MAR09836;MAR09837;MAR09839;MAR09847;MAR09849;MAR09858;MAR09860;MAR09862;MAR09864;MAR09868;MAR09872;MAR09883;MAR09884;MAR09895;MAR09902;MAR09904;MAR09913;MAR09920;MAR09921;MAR09960;MAR09968;MAR09973;MAR09983;MAR09989;MAR09996;MAR10023;MAR10024;MAR10039;MAR10040;MAR10046;MAR10047;MAR10049;MAR10184;MAR10188;MAR10193;MAR10195;MAR10197;MAR10243;MAR10250;MAR10363;MAR10364;MAR10366;MAR10375;MAR10440;MAR10486;MAR10489;MAR10496;MAR11250;MAR11256;MAR11257;MAR11261;MAR11318;MAR11357;MAR11400;MAR11403;MAR11414;MAR11424;MAR11583;MAR11756;MAR11787;MAR11823;MAR11894;MAR11895;MAR11896;MAR11897;MAR11947;MAR11953;MAR11973;MAR11974;MAR12127;MAR13086;MAR20137;MAR20138;MAR20139;MAR20148;MAR20156;MAR20161;MAR20164</x:v>
       </x:c>
       <x:c r="L1255" s="2" t="n">
-        <x:v>0.00032480145079112713</x:v>
+        <x:v>0.00031695600511984386</x:v>
       </x:c>
       <x:c r="M1255" s="3" t="b">
         <x:v>1</x:v>
@@ -50345,6259 +50345,6 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="M1257" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1258" ht="18" customHeight="1">
-      <x:c r="A1258" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1258" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1258" s="2" t="str">
-        <x:v>Acyl-CoA hydrolysis</x:v>
-      </x:c>
-      <x:c r="D1258" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1258" s="2" t="n">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="F1258" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1258" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1258" s="2" t="n">
-        <x:v>3.464920407647604</x:v>
-      </x:c>
-      <x:c r="I1258" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1258" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1258" s="2"/>
-      <x:c r="L1258" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1258" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1259" ht="18" customHeight="1">
-      <x:c r="A1259" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1259" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1259" s="2" t="str">
-        <x:v>Acylglycerides metabolism</x:v>
-      </x:c>
-      <x:c r="D1259" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1259" s="2" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F1259" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1259" s="2" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H1259" s="2" t="n">
-        <x:v>1.099974732586541</x:v>
-      </x:c>
-      <x:c r="I1259" s="2" t="n">
-        <x:v>3.6364471669218985</x:v>
-      </x:c>
-      <x:c r="J1259" s="2" t="n">
-        <x:v>0.021712206188381527</x:v>
-      </x:c>
-      <x:c r="K1259" s="2" t="str">
-        <x:v>MAR00604;MAR00605;MAR00670;MAR07588</x:v>
-      </x:c>
-      <x:c r="L1259" s="2" t="n">
-        <x:v>0.15573272763544718</x:v>
-      </x:c>
-      <x:c r="M1259" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1260" ht="18" customHeight="1">
-      <x:c r="A1260" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1260" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1260" s="2" t="str">
-        <x:v>Alanine, aspartate and glutamate metabolism</x:v>
-      </x:c>
-      <x:c r="D1260" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1260" s="2" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="F1260" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1260" s="2" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H1260" s="2" t="n">
-        <x:v>1.5399646256211572</x:v>
-      </x:c>
-      <x:c r="I1260" s="2" t="n">
-        <x:v>1.948096696565303</x:v>
-      </x:c>
-      <x:c r="J1260" s="2" t="n">
-        <x:v>0.197651044094222</x:v>
-      </x:c>
-      <x:c r="K1260" s="2" t="str">
-        <x:v>MAR03802;MAR03804;MAR03899</x:v>
-      </x:c>
-      <x:c r="L1260" s="2" t="n">
-        <x:v>0.8922713268534685</x:v>
-      </x:c>
-      <x:c r="M1260" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1261" ht="18" customHeight="1">
-      <x:c r="A1261" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1261" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1261" s="2" t="str">
-        <x:v>Alkaloids biosynthesis</x:v>
-      </x:c>
-      <x:c r="D1261" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1261" s="2" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F1261" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1261" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1261" s="2" t="n">
-        <x:v>0.10999747325865408</x:v>
-      </x:c>
-      <x:c r="I1261" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1261" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1261" s="2"/>
-      <x:c r="L1261" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1261" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1262" ht="18" customHeight="1">
-      <x:c r="A1262" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1262" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1262" s="2" t="str">
-        <x:v>Amino sugar and nucleotide sugar metabolism</x:v>
-      </x:c>
-      <x:c r="D1262" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1262" s="2" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F1262" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1262" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1262" s="2" t="n">
-        <x:v>1.4849658889918302</x:v>
-      </x:c>
-      <x:c r="I1262" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1262" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1262" s="2"/>
-      <x:c r="L1262" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1262" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1263" ht="18" customHeight="1">
-      <x:c r="A1263" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1263" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1263" s="2" t="str">
-        <x:v>Aminoacyl-tRNA biosynthesis</x:v>
-      </x:c>
-      <x:c r="D1263" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1263" s="2" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F1263" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1263" s="2" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H1263" s="2" t="n">
-        <x:v>1.099974732586541</x:v>
-      </x:c>
-      <x:c r="I1263" s="2" t="n">
-        <x:v>18.182235834609493</x:v>
-      </x:c>
-      <x:c r="J1263" s="2" t="n">
-        <x:v>4.8569833216080157e-26</x:v>
-      </x:c>
-      <x:c r="K1263" s="2" t="str">
-        <x:v>MAR05130;MAR05131;MAR05132;MAR05133;MAR05134;MAR05135;MAR05136;MAR05137;MAR05138;MAR05139;MAR05140;MAR05141;MAR05142;MAR05143;MAR05145;MAR05146;MAR05147;MAR05148;MAR05149;MAR05150</x:v>
-      </x:c>
-      <x:c r="L1263" s="2" t="n">
-        <x:v>2.7451669733728507e-24</x:v>
-      </x:c>
-      <x:c r="M1263" s="3" t="b">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1264" ht="18" customHeight="1">
-      <x:c r="A1264" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1264" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1264" s="2" t="str">
-        <x:v>Androgen metabolism</x:v>
-      </x:c>
-      <x:c r="D1264" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1264" s="2" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F1264" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1264" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1264" s="2" t="n">
-        <x:v>1.319969679103849</x:v>
-      </x:c>
-      <x:c r="I1264" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1264" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1264" s="2"/>
-      <x:c r="L1264" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1264" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1265" ht="18" customHeight="1">
-      <x:c r="A1265" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1265" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1265" s="2" t="str">
-        <x:v>Arachidonic acid metabolism</x:v>
-      </x:c>
-      <x:c r="D1265" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1265" s="2" t="n">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="F1265" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1265" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1265" s="2" t="n">
-        <x:v>4.784890086751453</x:v>
-      </x:c>
-      <x:c r="I1265" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1265" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1265" s="2"/>
-      <x:c r="L1265" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1265" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1266" ht="18" customHeight="1">
-      <x:c r="A1266" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1266" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1266" s="2" t="str">
-        <x:v>Arginine and proline metabolism</x:v>
-      </x:c>
-      <x:c r="D1266" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1266" s="2" t="n">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="F1266" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1266" s="2" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H1266" s="2" t="n">
-        <x:v>3.90491030068222</x:v>
-      </x:c>
-      <x:c r="I1266" s="2" t="n">
-        <x:v>2.0487026292517743</x:v>
-      </x:c>
-      <x:c r="J1266" s="2" t="n">
-        <x:v>0.04040050810958873</x:v>
-      </x:c>
-      <x:c r="K1266" s="2" t="str">
-        <x:v>MAR03806;MAR03820;MAR03837;MAR03956;MAR04785;MAR08096;MAR08097;MAR08427</x:v>
-      </x:c>
-      <x:c r="L1266" s="2" t="n">
-        <x:v>0.2548478480305753</x:v>
-      </x:c>
-      <x:c r="M1266" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1267" ht="18" customHeight="1">
-      <x:c r="A1267" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1267" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1267" s="2" t="str">
-        <x:v>Artificial reactions</x:v>
-      </x:c>
-      <x:c r="D1267" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1267" s="2" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F1267" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1267" s="2" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H1267" s="2" t="n">
-        <x:v>0.9899772593278868</x:v>
-      </x:c>
-      <x:c r="I1267" s="2" t="n">
-        <x:v>6.060745278203164</x:v>
-      </x:c>
-      <x:c r="J1267" s="2" t="n">
-        <x:v>0.00028398085548413874</x:v>
-      </x:c>
-      <x:c r="K1267" s="2" t="str">
-        <x:v>MAR00021;MAR00022;MAR00023;MAR00033;MAR00034;MAR04413</x:v>
-      </x:c>
-      <x:c r="L1267" s="2" t="n">
-        <x:v>0.0034296149470007527</x:v>
-      </x:c>
-      <x:c r="M1267" s="3" t="b">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1268" ht="18" customHeight="1">
-      <x:c r="A1268" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1268" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1268" s="2" t="str">
-        <x:v>Ascaroside transport and biosynthesis</x:v>
-      </x:c>
-      <x:c r="D1268" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1268" s="2" t="n">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F1268" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1268" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1268" s="2" t="n">
-        <x:v>1.7049608355091384</x:v>
-      </x:c>
-      <x:c r="I1268" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1268" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1268" s="2"/>
-      <x:c r="L1268" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1268" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1269" ht="18" customHeight="1">
-      <x:c r="A1269" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1269" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1269" s="2" t="str">
-        <x:v>Ascorbate and aldarate metabolism</x:v>
-      </x:c>
-      <x:c r="D1269" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1269" s="2" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F1269" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1269" s="2" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H1269" s="2" t="n">
-        <x:v>0.7699823128105786</x:v>
-      </x:c>
-      <x:c r="I1269" s="2" t="n">
-        <x:v>3.896193393130606</x:v>
-      </x:c>
-      <x:c r="J1269" s="2" t="n">
-        <x:v>0.038270472478803975</x:v>
-      </x:c>
-      <x:c r="K1269" s="2" t="str">
-        <x:v>MAR06394;MAR06396;MAR08619</x:v>
-      </x:c>
-      <x:c r="L1269" s="2" t="n">
-        <x:v>0.2458008073297728</x:v>
-      </x:c>
-      <x:c r="M1269" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1270" ht="18" customHeight="1">
-      <x:c r="A1270" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1270" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1270" s="2" t="str">
-        <x:v>Beta oxidation of branched-chain fatty acids (mitochondrial)</x:v>
-      </x:c>
-      <x:c r="D1270" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1270" s="2" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F1270" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1270" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1270" s="2" t="n">
-        <x:v>0.7149835761812516</x:v>
-      </x:c>
-      <x:c r="I1270" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1270" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1270" s="2"/>
-      <x:c r="L1270" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1270" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1271" ht="18" customHeight="1">
-      <x:c r="A1271" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1271" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1271" s="2" t="str">
-        <x:v>Beta oxidation of di-unsaturated fatty acids (n-6) (mitochondrial)</x:v>
-      </x:c>
-      <x:c r="D1271" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1271" s="2" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="F1271" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1271" s="2" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="H1271" s="2" t="n">
-        <x:v>1.0449759959572138</x:v>
-      </x:c>
-      <x:c r="I1271" s="2" t="n">
-        <x:v>10.526557588458129</x:v>
-      </x:c>
-      <x:c r="J1271" s="2" t="n">
-        <x:v>6.470331273123996e-10</x:v>
-      </x:c>
-      <x:c r="K1271" s="2" t="str">
-        <x:v>MAR03281;MAR03282;MAR03283;MAR03285;MAR03286;MAR03287;MAR03288;MAR03290;MAR03292;MAR03293;MAR03298</x:v>
-      </x:c>
-      <x:c r="L1271" s="2" t="n">
-        <x:v>1.549589506597323e-8</x:v>
-      </x:c>
-      <x:c r="M1271" s="3" t="b">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1272" ht="18" customHeight="1">
-      <x:c r="A1272" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1272" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1272" s="2" t="str">
-        <x:v>Beta oxidation of di-unsaturated fatty acids (n-6) (peroxisomal)</x:v>
-      </x:c>
-      <x:c r="D1272" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1272" s="2" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="F1272" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1272" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1272" s="2" t="n">
-        <x:v>1.0449759959572138</x:v>
-      </x:c>
-      <x:c r="I1272" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1272" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1272" s="2"/>
-      <x:c r="L1272" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1272" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1273" ht="18" customHeight="1">
-      <x:c r="A1273" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1273" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1273" s="2" t="str">
-        <x:v>Beta oxidation of even-chain fatty acids (mitochondrial)</x:v>
-      </x:c>
-      <x:c r="D1273" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1273" s="2" t="n">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="F1273" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1273" s="2" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H1273" s="2" t="n">
-        <x:v>3.2449254611302956</x:v>
-      </x:c>
-      <x:c r="I1273" s="2" t="n">
-        <x:v>2.1572144210553637</x:v>
-      </x:c>
-      <x:c r="J1273" s="2" t="n">
-        <x:v>0.04211313821724128</x:v>
-      </x:c>
-      <x:c r="K1273" s="2" t="str">
-        <x:v>MAR03136;MAR03137;MAR03139;MAR03150;MAR03151;MAR03153;MAR03430</x:v>
-      </x:c>
-      <x:c r="L1273" s="2" t="n">
-        <x:v>0.26099063289895585</x:v>
-      </x:c>
-      <x:c r="M1273" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1274" ht="18" customHeight="1">
-      <x:c r="A1274" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1274" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1274" s="2" t="str">
-        <x:v>Beta oxidation of even-chain fatty acids (peroxisomal)</x:v>
-      </x:c>
-      <x:c r="D1274" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1274" s="2" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="F1274" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1274" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1274" s="2" t="n">
-        <x:v>2.749936831466352</x:v>
-      </x:c>
-      <x:c r="I1274" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1274" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1274" s="2"/>
-      <x:c r="L1274" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1274" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1275" ht="18" customHeight="1">
-      <x:c r="A1275" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1275" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1275" s="2" t="str">
-        <x:v>Beta oxidation of odd-chain fatty acids (mitochondrial)</x:v>
-      </x:c>
-      <x:c r="D1275" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1275" s="2" t="n">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F1275" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1275" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1275" s="2" t="n">
-        <x:v>2.0899519919144276</x:v>
-      </x:c>
-      <x:c r="I1275" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1275" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1275" s="2"/>
-      <x:c r="L1275" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1275" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1276" ht="18" customHeight="1">
-      <x:c r="A1276" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1276" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1276" s="2" t="str">
-        <x:v>Beta oxidation of odd-chain fatty acids (peroxisomal)</x:v>
-      </x:c>
-      <x:c r="D1276" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1276" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F1276" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1276" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1276" s="2" t="n">
-        <x:v>0.05499873662932704</x:v>
-      </x:c>
-      <x:c r="I1276" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1276" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1276" s="2"/>
-      <x:c r="L1276" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1276" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1277" ht="18" customHeight="1">
-      <x:c r="A1277" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1277" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1277" s="2" t="str">
-        <x:v>Beta oxidation of phytanic acid (peroxisomal)</x:v>
-      </x:c>
-      <x:c r="D1277" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1277" s="2" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F1277" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1277" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1277" s="2" t="n">
-        <x:v>0.9349785226985597</x:v>
-      </x:c>
-      <x:c r="I1277" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1277" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1277" s="2"/>
-      <x:c r="L1277" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1277" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1278" ht="18" customHeight="1">
-      <x:c r="A1278" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1278" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1278" s="2" t="str">
-        <x:v>Beta oxidation of poly-unsaturated fatty acids (mitochondrial)</x:v>
-      </x:c>
-      <x:c r="D1278" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1278" s="2" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F1278" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1278" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1278" s="2" t="n">
-        <x:v>1.209972205845195</x:v>
-      </x:c>
-      <x:c r="I1278" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1278" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1278" s="2"/>
-      <x:c r="L1278" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1278" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1279" ht="18" customHeight="1">
-      <x:c r="A1279" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1279" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1279" s="2" t="str">
-        <x:v>Beta oxidation of unsaturated fatty acids (n-7) (mitochondrial)</x:v>
-      </x:c>
-      <x:c r="D1279" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1279" s="2" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F1279" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1279" s="2" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H1279" s="2" t="n">
-        <x:v>0.9349785226985597</x:v>
-      </x:c>
-      <x:c r="I1279" s="2" t="n">
-        <x:v>9.625889559499145</x:v>
-      </x:c>
-      <x:c r="J1279" s="2" t="n">
-        <x:v>7.120156792048489e-8</x:v>
-      </x:c>
-      <x:c r="K1279" s="2" t="str">
-        <x:v>MAR03250;MAR03252;MAR03254;MAR03256;MAR03258;MAR03260;MAR03262;MAR03264;MAR03272</x:v>
-      </x:c>
-      <x:c r="L1279" s="2" t="n">
-        <x:v>0.0000013055285331639876</x:v>
-      </x:c>
-      <x:c r="M1279" s="3" t="b">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1280" ht="18" customHeight="1">
-      <x:c r="A1280" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1280" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1280" s="2" t="str">
-        <x:v>Beta oxidation of unsaturated fatty acids (n-7) (peroxisomal)</x:v>
-      </x:c>
-      <x:c r="D1280" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1280" s="2" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F1280" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1280" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1280" s="2" t="n">
-        <x:v>0.43998989303461633</x:v>
-      </x:c>
-      <x:c r="I1280" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1280" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1280" s="2"/>
-      <x:c r="L1280" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1280" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1281" ht="18" customHeight="1">
-      <x:c r="A1281" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1281" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1281" s="2" t="str">
-        <x:v>Beta oxidation of unsaturated fatty acids (n-9) (mitochondrial)</x:v>
-      </x:c>
-      <x:c r="D1281" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1281" s="2" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F1281" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1281" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1281" s="2" t="n">
-        <x:v>1.154973469215868</x:v>
-      </x:c>
-      <x:c r="I1281" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1281" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1281" s="2"/>
-      <x:c r="L1281" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1281" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1282" ht="18" customHeight="1">
-      <x:c r="A1282" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1282" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1282" s="2" t="str">
-        <x:v>Beta oxidation of unsaturated fatty acids (n-9) (peroxisomal)</x:v>
-      </x:c>
-      <x:c r="D1282" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1282" s="2" t="n">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F1282" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1282" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1282" s="2" t="n">
-        <x:v>2.0899519919144276</x:v>
-      </x:c>
-      <x:c r="I1282" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1282" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1282" s="2"/>
-      <x:c r="L1282" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1282" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1283" ht="18" customHeight="1">
-      <x:c r="A1283" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1283" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1283" s="2" t="str">
-        <x:v>Beta-alanine metabolism</x:v>
-      </x:c>
-      <x:c r="D1283" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1283" s="2" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F1283" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1283" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1283" s="2" t="n">
-        <x:v>0.7699823128105786</x:v>
-      </x:c>
-      <x:c r="I1283" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1283" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1283" s="2"/>
-      <x:c r="L1283" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1283" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1284" ht="18" customHeight="1">
-      <x:c r="A1284" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1284" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1284" s="2" t="str">
-        <x:v>Bile acid biosynthesis</x:v>
-      </x:c>
-      <x:c r="D1284" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1284" s="2" t="n">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="F1284" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1284" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H1284" s="2" t="n">
-        <x:v>11.824728375305314</x:v>
-      </x:c>
-      <x:c r="I1284" s="2" t="n">
-        <x:v>0.08456853876562556</x:v>
-      </x:c>
-      <x:c r="J1284" s="2" t="n">
-        <x:v>0.9999953401283227</x:v>
-      </x:c>
-      <x:c r="K1284" s="2" t="str">
-        <x:v>MAR01843</x:v>
-      </x:c>
-      <x:c r="L1284" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1284" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1285" ht="18" customHeight="1">
-      <x:c r="A1285" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1285" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1285" s="2" t="str">
-        <x:v>Bile acid recycling</x:v>
-      </x:c>
-      <x:c r="D1285" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1285" s="2" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F1285" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1285" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1285" s="2" t="n">
-        <x:v>1.7599595721384653</x:v>
-      </x:c>
-      <x:c r="I1285" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1285" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1285" s="2"/>
-      <x:c r="L1285" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1285" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1286" ht="18" customHeight="1">
-      <x:c r="A1286" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1286" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1286" s="2" t="str">
-        <x:v>Biopterin metabolism</x:v>
-      </x:c>
-      <x:c r="D1286" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1286" s="2" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F1286" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1286" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1286" s="2" t="n">
-        <x:v>1.4849658889918302</x:v>
-      </x:c>
-      <x:c r="I1286" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1286" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1286" s="2"/>
-      <x:c r="L1286" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1286" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1287" ht="18" customHeight="1">
-      <x:c r="A1287" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1287" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1287" s="2" t="str">
-        <x:v>Biotin metabolism</x:v>
-      </x:c>
-      <x:c r="D1287" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1287" s="2" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F1287" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1287" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1287" s="2" t="n">
-        <x:v>0.43998989303461633</x:v>
-      </x:c>
-      <x:c r="I1287" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1287" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1287" s="2"/>
-      <x:c r="L1287" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1287" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1288" ht="18" customHeight="1">
-      <x:c r="A1288" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1288" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1288" s="2" t="str">
-        <x:v>Blood group biosynthesis</x:v>
-      </x:c>
-      <x:c r="D1288" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1288" s="2" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F1288" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1288" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1288" s="2" t="n">
-        <x:v>1.9249557820264465</x:v>
-      </x:c>
-      <x:c r="I1288" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1288" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1288" s="2"/>
-      <x:c r="L1288" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1288" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1289" ht="18" customHeight="1">
-      <x:c r="A1289" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1289" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1289" s="2" t="str">
-        <x:v>Butanoate metabolism</x:v>
-      </x:c>
-      <x:c r="D1289" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1289" s="2" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F1289" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1289" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1289" s="2" t="n">
-        <x:v>0.3849911564052893</x:v>
-      </x:c>
-      <x:c r="I1289" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1289" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1289" s="2"/>
-      <x:c r="L1289" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1289" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1290" ht="18" customHeight="1">
-      <x:c r="A1290" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1290" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1290" s="2" t="str">
-        <x:v>C5-branched dibasic acid metabolism</x:v>
-      </x:c>
-      <x:c r="D1290" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1290" s="2" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F1290" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1290" s="2" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H1290" s="2" t="n">
-        <x:v>0.43998989303461633</x:v>
-      </x:c>
-      <x:c r="I1290" s="2" t="n">
-        <x:v>4.545558958652374</x:v>
-      </x:c>
-      <x:c r="J1290" s="2" t="n">
-        <x:v>0.06781907372028059</x:v>
-      </x:c>
-      <x:c r="K1290" s="2" t="str">
-        <x:v>MAR08662;MAR08663</x:v>
-      </x:c>
-      <x:c r="L1290" s="2" t="n">
-        <x:v>0.389445018463027</x:v>
-      </x:c>
-      <x:c r="M1290" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1291" ht="18" customHeight="1">
-      <x:c r="A1291" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1291" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1291" s="2" t="str">
-        <x:v>Carnitine shuttle (cytosolic)</x:v>
-      </x:c>
-      <x:c r="D1291" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1291" s="2" t="n">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="F1291" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1291" s="2" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H1291" s="2" t="n">
-        <x:v>3.1349279878716416</x:v>
-      </x:c>
-      <x:c r="I1291" s="2" t="n">
-        <x:v>2.8708793423067624</x:v>
-      </x:c>
-      <x:c r="J1291" s="2" t="n">
-        <x:v>0.0036583766412469727</x:v>
-      </x:c>
-      <x:c r="K1291" s="2" t="str">
-        <x:v>MAR00159;MAR02591;MAR02594;MAR02599;MAR02626;MAR02730;MAR02742;MAR02746;MAR02759</x:v>
-      </x:c>
-      <x:c r="L1291" s="2" t="n">
-        <x:v>0.03210736766510542</x:v>
-      </x:c>
-      <x:c r="M1291" s="3" t="b">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1292" ht="18" customHeight="1">
-      <x:c r="A1292" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1292" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1292" s="2" t="str">
-        <x:v>Carnitine shuttle (endoplasmic reticular)</x:v>
-      </x:c>
-      <x:c r="D1292" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1292" s="2" t="n">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="F1292" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1292" s="2" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H1292" s="2" t="n">
-        <x:v>7.204834498441842</x:v>
-      </x:c>
-      <x:c r="I1292" s="2" t="n">
-        <x:v>0.5551827735758624</x:v>
-      </x:c>
-      <x:c r="J1292" s="2" t="n">
-        <x:v>0.9347155496663024</x:v>
-      </x:c>
-      <x:c r="K1292" s="2" t="str">
-        <x:v>MAR02869;MAR02870;MAR02896;MAR02897</x:v>
-      </x:c>
-      <x:c r="L1292" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1292" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1293" ht="18" customHeight="1">
-      <x:c r="A1293" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1293" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1293" s="2" t="str">
-        <x:v>Carnitine shuttle (mitochondrial)</x:v>
-      </x:c>
-      <x:c r="D1293" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1293" s="2" t="n">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="F1293" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1293" s="2" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H1293" s="2" t="n">
-        <x:v>6.159858502484629</x:v>
-      </x:c>
-      <x:c r="I1293" s="2" t="n">
-        <x:v>0.48702417414132576</x:v>
-      </x:c>
-      <x:c r="J1293" s="2" t="n">
-        <x:v>0.9501228912007186</x:v>
-      </x:c>
-      <x:c r="K1293" s="2" t="str">
-        <x:v>MAR02732;MAR02748;MAR02750</x:v>
-      </x:c>
-      <x:c r="L1293" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1293" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1294" ht="18" customHeight="1">
-      <x:c r="A1294" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1294" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1294" s="2" t="str">
-        <x:v>Carnitine shuttle (peroxisomal)</x:v>
-      </x:c>
-      <x:c r="D1294" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1294" s="2" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F1294" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1294" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1294" s="2" t="n">
-        <x:v>0.43998989303461633</x:v>
-      </x:c>
-      <x:c r="I1294" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1294" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1294" s="2"/>
-      <x:c r="L1294" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1294" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1295" ht="18" customHeight="1">
-      <x:c r="A1295" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1295" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1295" s="2" t="str">
-        <x:v>Cholesterol biosynthesis 1 (Bloch pathway)</x:v>
-      </x:c>
-      <x:c r="D1295" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1295" s="2" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F1295" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1295" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1295" s="2" t="n">
-        <x:v>0.7149835761812516</x:v>
-      </x:c>
-      <x:c r="I1295" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1295" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1295" s="2"/>
-      <x:c r="L1295" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1295" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1296" ht="18" customHeight="1">
-      <x:c r="A1296" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1296" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1296" s="2" t="str">
-        <x:v>Cholesterol biosynthesis 2</x:v>
-      </x:c>
-      <x:c r="D1296" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1296" s="2" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F1296" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1296" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H1296" s="2" t="n">
-        <x:v>0.10999747325865408</x:v>
-      </x:c>
-      <x:c r="I1296" s="2" t="n">
-        <x:v>9.091117917304748</x:v>
-      </x:c>
-      <x:c r="J1296" s="2" t="n">
-        <x:v>0.10697699008123482</x:v>
-      </x:c>
-      <x:c r="K1296" s="2" t="str">
-        <x:v>MAR01565</x:v>
-      </x:c>
-      <x:c r="L1296" s="2" t="n">
-        <x:v>0.5476756774811044</x:v>
-      </x:c>
-      <x:c r="M1296" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1297" ht="18" customHeight="1">
-      <x:c r="A1297" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1297" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1297" s="2" t="str">
-        <x:v>Cholesterol biosynthesis 3 (Kandustch-Russell pathway)</x:v>
-      </x:c>
-      <x:c r="D1297" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1297" s="2" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F1297" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1297" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1297" s="2" t="n">
-        <x:v>0.43998989303461633</x:v>
-      </x:c>
-      <x:c r="I1297" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1297" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1297" s="2"/>
-      <x:c r="L1297" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1297" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1298" ht="18" customHeight="1">
-      <x:c r="A1298" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1298" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1298" s="2" t="str">
-        <x:v>Cholesterol metabolism</x:v>
-      </x:c>
-      <x:c r="D1298" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1298" s="2" t="n">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="F1298" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1298" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1298" s="2" t="n">
-        <x:v>2.584940621578371</x:v>
-      </x:c>
-      <x:c r="I1298" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1298" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1298" s="2"/>
-      <x:c r="L1298" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1298" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1299" ht="18" customHeight="1">
-      <x:c r="A1299" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1299" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1299" s="2" t="str">
-        <x:v>Chondroitin / heparan sulfate biosynthesis</x:v>
-      </x:c>
-      <x:c r="D1299" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1299" s="2" t="n">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F1299" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1299" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1299" s="2" t="n">
-        <x:v>1.7049608355091384</x:v>
-      </x:c>
-      <x:c r="I1299" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1299" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1299" s="2"/>
-      <x:c r="L1299" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1299" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1300" ht="18" customHeight="1">
-      <x:c r="A1300" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1300" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1300" s="2" t="str">
-        <x:v>Chondroitin sulfate degradation</x:v>
-      </x:c>
-      <x:c r="D1300" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1300" s="2" t="n">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="F1300" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1300" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1300" s="2" t="n">
-        <x:v>2.309946938431736</x:v>
-      </x:c>
-      <x:c r="I1300" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1300" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1300" s="2"/>
-      <x:c r="L1300" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1300" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1301" ht="18" customHeight="1">
-      <x:c r="A1301" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1301" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1301" s="2" t="str">
-        <x:v>Cysteine and methionine metabolism</x:v>
-      </x:c>
-      <x:c r="D1301" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1301" s="2" t="n">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="F1301" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1301" s="2" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H1301" s="2" t="n">
-        <x:v>2.2549482018024087</x:v>
-      </x:c>
-      <x:c r="I1301" s="2" t="n">
-        <x:v>1.3304075000933777</x:v>
-      </x:c>
-      <x:c r="J1301" s="2" t="n">
-        <x:v>0.39396098743550334</x:v>
-      </x:c>
-      <x:c r="K1301" s="2" t="str">
-        <x:v>MAR03996;MAR04323;MAR08641</x:v>
-      </x:c>
-      <x:c r="L1301" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1301" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1302" ht="18" customHeight="1">
-      <x:c r="A1302" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1302" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1302" s="2" t="str">
-        <x:v>Dietary fiber binding</x:v>
-      </x:c>
-      <x:c r="D1302" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1302" s="2" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F1302" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1302" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1302" s="2" t="n">
-        <x:v>0.6599848395519246</x:v>
-      </x:c>
-      <x:c r="I1302" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1302" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1302" s="2"/>
-      <x:c r="L1302" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1302" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1303" ht="18" customHeight="1">
-      <x:c r="A1303" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1303" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1303" s="2" t="str">
-        <x:v>Drug metabolism</x:v>
-      </x:c>
-      <x:c r="D1303" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1303" s="2" t="n">
-        <x:v>558</x:v>
-      </x:c>
-      <x:c r="F1303" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1303" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1303" s="2" t="n">
-        <x:v>30.68929503916449</x:v>
-      </x:c>
-      <x:c r="I1303" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1303" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1303" s="2"/>
-      <x:c r="L1303" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1303" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1304" ht="18" customHeight="1">
-      <x:c r="A1304" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1304" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1304" s="2" t="str">
-        <x:v>Eicosanoid metabolism</x:v>
-      </x:c>
-      <x:c r="D1304" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1304" s="2" t="n">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="F1304" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1304" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1304" s="2" t="n">
-        <x:v>2.474943148319717</x:v>
-      </x:c>
-      <x:c r="I1304" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1304" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1304" s="2"/>
-      <x:c r="L1304" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1304" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1305" ht="18" customHeight="1">
-      <x:c r="A1305" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1305" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1305" s="2" t="str">
-        <x:v>Endoplasmic reticular transport</x:v>
-      </x:c>
-      <x:c r="D1305" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1305" s="2" t="n">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="F1305" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1305" s="2" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H1305" s="2" t="n">
-        <x:v>13.254695527667817</x:v>
-      </x:c>
-      <x:c r="I1305" s="2" t="n">
-        <x:v>1.056229467570676</x:v>
-      </x:c>
-      <x:c r="J1305" s="2" t="n">
-        <x:v>0.4559349165763039</x:v>
-      </x:c>
-      <x:c r="K1305" s="2" t="str">
-        <x:v>MAR00089;MAR01461;MAR04765;MAR04883;MAR04894;MAR06463;MAR06468;MAR06629;MAR07772;MAR07776;MAR07778;MAR07780;MAR08716;MAR08722</x:v>
-      </x:c>
-      <x:c r="L1305" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1305" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1306" ht="18" customHeight="1">
-      <x:c r="A1306" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1306" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1306" s="2" t="str">
-        <x:v>Estrogen metabolism</x:v>
-      </x:c>
-      <x:c r="D1306" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1306" s="2" t="n">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="F1306" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1306" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1306" s="2" t="n">
-        <x:v>3.2449254611302956</x:v>
-      </x:c>
-      <x:c r="I1306" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1306" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1306" s="2"/>
-      <x:c r="L1306" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1306" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1307" ht="18" customHeight="1">
-      <x:c r="A1307" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1307" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1307" s="2" t="str">
-        <x:v>Ether lipid metabolism</x:v>
-      </x:c>
-      <x:c r="D1307" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1307" s="2" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F1307" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1307" s="2" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H1307" s="2" t="n">
-        <x:v>0.8799797860692327</x:v>
-      </x:c>
-      <x:c r="I1307" s="2" t="n">
-        <x:v>3.4091692189892804</x:v>
-      </x:c>
-      <x:c r="J1307" s="2" t="n">
-        <x:v>0.05429730273448238</x:v>
-      </x:c>
-      <x:c r="K1307" s="2" t="str">
-        <x:v>MAR07598;MAR07614;MAR10061</x:v>
-      </x:c>
-      <x:c r="L1307" s="2" t="n">
-        <x:v>0.3223617174950572</x:v>
-      </x:c>
-      <x:c r="M1307" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1308" ht="18" customHeight="1">
-      <x:c r="A1308" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1308" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1308" s="2" t="str">
-        <x:v>Exchange/demand reactions</x:v>
-      </x:c>
-      <x:c r="D1308" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1308" s="2" t="n">
-        <x:v>1658</x:v>
-      </x:c>
-      <x:c r="F1308" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1308" s="2" t="n">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="H1308" s="2" t="n">
-        <x:v>91.18790533142425</x:v>
-      </x:c>
-      <x:c r="I1308" s="2" t="n">
-        <x:v>1.1843675935692553</x:v>
-      </x:c>
-      <x:c r="J1308" s="2" t="n">
-        <x:v>0.03108463754156427</x:v>
-      </x:c>
-      <x:c r="K1308" s="2" t="str">
-        <x:v>MAR00569;MAR00574;MAR00628;MAR00656;MAR00658;MAR00661;MAR00714;MAR01871;MAR01922;MAR01939;MAR04110;MAR04146;MAR04181;MAR04384;MAR04859;MAR04886;MAR04889;MAR04899;MAR08966;MAR09038;MAR09039;MAR09040;MAR09041;MAR09042;MAR09043;MAR09044;MAR09045;MAR09046;MAR09047;MAR09048;MAR09058;MAR09062;MAR09063;MAR09064;MAR09066;MAR09067;MAR09068;MAR09069;MAR09070;MAR09072;MAR09076;MAR09079;MAR09103;MAR09107;MAR09108;MAR09109;MAR09143;MAR09146;MAR09151;MAR09153;MAR09172;MAR09209;MAR09215;MAR09242;MAR09253;MAR09254;MAR09255;MAR09259;MAR09269;MAR09271;MAR09273;MAR09292;MAR09298;MAR09300;MAR09353;MAR09354;MAR09360;MAR09363;MAR09378;MAR09383;MAR09404;MAR09406;MAR09437;MAR09440;MAR09702;MAR09729;MAR09847;MAR09849;MAR09858;MAR09860;MAR09861;MAR09862;MAR09864;MAR09868;MAR09920;MAR09921;MAR09925;MAR10024;MAR10047;MAR10188;MAR10193;MAR10195;MAR10197;MAR10202;MAR10222;MAR10243;MAR10250;MAR10254;MAR10496;MAR11400;MAR11424;MAR11428;MAR11895;MAR11897;MAR11947;MAR11953;MAR11974;MAR12127</x:v>
-      </x:c>
-      <x:c r="L1308" s="2" t="n">
-        <x:v>0.20620935608558832</x:v>
-      </x:c>
-      <x:c r="M1308" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1309" ht="18" customHeight="1">
-      <x:c r="A1309" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1309" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1309" s="2" t="str">
-        <x:v>Extracellular transport</x:v>
-      </x:c>
-      <x:c r="D1309" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1309" s="2" t="n">
-        <x:v>2575</x:v>
-      </x:c>
-      <x:c r="F1309" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1309" s="2" t="n">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="H1309" s="2" t="n">
-        <x:v>141.62174682051713</x:v>
-      </x:c>
-      <x:c r="I1309" s="2" t="n">
-        <x:v>0.8473274952051028</x:v>
-      </x:c>
-      <x:c r="J1309" s="2" t="n">
-        <x:v>0.9858733410923252</x:v>
-      </x:c>
-      <x:c r="K1309" s="2" t="str">
-        <x:v>MAR00019;MAR00142;MAR01499;MAR01525;MAR01534;MAR01601;MAR01607;MAR01669;MAR01827;MAR02351;MAR02382;MAR03951;MAR03959;MAR04847;MAR04882;MAR04896;MAR04919;MAR04947;MAR04948;MAR04958;MAR04969;MAR04985;MAR04990;MAR05023;MAR05032;MAR05068;MAR05071;MAR05074;MAR05076;MAR05080;MAR05082;MAR05085;MAR05088;MAR05089;MAR05091;MAR05206;MAR05303;MAR05448;MAR05471;MAR05498;MAR05510;MAR05521;MAR05548;MAR05566;MAR05570;MAR05575;MAR05577;MAR05969;MAR05987;MAR06058;MAR06072;MAR06090;MAR06095;MAR06250;MAR06366;MAR06383;MAR06462;MAR06474;MAR06505;MAR06512;MAR07609;MAR07735;MAR07781;MAR07811;MAR07819;MAR08010;MAR08408;MAR08612;MAR08676;MAR08687;MAR08720;MAR08721;MAR09112;MAR09609;MAR09637;MAR09641;MAR09650;MAR09728;MAR09824;MAR09825;MAR09827;MAR09828;MAR09830;MAR09833;MAR09834;MAR09835;MAR09836;MAR09837;MAR09838;MAR09839;MAR09883;MAR09884;MAR09913;MAR09975;MAR09983;MAR09989;MAR09996;MAR10004;MAR10023;MAR10046;MAR10159;MAR10363;MAR10364;MAR10366;MAR10375;MAR10383;MAR10489;MAR11250;MAR11252;MAR11256;MAR11257;MAR11261;MAR11276;MAR11583;MAR11787;MAR11894;MAR11896;MAR11973;MAR12306;MAR12307</x:v>
-      </x:c>
-      <x:c r="L1309" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1309" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1310" ht="18" customHeight="1">
-      <x:c r="A1310" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1310" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1310" s="2" t="str">
-        <x:v>Fatty acid activation (cytosolic)</x:v>
-      </x:c>
-      <x:c r="D1310" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1310" s="2" t="n">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="F1310" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1310" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1310" s="2" t="n">
-        <x:v>3.684915354164912</x:v>
-      </x:c>
-      <x:c r="I1310" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1310" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1310" s="2"/>
-      <x:c r="L1310" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1310" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1311" ht="18" customHeight="1">
-      <x:c r="A1311" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1311" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1311" s="2" t="str">
-        <x:v>Fatty acid activation (endoplasmic reticular)</x:v>
-      </x:c>
-      <x:c r="D1311" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1311" s="2" t="n">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="F1311" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1311" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1311" s="2" t="n">
-        <x:v>3.0249305146129872</x:v>
-      </x:c>
-      <x:c r="I1311" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1311" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1311" s="2"/>
-      <x:c r="L1311" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1311" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1312" ht="18" customHeight="1">
-      <x:c r="A1312" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1312" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1312" s="2" t="str">
-        <x:v>Fatty acid biosynthesis</x:v>
-      </x:c>
-      <x:c r="D1312" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1312" s="2" t="n">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="F1312" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1312" s="2" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H1312" s="2" t="n">
-        <x:v>3.849911564052893</x:v>
-      </x:c>
-      <x:c r="I1312" s="2" t="n">
-        <x:v>2.0779698096696566</x:v>
-      </x:c>
-      <x:c r="J1312" s="2" t="n">
-        <x:v>0.03757921832979448</x:v>
-      </x:c>
-      <x:c r="K1312" s="2" t="str">
-        <x:v>MAR00144;MAR00148;MAR00152;MAR00181;MAR00743;MAR00747;MAR02150;MAR02151</x:v>
-      </x:c>
-      <x:c r="L1312" s="2" t="n">
-        <x:v>0.2424631757990849</x:v>
-      </x:c>
-      <x:c r="M1312" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1313" ht="18" customHeight="1">
-      <x:c r="A1313" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1313" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1313" s="2" t="str">
-        <x:v>Fatty acid biosynthesis (even-chain)</x:v>
-      </x:c>
-      <x:c r="D1313" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1313" s="2" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F1313" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1313" s="2" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="H1313" s="2" t="n">
-        <x:v>1.7599595721384653</x:v>
-      </x:c>
-      <x:c r="I1313" s="2" t="n">
-        <x:v>6.818338437978561</x:v>
-      </x:c>
-      <x:c r="J1313" s="2" t="n">
-        <x:v>5.6597176462084945e-8</x:v>
-      </x:c>
-      <x:c r="K1313" s="2" t="str">
-        <x:v>MAR02152;MAR02153;MAR02154;MAR02155;MAR02156;MAR02157;MAR02158;MAR02159;MAR02160;MAR02161;MAR02162;MAR02163</x:v>
-      </x:c>
-      <x:c r="L1313" s="2" t="n">
-        <x:v>0.0000010522606623806055</x:v>
-      </x:c>
-      <x:c r="M1313" s="3" t="b">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1314" ht="18" customHeight="1">
-      <x:c r="A1314" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1314" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1314" s="2" t="str">
-        <x:v>Fatty acid biosynthesis (odd-chain)</x:v>
-      </x:c>
-      <x:c r="D1314" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1314" s="2" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F1314" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1314" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1314" s="2" t="n">
-        <x:v>1.5949633622504842</x:v>
-      </x:c>
-      <x:c r="I1314" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1314" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1314" s="2"/>
-      <x:c r="L1314" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1314" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1315" ht="18" customHeight="1">
-      <x:c r="A1315" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1315" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1315" s="2" t="str">
-        <x:v>Fatty acid biosynthesis (unsaturated)</x:v>
-      </x:c>
-      <x:c r="D1315" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1315" s="2" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F1315" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1315" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1315" s="2" t="n">
-        <x:v>1.7599595721384653</x:v>
-      </x:c>
-      <x:c r="I1315" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1315" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1315" s="2"/>
-      <x:c r="L1315" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1315" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1316" ht="18" customHeight="1">
-      <x:c r="A1316" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1316" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1316" s="2" t="str">
-        <x:v>Fatty acid degradation</x:v>
-      </x:c>
-      <x:c r="D1316" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1316" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F1316" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1316" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1316" s="2" t="n">
-        <x:v>0.05499873662932704</x:v>
-      </x:c>
-      <x:c r="I1316" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1316" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1316" s="2"/>
-      <x:c r="L1316" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1316" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1317" ht="18" customHeight="1">
-      <x:c r="A1317" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1317" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1317" s="2" t="str">
-        <x:v>Fatty acid desaturation (even-chain)</x:v>
-      </x:c>
-      <x:c r="D1317" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1317" s="2" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F1317" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1317" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1317" s="2" t="n">
-        <x:v>0.6599848395519246</x:v>
-      </x:c>
-      <x:c r="I1317" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1317" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1317" s="2"/>
-      <x:c r="L1317" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1317" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1318" ht="18" customHeight="1">
-      <x:c r="A1318" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1318" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1318" s="2" t="str">
-        <x:v>Fatty acid desaturation (odd-chain)</x:v>
-      </x:c>
-      <x:c r="D1318" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1318" s="2" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F1318" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1318" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1318" s="2" t="n">
-        <x:v>0.10999747325865408</x:v>
-      </x:c>
-      <x:c r="I1318" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1318" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1318" s="2"/>
-      <x:c r="L1318" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1318" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1319" ht="18" customHeight="1">
-      <x:c r="A1319" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1319" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1319" s="2" t="str">
-        <x:v>Fatty acid elongation (even-chain)</x:v>
-      </x:c>
-      <x:c r="D1319" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1319" s="2" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F1319" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1319" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H1319" s="2" t="n">
-        <x:v>1.154973469215868</x:v>
-      </x:c>
-      <x:c r="I1319" s="2" t="n">
-        <x:v>0.8658207540290236</x:v>
-      </x:c>
-      <x:c r="J1319" s="2" t="n">
-        <x:v>0.6954682462000511</x:v>
-      </x:c>
-      <x:c r="K1319" s="2" t="str">
-        <x:v>MAR02194</x:v>
-      </x:c>
-      <x:c r="L1319" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1319" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1320" ht="18" customHeight="1">
-      <x:c r="A1320" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1320" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1320" s="2" t="str">
-        <x:v>Fatty acid elongation (odd-chain)</x:v>
-      </x:c>
-      <x:c r="D1320" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1320" s="2" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F1320" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1320" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1320" s="2" t="n">
-        <x:v>0.6599848395519246</x:v>
-      </x:c>
-      <x:c r="I1320" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1320" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1320" s="2"/>
-      <x:c r="L1320" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1320" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1321" ht="18" customHeight="1">
-      <x:c r="A1321" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1321" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1321" s="2" t="str">
-        <x:v>Fatty acid metabolism</x:v>
-      </x:c>
-      <x:c r="D1321" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1321" s="2" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F1321" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1321" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1321" s="2" t="n">
-        <x:v>1.9249557820264465</x:v>
-      </x:c>
-      <x:c r="I1321" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1321" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1321" s="2"/>
-      <x:c r="L1321" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1321" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1322" ht="18" customHeight="1">
-      <x:c r="A1322" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1322" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1322" s="2" t="str">
-        <x:v>Fatty acid oxidation</x:v>
-      </x:c>
-      <x:c r="D1322" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1322" s="2" t="n">
-        <x:v>393</x:v>
-      </x:c>
-      <x:c r="F1322" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1322" s="2" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H1322" s="2" t="n">
-        <x:v>21.61450349532553</x:v>
-      </x:c>
-      <x:c r="I1322" s="2" t="n">
-        <x:v>0.693978466969828</x:v>
-      </x:c>
-      <x:c r="J1322" s="2" t="n">
-        <x:v>0.9516171447616222</x:v>
-      </x:c>
-      <x:c r="K1322" s="2" t="str">
-        <x:v>MAR00112;MAR02121;MAR02148;MAR02187;MAR02207;MAR03371;MAR03437;MAR03438;MAR04003;MAR04457;MAR04719;MAR04967;MAR04970;MAR05449;MAR06279</x:v>
-      </x:c>
-      <x:c r="L1322" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1322" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1323" ht="18" customHeight="1">
-      <x:c r="A1323" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1323" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1323" s="2" t="str">
-        <x:v>Folate metabolism</x:v>
-      </x:c>
-      <x:c r="D1323" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1323" s="2" t="n">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F1323" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1323" s="2" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H1323" s="2" t="n">
-        <x:v>2.364945675061063</x:v>
-      </x:c>
-      <x:c r="I1323" s="2" t="n">
-        <x:v>2.1142134691406387</x:v>
-      </x:c>
-      <x:c r="J1323" s="2" t="n">
-        <x:v>0.08543365705053253</x:v>
-      </x:c>
-      <x:c r="K1323" s="2" t="str">
-        <x:v>MAR04332;MAR04333;MAR04335;MAR04655;MAR04656</x:v>
-      </x:c>
-      <x:c r="L1323" s="2" t="n">
-        <x:v>0.4715537398921971</x:v>
-      </x:c>
-      <x:c r="M1323" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1324" ht="18" customHeight="1">
-      <x:c r="A1324" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1324" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1324" s="2" t="str">
-        <x:v>Formation and hydrolysis of cholesterol esters</x:v>
-      </x:c>
-      <x:c r="D1324" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1324" s="2" t="n">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="F1324" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1324" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1324" s="2" t="n">
-        <x:v>9.84477385664954</x:v>
-      </x:c>
-      <x:c r="I1324" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1324" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1324" s="2"/>
-      <x:c r="L1324" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1324" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1325" ht="18" customHeight="1">
-      <x:c r="A1325" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1325" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1325" s="2" t="str">
-        <x:v>Fructose and mannose metabolism</x:v>
-      </x:c>
-      <x:c r="D1325" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1325" s="2" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F1325" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1325" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1325" s="2" t="n">
-        <x:v>1.209972205845195</x:v>
-      </x:c>
-      <x:c r="I1325" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1325" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1325" s="2"/>
-      <x:c r="L1325" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1325" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1326" ht="18" customHeight="1">
-      <x:c r="A1326" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1326" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1326" s="2" t="str">
-        <x:v>Galactose metabolism</x:v>
-      </x:c>
-      <x:c r="D1326" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1326" s="2" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F1326" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1326" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1326" s="2" t="n">
-        <x:v>1.154973469215868</x:v>
-      </x:c>
-      <x:c r="I1326" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1326" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1326" s="2"/>
-      <x:c r="L1326" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1326" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1327" ht="18" customHeight="1">
-      <x:c r="A1327" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1327" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1327" s="2" t="str">
-        <x:v>Glucocorticoid biosynthesis</x:v>
-      </x:c>
-      <x:c r="D1327" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1327" s="2" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F1327" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1327" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1327" s="2" t="n">
-        <x:v>0.3299924197759623</x:v>
-      </x:c>
-      <x:c r="I1327" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1327" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1327" s="2"/>
-      <x:c r="L1327" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1327" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1328" ht="18" customHeight="1">
-      <x:c r="A1328" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1328" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1328" s="2" t="str">
-        <x:v>Glutathione metabolism</x:v>
-      </x:c>
-      <x:c r="D1328" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1328" s="2" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F1328" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1328" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1328" s="2" t="n">
-        <x:v>0.9349785226985597</x:v>
-      </x:c>
-      <x:c r="I1328" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1328" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1328" s="2"/>
-      <x:c r="L1328" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1328" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1329" ht="18" customHeight="1">
-      <x:c r="A1329" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1329" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1329" s="2" t="str">
-        <x:v>Glycerolipid metabolism</x:v>
-      </x:c>
-      <x:c r="D1329" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1329" s="2" t="n">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="F1329" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1329" s="2" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H1329" s="2" t="n">
-        <x:v>4.179903983828855</x:v>
-      </x:c>
-      <x:c r="I1329" s="2" t="n">
-        <x:v>0.7177198355766906</x:v>
-      </x:c>
-      <x:c r="J1329" s="2" t="n">
-        <x:v>0.7961973829512988</x:v>
-      </x:c>
-      <x:c r="K1329" s="2" t="str">
-        <x:v>MAR00588;MAR00675;MAR07599</x:v>
-      </x:c>
-      <x:c r="L1329" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1329" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1330" ht="18" customHeight="1">
-      <x:c r="A1330" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1330" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1330" s="2" t="str">
-        <x:v>Glycerophospholipid metabolism</x:v>
-      </x:c>
-      <x:c r="D1330" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1330" s="2" t="n">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="F1330" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1330" s="2" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="H1330" s="2" t="n">
-        <x:v>4.784890086751453</x:v>
-      </x:c>
-      <x:c r="I1330" s="2" t="n">
-        <x:v>2.5078945978771716</x:v>
-      </x:c>
-      <x:c r="J1330" s="2" t="n">
-        <x:v>0.0027747160591384775</x:v>
-      </x:c>
-      <x:c r="K1330" s="2" t="str">
-        <x:v>MAR00129;MAR00579;MAR00580;MAR00581;MAR00598;MAR00632;MAR00643;MAR00651;MAR07591;MAR07594;MAR07597;MAR07601</x:v>
-      </x:c>
-      <x:c r="L1330" s="2" t="n">
-        <x:v>0.024658325733098545</x:v>
-      </x:c>
-      <x:c r="M1330" s="3" t="b">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1331" ht="18" customHeight="1">
-      <x:c r="A1331" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1331" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1331" s="2" t="str">
-        <x:v>Glycine, serine and threonine metabolism</x:v>
-      </x:c>
-      <x:c r="D1331" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1331" s="2" t="n">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="F1331" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1331" s="2" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H1331" s="2" t="n">
-        <x:v>2.9149330413543333</x:v>
-      </x:c>
-      <x:c r="I1331" s="2" t="n">
-        <x:v>1.3722442139327922</x:v>
-      </x:c>
-      <x:c r="J1331" s="2" t="n">
-        <x:v>0.33303723865819196</x:v>
-      </x:c>
-      <x:c r="K1331" s="2" t="str">
-        <x:v>MAR03845;MAR04199;MAR04584;MAR06409</x:v>
-      </x:c>
-      <x:c r="L1331" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1331" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1332" ht="18" customHeight="1">
-      <x:c r="A1332" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1332" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1332" s="2" t="str">
-        <x:v>Glycolysis / Gluconeogenesis</x:v>
-      </x:c>
-      <x:c r="D1332" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1332" s="2" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="F1332" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1332" s="2" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H1332" s="2" t="n">
-        <x:v>1.9799545186557737</x:v>
-      </x:c>
-      <x:c r="I1332" s="2" t="n">
-        <x:v>3.5354347456185127</x:v>
-      </x:c>
-      <x:c r="J1332" s="2" t="n">
-        <x:v>0.003040978517631495</x:v>
-      </x:c>
-      <x:c r="K1332" s="2" t="str">
-        <x:v>MAR04358;MAR04368;MAR04373;MAR04375;MAR04391;MAR06412;MAR20069</x:v>
-      </x:c>
-      <x:c r="L1332" s="2" t="n">
-        <x:v>0.026855641533833144</x:v>
-      </x:c>
-      <x:c r="M1332" s="3" t="b">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1333" ht="18" customHeight="1">
-      <x:c r="A1333" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1333" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1333" s="2" t="str">
-        <x:v>Glycosphingolipid biosynthesis-ganglio series</x:v>
-      </x:c>
-      <x:c r="D1333" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1333" s="2" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F1333" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1333" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1333" s="2" t="n">
-        <x:v>0.43998989303461633</x:v>
-      </x:c>
-      <x:c r="I1333" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1333" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1333" s="2"/>
-      <x:c r="L1333" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1333" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1334" ht="18" customHeight="1">
-      <x:c r="A1334" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1334" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1334" s="2" t="str">
-        <x:v>Glycosphingolipid biosynthesis-globo series</x:v>
-      </x:c>
-      <x:c r="D1334" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1334" s="2" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F1334" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1334" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1334" s="2" t="n">
-        <x:v>0.3849911564052893</x:v>
-      </x:c>
-      <x:c r="I1334" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1334" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1334" s="2"/>
-      <x:c r="L1334" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1334" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1335" ht="18" customHeight="1">
-      <x:c r="A1335" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1335" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1335" s="2" t="str">
-        <x:v>Glycosphingolipid biosynthesis-lacto and neolacto series</x:v>
-      </x:c>
-      <x:c r="D1335" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1335" s="2" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="F1335" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1335" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1335" s="2" t="n">
-        <x:v>1.9799545186557737</x:v>
-      </x:c>
-      <x:c r="I1335" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1335" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1335" s="2"/>
-      <x:c r="L1335" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1335" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1336" ht="18" customHeight="1">
-      <x:c r="A1336" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1336" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1336" s="2" t="str">
-        <x:v>Glycosphingolipid metabolism</x:v>
-      </x:c>
-      <x:c r="D1336" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1336" s="2" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F1336" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1336" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1336" s="2" t="n">
-        <x:v>0.9349785226985597</x:v>
-      </x:c>
-      <x:c r="I1336" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1336" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1336" s="2"/>
-      <x:c r="L1336" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1336" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1337" ht="18" customHeight="1">
-      <x:c r="A1337" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1337" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1337" s="2" t="str">
-        <x:v>Glycosylphosphatidylinositol (GPI)-anchor biosynthesis</x:v>
-      </x:c>
-      <x:c r="D1337" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1337" s="2" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F1337" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1337" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1337" s="2" t="n">
-        <x:v>1.4849658889918302</x:v>
-      </x:c>
-      <x:c r="I1337" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1337" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1337" s="2"/>
-      <x:c r="L1337" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1337" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1338" ht="18" customHeight="1">
-      <x:c r="A1338" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1338" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1338" s="2" t="str">
-        <x:v>Glyoxylate and dicarboxylate metabolism</x:v>
-      </x:c>
-      <x:c r="D1338" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1338" s="2" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F1338" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1338" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1338" s="2" t="n">
-        <x:v>0.16499620988798114</x:v>
-      </x:c>
-      <x:c r="I1338" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1338" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1338" s="2"/>
-      <x:c r="L1338" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1338" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1339" ht="18" customHeight="1">
-      <x:c r="A1339" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1339" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1339" s="2" t="str">
-        <x:v>Golgi transport</x:v>
-      </x:c>
-      <x:c r="D1339" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1339" s="2" t="n">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="F1339" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1339" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1339" s="2" t="n">
-        <x:v>6.269855975743283</x:v>
-      </x:c>
-      <x:c r="I1339" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1339" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1339" s="2"/>
-      <x:c r="L1339" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1339" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1340" ht="18" customHeight="1">
-      <x:c r="A1340" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1340" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1340" s="2" t="str">
-        <x:v>Heme degradation</x:v>
-      </x:c>
-      <x:c r="D1340" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1340" s="2" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F1340" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1340" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1340" s="2" t="n">
-        <x:v>0.10999747325865408</x:v>
-      </x:c>
-      <x:c r="I1340" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1340" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1340" s="2"/>
-      <x:c r="L1340" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1340" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1341" ht="18" customHeight="1">
-      <x:c r="A1341" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1341" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1341" s="2" t="str">
-        <x:v>Heparan sulfate degradation</x:v>
-      </x:c>
-      <x:c r="D1341" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1341" s="2" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F1341" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1341" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1341" s="2" t="n">
-        <x:v>0.6049861029225975</x:v>
-      </x:c>
-      <x:c r="I1341" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1341" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1341" s="2"/>
-      <x:c r="L1341" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1341" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1342" ht="18" customHeight="1">
-      <x:c r="A1342" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1342" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1342" s="2" t="str">
-        <x:v>Hippurate metabolism</x:v>
-      </x:c>
-      <x:c r="D1342" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1342" s="2" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F1342" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1342" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1342" s="2" t="n">
-        <x:v>0.10999747325865408</x:v>
-      </x:c>
-      <x:c r="I1342" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1342" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1342" s="2"/>
-      <x:c r="L1342" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1342" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1343" ht="18" customHeight="1">
-      <x:c r="A1343" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1343" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1343" s="2" t="str">
-        <x:v>Histidine metabolism</x:v>
-      </x:c>
-      <x:c r="D1343" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1343" s="2" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F1343" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1343" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H1343" s="2" t="n">
-        <x:v>0.8249810494399057</x:v>
-      </x:c>
-      <x:c r="I1343" s="2" t="n">
-        <x:v>1.212149055640633</x:v>
-      </x:c>
-      <x:c r="J1343" s="2" t="n">
-        <x:v>0.5721789783380324</x:v>
-      </x:c>
-      <x:c r="K1343" s="2" t="str">
-        <x:v>MAR09939</x:v>
-      </x:c>
-      <x:c r="L1343" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1343" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1344" ht="18" customHeight="1">
-      <x:c r="A1344" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1344" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1344" s="2" t="str">
-        <x:v>Inositol phosphate metabolism</x:v>
-      </x:c>
-      <x:c r="D1344" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1344" s="2" t="n">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="F1344" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1344" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1344" s="2" t="n">
-        <x:v>4.619893876863472</x:v>
-      </x:c>
-      <x:c r="I1344" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1344" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1344" s="2"/>
-      <x:c r="L1344" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1344" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1345" ht="18" customHeight="1">
-      <x:c r="A1345" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1345" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1345" s="2" t="str">
-        <x:v>Insect hormone biosynthesis</x:v>
-      </x:c>
-      <x:c r="D1345" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1345" s="2" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F1345" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1345" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1345" s="2" t="n">
-        <x:v>0.10999747325865408</x:v>
-      </x:c>
-      <x:c r="I1345" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1345" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1345" s="2"/>
-      <x:c r="L1345" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1345" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1346" ht="18" customHeight="1">
-      <x:c r="A1346" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1346" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1346" s="2" t="str">
-        <x:v>Intracellular transport</x:v>
-      </x:c>
-      <x:c r="D1346" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1346" s="2" t="n">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="F1346" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1346" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H1346" s="2" t="n">
-        <x:v>3.0799292512423144</x:v>
-      </x:c>
-      <x:c r="I1346" s="2" t="n">
-        <x:v>0.32468278276088386</x:v>
-      </x:c>
-      <x:c r="J1346" s="2" t="n">
-        <x:v>0.9582241960544965</x:v>
-      </x:c>
-      <x:c r="K1346" s="2" t="str">
-        <x:v>MAR03597</x:v>
-      </x:c>
-      <x:c r="L1346" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1346" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1347" ht="18" customHeight="1">
-      <x:c r="A1347" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1347" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1347" s="2" t="str">
-        <x:v>Isolated</x:v>
-      </x:c>
-      <x:c r="D1347" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1347" s="2" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="F1347" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1347" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1347" s="2" t="n">
-        <x:v>7.149835761812516</x:v>
-      </x:c>
-      <x:c r="I1347" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1347" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1347" s="2"/>
-      <x:c r="L1347" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1347" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1348" ht="18" customHeight="1">
-      <x:c r="A1348" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1348" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1348" s="2" t="str">
-        <x:v>Keratan sulfate biosynthesis</x:v>
-      </x:c>
-      <x:c r="D1348" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1348" s="2" t="n">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F1348" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1348" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1348" s="2" t="n">
-        <x:v>2.0899519919144276</x:v>
-      </x:c>
-      <x:c r="I1348" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1348" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1348" s="2"/>
-      <x:c r="L1348" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1348" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1349" ht="18" customHeight="1">
-      <x:c r="A1349" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1349" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1349" s="2" t="str">
-        <x:v>Keratan sulfate degradation</x:v>
-      </x:c>
-      <x:c r="D1349" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1349" s="2" t="n">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="F1349" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1349" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1349" s="2" t="n">
-        <x:v>4.179903983828855</x:v>
-      </x:c>
-      <x:c r="I1349" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1349" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1349" s="2"/>
-      <x:c r="L1349" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1349" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1350" ht="18" customHeight="1">
-      <x:c r="A1350" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1350" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1350" s="2" t="str">
-        <x:v>Leukotriene metabolism</x:v>
-      </x:c>
-      <x:c r="D1350" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1350" s="2" t="n">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="F1350" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1350" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1350" s="2" t="n">
-        <x:v>7.974816811252421</x:v>
-      </x:c>
-      <x:c r="I1350" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1350" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1350" s="2"/>
-      <x:c r="L1350" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1350" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1351" ht="18" customHeight="1">
-      <x:c r="A1351" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1351" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1351" s="2" t="str">
-        <x:v>Linoleate metabolism</x:v>
-      </x:c>
-      <x:c r="D1351" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1351" s="2" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F1351" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1351" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1351" s="2" t="n">
-        <x:v>1.8149583087677925</x:v>
-      </x:c>
-      <x:c r="I1351" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1351" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1351" s="2"/>
-      <x:c r="L1351" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1351" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1352" ht="18" customHeight="1">
-      <x:c r="A1352" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1352" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1352" s="2" t="str">
-        <x:v>Lipoic acid metabolism</x:v>
-      </x:c>
-      <x:c r="D1352" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1352" s="2" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F1352" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1352" s="2" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H1352" s="2" t="n">
-        <x:v>0.21999494651730817</x:v>
-      </x:c>
-      <x:c r="I1352" s="2" t="n">
-        <x:v>13.636676875957122</x:v>
-      </x:c>
-      <x:c r="J1352" s="2" t="n">
-        <x:v>0.0006353558546654095</x:v>
-      </x:c>
-      <x:c r="K1352" s="2" t="str">
-        <x:v>MAR06397;MAR06402;MAR06403</x:v>
-      </x:c>
-      <x:c r="L1352" s="2" t="n">
-        <x:v>0.006699685243598684</x:v>
-      </x:c>
-      <x:c r="M1352" s="3" t="b">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1353" ht="18" customHeight="1">
-      <x:c r="A1353" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1353" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1353" s="2" t="str">
-        <x:v>Lysine metabolism</x:v>
-      </x:c>
-      <x:c r="D1353" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1353" s="2" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F1353" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1353" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H1353" s="2" t="n">
-        <x:v>2.199949465173082</x:v>
-      </x:c>
-      <x:c r="I1353" s="2" t="n">
-        <x:v>0.4545558958652373</x:v>
-      </x:c>
-      <x:c r="J1353" s="2" t="n">
-        <x:v>0.8963352116522223</x:v>
-      </x:c>
-      <x:c r="K1353" s="2" t="str">
-        <x:v>MAR09952</x:v>
-      </x:c>
-      <x:c r="L1353" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1353" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1354" ht="18" customHeight="1">
-      <x:c r="A1354" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1354" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1354" s="2" t="str">
-        <x:v>Lysosomal transport</x:v>
-      </x:c>
-      <x:c r="D1354" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1354" s="2" t="n">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="F1354" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1354" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1354" s="2" t="n">
-        <x:v>9.899772593278868</x:v>
-      </x:c>
-      <x:c r="I1354" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1354" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1354" s="2"/>
-      <x:c r="L1354" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1354" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1355" ht="18" customHeight="1">
-      <x:c r="A1355" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1355" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1355" s="2" t="str">
-        <x:v>Metabolism of other amino acids</x:v>
-      </x:c>
-      <x:c r="D1355" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1355" s="2" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F1355" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1355" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1355" s="2" t="n">
-        <x:v>1.2649709424745221</x:v>
-      </x:c>
-      <x:c r="I1355" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1355" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1355" s="2"/>
-      <x:c r="L1355" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1355" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1356" ht="18" customHeight="1">
-      <x:c r="A1356" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1356" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1356" s="2" t="str">
-        <x:v>Miscellaneous</x:v>
-      </x:c>
-      <x:c r="D1356" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1356" s="2" t="n">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="F1356" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1356" s="2" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H1356" s="2" t="n">
-        <x:v>4.234902720458183</x:v>
-      </x:c>
-      <x:c r="I1356" s="2" t="n">
-        <x:v>0.9445317316680256</x:v>
-      </x:c>
-      <x:c r="J1356" s="2" t="n">
-        <x:v>0.6181669849834102</x:v>
-      </x:c>
-      <x:c r="K1356" s="2" t="str">
-        <x:v>MAR02186;MAR03955;MAR08617;MAR20110</x:v>
-      </x:c>
-      <x:c r="L1356" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1356" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1357" ht="18" customHeight="1">
-      <x:c r="A1357" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1357" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1357" s="2" t="str">
-        <x:v>Mitochondrial transport</x:v>
-      </x:c>
-      <x:c r="D1357" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1357" s="2" t="n">
-        <x:v>480</x:v>
-      </x:c>
-      <x:c r="F1357" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1357" s="2" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H1357" s="2" t="n">
-        <x:v>26.399393582076982</x:v>
-      </x:c>
-      <x:c r="I1357" s="2" t="n">
-        <x:v>1.893982899438489</x:v>
-      </x:c>
-      <x:c r="J1357" s="2" t="n">
-        <x:v>0.000009195101940453136</x:v>
-      </x:c>
-      <x:c r="K1357" s="2" t="str">
-        <x:v>MAR00061;MAR00158;MAR00182;MAR00578;MAR02225;MAR02379;MAR03789;MAR03946;MAR03952;MAR04756;MAR04852;MAR04855;MAR04874;MAR04898;MAR04905;MAR04914;MAR04922;MAR04963;MAR05006;MAR05043;MAR05115;MAR05116;MAR05126;MAR05227;MAR05304;MAR05361;MAR05420;MAR06328;MAR06438;MAR06454;MAR06469;MAR06481;MAR06513;MAR07638;MAR08009;MAR08428;MAR08430;MAR08614;MAR08891;MAR08987;MAR08998;MAR10049;MAR11443;MAR13080;MAR20137;MAR20139;MAR20149;MAR20156;MAR20160;MAR20164</x:v>
-      </x:c>
-      <x:c r="L1357" s="2" t="n">
-        <x:v>0.0001353404066860446</x:v>
-      </x:c>
-      <x:c r="M1357" s="3" t="b">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1358" ht="18" customHeight="1">
-      <x:c r="A1358" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1358" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1358" s="2" t="str">
-        <x:v>N-glycan metabolism</x:v>
-      </x:c>
-      <x:c r="D1358" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1358" s="2" t="n">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="F1358" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1358" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1358" s="2" t="n">
-        <x:v>4.894887560010107</x:v>
-      </x:c>
-      <x:c r="I1358" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1358" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1358" s="2"/>
-      <x:c r="L1358" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1358" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1359" ht="18" customHeight="1">
-      <x:c r="A1359" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1359" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1359" s="2" t="str">
-        <x:v>Nicotinate and nicotinamide metabolism</x:v>
-      </x:c>
-      <x:c r="D1359" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1359" s="2" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F1359" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1359" s="2" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H1359" s="2" t="n">
-        <x:v>1.5949633622504842</x:v>
-      </x:c>
-      <x:c r="I1359" s="2" t="n">
-        <x:v>2.507894597877172</x:v>
-      </x:c>
-      <x:c r="J1359" s="2" t="n">
-        <x:v>0.07236009533972428</x:v>
-      </x:c>
-      <x:c r="K1359" s="2" t="str">
-        <x:v>MAR01542;MAR04265;MAR04269;MAR08791</x:v>
-      </x:c>
-      <x:c r="L1359" s="2" t="n">
-        <x:v>0.4122774786896387</x:v>
-      </x:c>
-      <x:c r="M1359" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1360" ht="18" customHeight="1">
-      <x:c r="A1360" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1360" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1360" s="2" t="str">
-        <x:v>Nuclear transport</x:v>
-      </x:c>
-      <x:c r="D1360" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1360" s="2" t="n">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="F1360" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1360" s="2" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="H1360" s="2" t="n">
-        <x:v>5.169881243156742</x:v>
-      </x:c>
-      <x:c r="I1360" s="2" t="n">
-        <x:v>2.5145645303183346</x:v>
-      </x:c>
-      <x:c r="J1360" s="2" t="n">
-        <x:v>0.0018365276680507095</x:v>
-      </x:c>
-      <x:c r="K1360" s="2" t="str">
-        <x:v>MAR01095;MAR05422;MAR05423;MAR07765;MAR07767;MAR07786;MAR07792;MAR07796;MAR07857;MAR07860;MAR07861;MAR07862;MAR13086</x:v>
-      </x:c>
-      <x:c r="L1360" s="2" t="n">
-        <x:v>0.016850737629582162</x:v>
-      </x:c>
-      <x:c r="M1360" s="3" t="b">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1361" ht="18" customHeight="1">
-      <x:c r="A1361" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1361" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1361" s="2" t="str">
-        <x:v>Nucleotide metabolism</x:v>
-      </x:c>
-      <x:c r="D1361" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1361" s="2" t="n">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="F1361" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1361" s="2" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H1361" s="2" t="n">
-        <x:v>5.884864819337993</x:v>
-      </x:c>
-      <x:c r="I1361" s="2" t="n">
-        <x:v>2.7188390033060927</x:v>
-      </x:c>
-      <x:c r="J1361" s="2" t="n">
-        <x:v>0.00023416937791764875</x:v>
-      </x:c>
-      <x:c r="K1361" s="2" t="str">
-        <x:v>MAR03967;MAR03968;MAR04024;MAR04344;MAR07160;MAR07161;MAR07863;MAR07865;MAR07869;MAR07871;MAR07886;MAR08452;MAR08456;MAR08463;MAR08482;MAR08486</x:v>
-      </x:c>
-      <x:c r="L1361" s="2" t="n">
-        <x:v>0.0028772289651968494</x:v>
-      </x:c>
-      <x:c r="M1361" s="3" t="b">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1362" ht="18" customHeight="1">
-      <x:c r="A1362" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1362" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1362" s="2" t="str">
-        <x:v>O-glycan metabolism</x:v>
-      </x:c>
-      <x:c r="D1362" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1362" s="2" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F1362" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1362" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1362" s="2" t="n">
-        <x:v>0.7699823128105786</x:v>
-      </x:c>
-      <x:c r="I1362" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1362" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1362" s="2"/>
-      <x:c r="L1362" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1362" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1363" ht="18" customHeight="1">
-      <x:c r="A1363" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1363" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1363" s="2" t="str">
-        <x:v>Octane oxidation</x:v>
-      </x:c>
-      <x:c r="D1363" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1363" s="2" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F1363" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1363" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1363" s="2" t="n">
-        <x:v>0.10999747325865408</x:v>
-      </x:c>
-      <x:c r="I1363" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1363" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1363" s="2"/>
-      <x:c r="L1363" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1363" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1364" ht="18" customHeight="1">
-      <x:c r="A1364" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1364" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1364" s="2" t="str">
-        <x:v>Omega-3 fatty acid metabolism</x:v>
-      </x:c>
-      <x:c r="D1364" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1364" s="2" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="F1364" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1364" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1364" s="2" t="n">
-        <x:v>3.2999241977596228</x:v>
-      </x:c>
-      <x:c r="I1364" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1364" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1364" s="2"/>
-      <x:c r="L1364" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1364" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1365" ht="18" customHeight="1">
-      <x:c r="A1365" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1365" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1365" s="2" t="str">
-        <x:v>Omega-6 fatty acid metabolism</x:v>
-      </x:c>
-      <x:c r="D1365" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1365" s="2" t="n">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="F1365" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1365" s="2" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H1365" s="2" t="n">
-        <x:v>3.2449254611302956</x:v>
-      </x:c>
-      <x:c r="I1365" s="2" t="n">
-        <x:v>2.1572144210553637</x:v>
-      </x:c>
-      <x:c r="J1365" s="2" t="n">
-        <x:v>0.04211313821724128</x:v>
-      </x:c>
-      <x:c r="K1365" s="2" t="str">
-        <x:v>MAR03452;MAR03453;MAR03454;MAR03455;MAR03456;MAR03457;MAR03458</x:v>
-      </x:c>
-      <x:c r="L1365" s="2" t="n">
-        <x:v>0.26099063289895585</x:v>
-      </x:c>
-      <x:c r="M1365" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1366" ht="18" customHeight="1">
-      <x:c r="A1366" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1366" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1366" s="2" t="str">
-        <x:v>Oxidative phosphorylation</x:v>
-      </x:c>
-      <x:c r="D1366" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1366" s="2" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F1366" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1366" s="2" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H1366" s="2" t="n">
-        <x:v>0.5499873662932705</x:v>
-      </x:c>
-      <x:c r="I1366" s="2" t="n">
-        <x:v>10.909341500765695</x:v>
-      </x:c>
-      <x:c r="J1366" s="2" t="n">
-        <x:v>0.000004697444272199147</x:v>
-      </x:c>
-      <x:c r="K1366" s="2" t="str">
-        <x:v>MAR03977;MAR06911;MAR06912;MAR06914;MAR06916;MAR06918</x:v>
-      </x:c>
-      <x:c r="L1366" s="2" t="n">
-        <x:v>0.00007061158251720632</x:v>
-      </x:c>
-      <x:c r="M1366" s="3" t="b">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1367" ht="18" customHeight="1">
-      <x:c r="A1367" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1367" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1367" s="2" t="str">
-        <x:v>Pantothenate and CoA metabolism</x:v>
-      </x:c>
-      <x:c r="D1367" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1367" s="2" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="F1367" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1367" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1367" s="2" t="n">
-        <x:v>1.0449759959572138</x:v>
-      </x:c>
-      <x:c r="I1367" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1367" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1367" s="2"/>
-      <x:c r="L1367" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1367" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1368" ht="18" customHeight="1">
-      <x:c r="A1368" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1368" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1368" s="2" t="str">
-        <x:v>Pentose and glucuronate interconversions</x:v>
-      </x:c>
-      <x:c r="D1368" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1368" s="2" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F1368" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1368" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1368" s="2" t="n">
-        <x:v>0.8249810494399057</x:v>
-      </x:c>
-      <x:c r="I1368" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1368" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1368" s="2"/>
-      <x:c r="L1368" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1368" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1369" ht="18" customHeight="1">
-      <x:c r="A1369" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1369" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1369" s="2" t="str">
-        <x:v>Pentose phosphate pathway</x:v>
-      </x:c>
-      <x:c r="D1369" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1369" s="2" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F1369" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1369" s="2" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H1369" s="2" t="n">
-        <x:v>1.374968415733176</x:v>
-      </x:c>
-      <x:c r="I1369" s="2" t="n">
-        <x:v>2.909157733537519</x:v>
-      </x:c>
-      <x:c r="J1369" s="2" t="n">
-        <x:v>0.045703733170350806</x:v>
-      </x:c>
-      <x:c r="K1369" s="2" t="str">
-        <x:v>MAR04350;MAR04354;MAR04398;MAR04710</x:v>
-      </x:c>
-      <x:c r="L1369" s="2" t="n">
-        <x:v>0.27956439380824977</x:v>
-      </x:c>
-      <x:c r="M1369" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1370" ht="18" customHeight="1">
-      <x:c r="A1370" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1370" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1370" s="2" t="str">
-        <x:v>Peptide metabolism</x:v>
-      </x:c>
-      <x:c r="D1370" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1370" s="2" t="n">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="F1370" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1370" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1370" s="2" t="n">
-        <x:v>13.309694264297145</x:v>
-      </x:c>
-      <x:c r="I1370" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1370" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1370" s="2"/>
-      <x:c r="L1370" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1370" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1371" ht="18" customHeight="1">
-      <x:c r="A1371" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1371" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1371" s="2" t="str">
-        <x:v>Peroxisomal transport</x:v>
-      </x:c>
-      <x:c r="D1371" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1371" s="2" t="n">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="F1371" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1371" s="2" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H1371" s="2" t="n">
-        <x:v>8.799797860692328</x:v>
-      </x:c>
-      <x:c r="I1371" s="2" t="n">
-        <x:v>1.022750765696784</x:v>
-      </x:c>
-      <x:c r="J1371" s="2" t="n">
-        <x:v>0.5214393646505396</x:v>
-      </x:c>
-      <x:c r="K1371" s="2" t="str">
-        <x:v>MAR01462;MAR01633;MAR02278;MAR07590;MAR07596;MAR07777;MAR07779;MAR10039;MAR10040</x:v>
-      </x:c>
-      <x:c r="L1371" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1371" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1372" ht="18" customHeight="1">
-      <x:c r="A1372" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1372" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1372" s="2" t="str">
-        <x:v>Phenylalanine metabolism</x:v>
-      </x:c>
-      <x:c r="D1372" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1372" s="2" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F1372" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1372" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H1372" s="2" t="n">
-        <x:v>0.3299924197759623</x:v>
-      </x:c>
-      <x:c r="I1372" s="2" t="n">
-        <x:v>3.030372639101582</x:v>
-      </x:c>
-      <x:c r="J1372" s="2" t="n">
-        <x:v>0.28786490018138805</x:v>
-      </x:c>
-      <x:c r="K1372" s="2" t="str">
-        <x:v>MAR01616</x:v>
-      </x:c>
-      <x:c r="L1372" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1372" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1373" ht="18" customHeight="1">
-      <x:c r="A1373" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1373" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1373" s="2" t="str">
-        <x:v>Phenylalanine, tyrosine and tryptophan biosynthesis</x:v>
-      </x:c>
-      <x:c r="D1373" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1373" s="2" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="F1373" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1373" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H1373" s="2" t="n">
-        <x:v>7.149835761812516</x:v>
-      </x:c>
-      <x:c r="I1373" s="2" t="n">
-        <x:v>0.1398633525739192</x:v>
-      </x:c>
-      <x:c r="J1373" s="2" t="n">
-        <x:v>0.9993859192188355</x:v>
-      </x:c>
-      <x:c r="K1373" s="2" t="str">
-        <x:v>MAR06725</x:v>
-      </x:c>
-      <x:c r="L1373" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1373" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1374" ht="18" customHeight="1">
-      <x:c r="A1374" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1374" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1374" s="2" t="str">
-        <x:v>Phosphatidylinositol phosphate metabolism</x:v>
-      </x:c>
-      <x:c r="D1374" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1374" s="2" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F1374" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1374" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1374" s="2" t="n">
-        <x:v>0.9349785226985597</x:v>
-      </x:c>
-      <x:c r="I1374" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1374" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1374" s="2"/>
-      <x:c r="L1374" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1374" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1375" ht="18" customHeight="1">
-      <x:c r="A1375" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1375" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1375" s="2" t="str">
-        <x:v>Pool reactions</x:v>
-      </x:c>
-      <x:c r="D1375" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1375" s="2" t="n">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="F1375" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1375" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H1375" s="2" t="n">
-        <x:v>2.5299418849490443</x:v>
-      </x:c>
-      <x:c r="I1375" s="2" t="n">
-        <x:v>0.3952659964045542</x:v>
-      </x:c>
-      <x:c r="J1375" s="2" t="n">
-        <x:v>0.9262638031306835</x:v>
-      </x:c>
-      <x:c r="K1375" s="2" t="str">
-        <x:v>MAR00031</x:v>
-      </x:c>
-      <x:c r="L1375" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1375" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1376" ht="18" customHeight="1">
-      <x:c r="A1376" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1376" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1376" s="2" t="str">
-        <x:v>Porphyrin metabolism</x:v>
-      </x:c>
-      <x:c r="D1376" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1376" s="2" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F1376" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1376" s="2" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H1376" s="2" t="n">
-        <x:v>1.154973469215868</x:v>
-      </x:c>
-      <x:c r="I1376" s="2" t="n">
-        <x:v>5.194924524174141</x:v>
-      </x:c>
-      <x:c r="J1376" s="2" t="n">
-        <x:v>0.000720461102843526</x:v>
-      </x:c>
-      <x:c r="K1376" s="2" t="str">
-        <x:v>MAR01044;MAR04752;MAR04762;MAR04770;MAR11316;MAR11406</x:v>
-      </x:c>
-      <x:c r="L1376" s="2" t="n">
-        <x:v>0.007485378958219871</x:v>
-      </x:c>
-      <x:c r="M1376" s="3" t="b">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1377" ht="18" customHeight="1">
-      <x:c r="A1377" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1377" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1377" s="2" t="str">
-        <x:v>Propanoate metabolism</x:v>
-      </x:c>
-      <x:c r="D1377" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1377" s="2" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F1377" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1377" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1377" s="2" t="n">
-        <x:v>1.374968415733176</x:v>
-      </x:c>
-      <x:c r="I1377" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1377" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1377" s="2"/>
-      <x:c r="L1377" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1377" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1378" ht="18" customHeight="1">
-      <x:c r="A1378" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1378" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1378" s="2" t="str">
-        <x:v>Prostaglandin biosynthesis</x:v>
-      </x:c>
-      <x:c r="D1378" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1378" s="2" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="F1378" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1378" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1378" s="2" t="n">
-        <x:v>3.2999241977596228</x:v>
-      </x:c>
-      <x:c r="I1378" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1378" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1378" s="2"/>
-      <x:c r="L1378" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1378" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1379" ht="18" customHeight="1">
-      <x:c r="A1379" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1379" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1379" s="2" t="str">
-        <x:v>Protein assembly</x:v>
-      </x:c>
-      <x:c r="D1379" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1379" s="2" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F1379" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1379" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H1379" s="2" t="n">
-        <x:v>0.8799797860692327</x:v>
-      </x:c>
-      <x:c r="I1379" s="2" t="n">
-        <x:v>1.1363897396630935</x:v>
-      </x:c>
-      <x:c r="J1379" s="2" t="n">
-        <x:v>0.5957383582625783</x:v>
-      </x:c>
-      <x:c r="K1379" s="2" t="str">
-        <x:v>MAR05171</x:v>
-      </x:c>
-      <x:c r="L1379" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1379" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1380" ht="18" customHeight="1">
-      <x:c r="A1380" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1380" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1380" s="2" t="str">
-        <x:v>Protein degradation</x:v>
-      </x:c>
-      <x:c r="D1380" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1380" s="2" t="n">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F1380" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1380" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1380" s="2" t="n">
-        <x:v>1.8699570453971195</x:v>
-      </x:c>
-      <x:c r="I1380" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1380" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1380" s="2"/>
-      <x:c r="L1380" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1380" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1381" ht="18" customHeight="1">
-      <x:c r="A1381" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1381" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1381" s="2" t="str">
-        <x:v>Protein modification</x:v>
-      </x:c>
-      <x:c r="D1381" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1381" s="2" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F1381" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1381" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1381" s="2" t="n">
-        <x:v>0.27499368314663525</x:v>
-      </x:c>
-      <x:c r="I1381" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1381" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1381" s="2"/>
-      <x:c r="L1381" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1381" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1382" ht="18" customHeight="1">
-      <x:c r="A1382" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1382" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1382" s="2" t="str">
-        <x:v>Purine metabolism</x:v>
-      </x:c>
-      <x:c r="D1382" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1382" s="2" t="n">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="F1382" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1382" s="2" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="H1382" s="2" t="n">
-        <x:v>5.77486734607934</x:v>
-      </x:c>
-      <x:c r="I1382" s="2" t="n">
-        <x:v>2.251133960475461</x:v>
-      </x:c>
-      <x:c r="J1382" s="2" t="n">
-        <x:v>0.004905448927420309</x:v>
-      </x:c>
-      <x:c r="K1382" s="2" t="str">
-        <x:v>MAR04002;MAR04004;MAR04010;MAR04020;MAR04080;MAR04135;MAR04453;MAR04603;MAR04611;MAR04612;MAR04614;MAR04621;MAR04663</x:v>
-      </x:c>
-      <x:c r="L1382" s="2" t="n">
-        <x:v>0.042008480814817555</x:v>
-      </x:c>
-      <x:c r="M1382" s="3" t="b">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1383" ht="18" customHeight="1">
-      <x:c r="A1383" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1383" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1383" s="2" t="str">
-        <x:v>Pyrimidine metabolism</x:v>
-      </x:c>
-      <x:c r="D1383" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1383" s="2" t="n">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="F1383" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1383" s="2" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H1383" s="2" t="n">
-        <x:v>3.794912827423566</x:v>
-      </x:c>
-      <x:c r="I1383" s="2" t="n">
-        <x:v>2.635106642697028</x:v>
-      </x:c>
-      <x:c r="J1383" s="2" t="n">
-        <x:v>0.0042485522967605355</x:v>
-      </x:c>
-      <x:c r="K1383" s="2" t="str">
-        <x:v>MAR03931;MAR03970;MAR04008;MAR04032;MAR04512;MAR04579;MAR04644;MAR04673;MAR06621;MAR08274</x:v>
-      </x:c>
-      <x:c r="L1383" s="2" t="n">
-        <x:v>0.03682947481793028</x:v>
-      </x:c>
-      <x:c r="M1383" s="3" t="b">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1384" ht="18" customHeight="1">
-      <x:c r="A1384" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1384" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1384" s="2" t="str">
-        <x:v>Pyruvate metabolism</x:v>
-      </x:c>
-      <x:c r="D1384" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1384" s="2" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F1384" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1384" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H1384" s="2" t="n">
-        <x:v>1.7599595721384653</x:v>
-      </x:c>
-      <x:c r="I1384" s="2" t="n">
-        <x:v>0.5681948698315468</x:v>
-      </x:c>
-      <x:c r="J1384" s="2" t="n">
-        <x:v>0.8367780288040122</x:v>
-      </x:c>
-      <x:c r="K1384" s="2" t="str">
-        <x:v>MAR11430</x:v>
-      </x:c>
-      <x:c r="L1384" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1384" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1385" ht="18" customHeight="1">
-      <x:c r="A1385" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1385" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1385" s="2" t="str">
-        <x:v>ROS detoxification</x:v>
-      </x:c>
-      <x:c r="D1385" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1385" s="2" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F1385" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1385" s="2" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H1385" s="2" t="n">
-        <x:v>0.5499873662932705</x:v>
-      </x:c>
-      <x:c r="I1385" s="2" t="n">
-        <x:v>5.4546707503828475</x:v>
-      </x:c>
-      <x:c r="J1385" s="2" t="n">
-        <x:v>0.014858222150050572</x:v>
-      </x:c>
-      <x:c r="K1385" s="2" t="str">
-        <x:v>MAR03980;MAR03982;MAR04767</x:v>
-      </x:c>
-      <x:c r="L1385" s="2" t="n">
-        <x:v>0.11049825209484977</x:v>
-      </x:c>
-      <x:c r="M1385" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1386" ht="18" customHeight="1">
-      <x:c r="A1386" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1386" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1386" s="2" t="str">
-        <x:v>Retinol metabolism</x:v>
-      </x:c>
-      <x:c r="D1386" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1386" s="2" t="n">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="F1386" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1386" s="2" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H1386" s="2" t="n">
-        <x:v>4.619893876863472</x:v>
-      </x:c>
-      <x:c r="I1386" s="2" t="n">
-        <x:v>8.658207540290235</x:v>
-      </x:c>
-      <x:c r="J1386" s="2" t="n">
-        <x:v>2.019008393456182e-28</x:v>
-      </x:c>
-      <x:c r="K1386" s="2" t="str">
-        <x:v>MAR06633;MAR06634;MAR06638;MAR06641;MAR06642;MAR06644;MAR06649;MAR06651;MAR06652;MAR06654;MAR06655;MAR06656;MAR06657;MAR06658;MAR06660;MAR06664;MAR06665;MAR06668;MAR06669;MAR06672;MAR06673;MAR06674;MAR06675;MAR06677;MAR06678;MAR06682;MAR06687;MAR06690;MAR06691;MAR06692;MAR06693;MAR06700;MAR06701;MAR06702;MAR06703;MAR08698;MAR08699;MAR08702;MAR08709;MAR08711</x:v>
-      </x:c>
-      <x:c r="L1386" s="2" t="n">
-        <x:v>2.194506815348912e-26</x:v>
-      </x:c>
-      <x:c r="M1386" s="3" t="b">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1387" ht="18" customHeight="1">
-      <x:c r="A1387" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1387" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1387" s="2" t="str">
-        <x:v>Riboflavin metabolism</x:v>
-      </x:c>
-      <x:c r="D1387" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1387" s="2" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F1387" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1387" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1387" s="2" t="n">
-        <x:v>0.3299924197759623</x:v>
-      </x:c>
-      <x:c r="I1387" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1387" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1387" s="2"/>
-      <x:c r="L1387" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1387" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1388" ht="18" customHeight="1">
-      <x:c r="A1388" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1388" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1388" s="2" t="str">
-        <x:v>Serotonin and melatonin biosynthesis</x:v>
-      </x:c>
-      <x:c r="D1388" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1388" s="2" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F1388" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1388" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1388" s="2" t="n">
-        <x:v>0.7699823128105786</x:v>
-      </x:c>
-      <x:c r="I1388" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1388" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1388" s="2"/>
-      <x:c r="L1388" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1388" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1389" ht="18" customHeight="1">
-      <x:c r="A1389" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1389" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1389" s="2" t="str">
-        <x:v>Sphingolipid metabolism</x:v>
-      </x:c>
-      <x:c r="D1389" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1389" s="2" t="n">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="F1389" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1389" s="2" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H1389" s="2" t="n">
-        <x:v>4.454897666975491</x:v>
-      </x:c>
-      <x:c r="I1389" s="2" t="n">
-        <x:v>0.6734161420225738</x:v>
-      </x:c>
-      <x:c r="J1389" s="2" t="n">
-        <x:v>0.8301675422116803</x:v>
-      </x:c>
-      <x:c r="K1389" s="2" t="str">
-        <x:v>MAR00736;MAR00758;MAR12040</x:v>
-      </x:c>
-      <x:c r="L1389" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1389" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1390" ht="18" customHeight="1">
-      <x:c r="A1390" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1390" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1390" s="2" t="str">
-        <x:v>Starch and sucrose metabolism</x:v>
-      </x:c>
-      <x:c r="D1390" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1390" s="2" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F1390" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1390" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1390" s="2" t="n">
-        <x:v>1.9249557820264465</x:v>
-      </x:c>
-      <x:c r="I1390" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1390" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1390" s="2"/>
-      <x:c r="L1390" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1390" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1391" ht="18" customHeight="1">
-      <x:c r="A1391" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1391" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1391" s="2" t="str">
-        <x:v>Steroid metabolism</x:v>
-      </x:c>
-      <x:c r="D1391" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1391" s="2" t="n">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="F1391" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1391" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H1391" s="2" t="n">
-        <x:v>3.1899267245009684</x:v>
-      </x:c>
-      <x:c r="I1391" s="2" t="n">
-        <x:v>0.3134868247346465</x:v>
-      </x:c>
-      <x:c r="J1391" s="2" t="n">
-        <x:v>0.962713823498855</x:v>
-      </x:c>
-      <x:c r="K1391" s="2" t="str">
-        <x:v>MAR01820</x:v>
-      </x:c>
-      <x:c r="L1391" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1391" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1392" ht="18" customHeight="1">
-      <x:c r="A1392" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1392" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1392" s="2" t="str">
-        <x:v>Sulfur metabolism</x:v>
-      </x:c>
-      <x:c r="D1392" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1392" s="2" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F1392" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1392" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1392" s="2" t="n">
-        <x:v>0.43998989303461633</x:v>
-      </x:c>
-      <x:c r="I1392" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1392" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1392" s="2"/>
-      <x:c r="L1392" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1392" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1393" ht="18" customHeight="1">
-      <x:c r="A1393" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1393" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1393" s="2" t="str">
-        <x:v>Terpenoid backbone biosynthesis</x:v>
-      </x:c>
-      <x:c r="D1393" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1393" s="2" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F1393" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1393" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1393" s="2" t="n">
-        <x:v>0.8799797860692327</x:v>
-      </x:c>
-      <x:c r="I1393" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1393" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1393" s="2"/>
-      <x:c r="L1393" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1393" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1394" ht="18" customHeight="1">
-      <x:c r="A1394" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1394" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1394" s="2" t="str">
-        <x:v>Thiamine metabolism</x:v>
-      </x:c>
-      <x:c r="D1394" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1394" s="2" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F1394" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1394" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H1394" s="2" t="n">
-        <x:v>0.21999494651730817</x:v>
-      </x:c>
-      <x:c r="I1394" s="2" t="n">
-        <x:v>4.545558958652374</x:v>
-      </x:c>
-      <x:c r="J1394" s="2" t="n">
-        <x:v>0.2025255443707365</x:v>
-      </x:c>
-      <x:c r="K1394" s="2" t="str">
-        <x:v>MAR08746</x:v>
-      </x:c>
-      <x:c r="L1394" s="2" t="n">
-        <x:v>0.9113649496683143</x:v>
-      </x:c>
-      <x:c r="M1394" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1395" ht="18" customHeight="1">
-      <x:c r="A1395" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1395" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1395" s="2" t="str">
-        <x:v>Toluene degradation</x:v>
-      </x:c>
-      <x:c r="D1395" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1395" s="2" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F1395" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1395" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1395" s="2" t="n">
-        <x:v>0.10999747325865408</x:v>
-      </x:c>
-      <x:c r="I1395" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1395" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1395" s="2"/>
-      <x:c r="L1395" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1395" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1396" ht="18" customHeight="1">
-      <x:c r="A1396" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1396" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1396" s="2" t="str">
-        <x:v>Triacylglycerol synthesis</x:v>
-      </x:c>
-      <x:c r="D1396" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1396" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F1396" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1396" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1396" s="2" t="n">
-        <x:v>0.05499873662932704</x:v>
-      </x:c>
-      <x:c r="I1396" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1396" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1396" s="2"/>
-      <x:c r="L1396" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1396" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1397" ht="18" customHeight="1">
-      <x:c r="A1397" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1397" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1397" s="2" t="str">
-        <x:v>Tricarboxylic acid cycle and glyoxylate/dicarboxylate metabolism</x:v>
-      </x:c>
-      <x:c r="D1397" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1397" s="2" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F1397" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1397" s="2" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H1397" s="2" t="n">
-        <x:v>1.5949633622504842</x:v>
-      </x:c>
-      <x:c r="I1397" s="2" t="n">
-        <x:v>4.388815546285051</x:v>
-      </x:c>
-      <x:c r="J1397" s="2" t="n">
-        <x:v>0.0007944867667857099</x:v>
-      </x:c>
-      <x:c r="K1397" s="2" t="str">
-        <x:v>MAR04139;MAR04141;MAR04147;MAR04152;MAR04408;MAR04410;MAR04652</x:v>
-      </x:c>
-      <x:c r="L1397" s="2" t="n">
-        <x:v>0.008134853633827595</x:v>
-      </x:c>
-      <x:c r="M1397" s="3" t="b">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1398" ht="18" customHeight="1">
-      <x:c r="A1398" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1398" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1398" s="2" t="str">
-        <x:v>Tryptophan metabolism</x:v>
-      </x:c>
-      <x:c r="D1398" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1398" s="2" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F1398" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1398" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1398" s="2" t="n">
-        <x:v>0.8249810494399057</x:v>
-      </x:c>
-      <x:c r="I1398" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1398" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1398" s="2"/>
-      <x:c r="L1398" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1398" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1399" ht="18" customHeight="1">
-      <x:c r="A1399" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1399" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1399" s="2" t="str">
-        <x:v>Tyrosine metabolism</x:v>
-      </x:c>
-      <x:c r="D1399" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1399" s="2" t="n">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="F1399" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1399" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1399" s="2" t="n">
-        <x:v>3.794912827423566</x:v>
-      </x:c>
-      <x:c r="I1399" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1399" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1399" s="2"/>
-      <x:c r="L1399" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1399" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1400" ht="18" customHeight="1">
-      <x:c r="A1400" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1400" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1400" s="2" t="str">
-        <x:v>Ubiquinone synthesis</x:v>
-      </x:c>
-      <x:c r="D1400" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1400" s="2" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F1400" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1400" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1400" s="2" t="n">
-        <x:v>0.5499873662932705</x:v>
-      </x:c>
-      <x:c r="I1400" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1400" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1400" s="2"/>
-      <x:c r="L1400" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1400" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1401" ht="18" customHeight="1">
-      <x:c r="A1401" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1401" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1401" s="2" t="str">
-        <x:v>Unassigned</x:v>
-      </x:c>
-      <x:c r="D1401" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1401" s="2" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F1401" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1401" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H1401" s="2" t="n">
-        <x:v>0.3849911564052893</x:v>
-      </x:c>
-      <x:c r="I1401" s="2" t="n">
-        <x:v>2.597462262087071</x:v>
-      </x:c>
-      <x:c r="J1401" s="2" t="n">
-        <x:v>0.3270512337266441</x:v>
-      </x:c>
-      <x:c r="K1401" s="2" t="str">
-        <x:v>ASCTm</x:v>
-      </x:c>
-      <x:c r="L1401" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1401" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1402" ht="18" customHeight="1">
-      <x:c r="A1402" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1402" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1402" s="2" t="str">
-        <x:v>Urea cycle</x:v>
-      </x:c>
-      <x:c r="D1402" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1402" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F1402" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1402" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1402" s="2" t="n">
-        <x:v>0.05499873662932704</x:v>
-      </x:c>
-      <x:c r="I1402" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1402" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1402" s="2"/>
-      <x:c r="L1402" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1402" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1403" ht="18" customHeight="1">
-      <x:c r="A1403" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1403" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1403" s="2" t="str">
-        <x:v>Valine, leucine, and isoleucine metabolism</x:v>
-      </x:c>
-      <x:c r="D1403" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1403" s="2" t="n">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="F1403" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1403" s="2" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H1403" s="2" t="n">
-        <x:v>2.9149330413543333</x:v>
-      </x:c>
-      <x:c r="I1403" s="2" t="n">
-        <x:v>0.6861221069663961</x:v>
-      </x:c>
-      <x:c r="J1403" s="2" t="n">
-        <x:v>0.796929860773349</x:v>
-      </x:c>
-      <x:c r="K1403" s="2" t="str">
-        <x:v>MAR03215;MAR03763</x:v>
-      </x:c>
-      <x:c r="L1403" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1403" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1404" ht="18" customHeight="1">
-      <x:c r="A1404" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1404" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1404" s="2" t="str">
-        <x:v>Vitamin A metabolism</x:v>
-      </x:c>
-      <x:c r="D1404" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1404" s="2" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F1404" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1404" s="2" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H1404" s="2" t="n">
-        <x:v>0.4949886296639434</x:v>
-      </x:c>
-      <x:c r="I1404" s="2" t="n">
-        <x:v>4.040496852135443</x:v>
-      </x:c>
-      <x:c r="J1404" s="2" t="n">
-        <x:v>0.08409930906545178</x:v>
-      </x:c>
-      <x:c r="K1404" s="2" t="str">
-        <x:v>MAR02960;MAR02993</x:v>
-      </x:c>
-      <x:c r="L1404" s="2" t="n">
-        <x:v>0.46774485757349105</x:v>
-      </x:c>
-      <x:c r="M1404" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1405" ht="18" customHeight="1">
-      <x:c r="A1405" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1405" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1405" s="2" t="str">
-        <x:v>Vitamin B12 metabolism</x:v>
-      </x:c>
-      <x:c r="D1405" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1405" s="2" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F1405" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1405" s="2" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H1405" s="2" t="n">
-        <x:v>0.21999494651730817</x:v>
-      </x:c>
-      <x:c r="I1405" s="2" t="n">
-        <x:v>13.636676875957122</x:v>
-      </x:c>
-      <x:c r="J1405" s="2" t="n">
-        <x:v>0.0006353558546654095</x:v>
-      </x:c>
-      <x:c r="K1405" s="2" t="str">
-        <x:v>MAR08613;MAR08615;MAR08616</x:v>
-      </x:c>
-      <x:c r="L1405" s="2" t="n">
-        <x:v>0.006699685243598684</x:v>
-      </x:c>
-      <x:c r="M1405" s="3" t="b">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1406" ht="18" customHeight="1">
-      <x:c r="A1406" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1406" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1406" s="2" t="str">
-        <x:v>Vitamin B2 metabolism</x:v>
-      </x:c>
-      <x:c r="D1406" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1406" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F1406" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1406" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1406" s="2" t="n">
-        <x:v>0.05499873662932704</x:v>
-      </x:c>
-      <x:c r="I1406" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1406" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1406" s="2"/>
-      <x:c r="L1406" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1406" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1407" ht="18" customHeight="1">
-      <x:c r="A1407" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1407" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1407" s="2" t="str">
-        <x:v>Vitamin B6 metabolism</x:v>
-      </x:c>
-      <x:c r="D1407" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1407" s="2" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F1407" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1407" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1407" s="2" t="n">
-        <x:v>0.6049861029225975</x:v>
-      </x:c>
-      <x:c r="I1407" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1407" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1407" s="2"/>
-      <x:c r="L1407" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1407" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1408" ht="18" customHeight="1">
-      <x:c r="A1408" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1408" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1408" s="2" t="str">
-        <x:v>Vitamin C metabolism</x:v>
-      </x:c>
-      <x:c r="D1408" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1408" s="2" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F1408" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1408" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1408" s="2" t="n">
-        <x:v>0.10999747325865408</x:v>
-      </x:c>
-      <x:c r="I1408" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1408" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1408" s="2"/>
-      <x:c r="L1408" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1408" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1409" ht="18" customHeight="1">
-      <x:c r="A1409" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1409" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1409" s="2" t="str">
-        <x:v>Vitamin D metabolism</x:v>
-      </x:c>
-      <x:c r="D1409" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1409" s="2" t="n">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F1409" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1409" s="2" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H1409" s="2" t="n">
-        <x:v>1.8699570453971195</x:v>
-      </x:c>
-      <x:c r="I1409" s="2" t="n">
-        <x:v>8.55634627511035</x:v>
-      </x:c>
-      <x:c r="J1409" s="2" t="n">
-        <x:v>5.1000237515933474e-12</x:v>
-      </x:c>
-      <x:c r="K1409" s="2" t="str">
-        <x:v>MAR02129;MAR02130;MAR02131;MAR02132;MAR02133;MAR02134;MAR02135;MAR02136;MAR02137;MAR02138;MAR02139;MAR02142;MAR02143;MAR02144;MAR02145;MAR08006</x:v>
-      </x:c>
-      <x:c r="L1409" s="2" t="n">
-        <x:v>1.44126671220028e-10</x:v>
-      </x:c>
-      <x:c r="M1409" s="3" t="b">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1410" ht="18" customHeight="1">
-      <x:c r="A1410" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1410" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1410" s="2" t="str">
-        <x:v>Vitamin E metabolism</x:v>
-      </x:c>
-      <x:c r="D1410" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1410" s="2" t="n">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F1410" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1410" s="2" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H1410" s="2" t="n">
-        <x:v>2.144950728543755</x:v>
-      </x:c>
-      <x:c r="I1410" s="2" t="n">
-        <x:v>6.993167628695959</x:v>
-      </x:c>
-      <x:c r="J1410" s="2" t="n">
-        <x:v>7.953722565771817e-10</x:v>
-      </x:c>
-      <x:c r="K1410" s="2" t="str">
-        <x:v>MAR06436;MAR06453;MAR06465;MAR06467;MAR06470;MAR06471;MAR06472;MAR06473;MAR06476;MAR06478;MAR06482;MAR06484;MAR06486;MAR06488;MAR06492</x:v>
-      </x:c>
-      <x:c r="L1410" s="2" t="n">
-        <x:v>1.873101664239263e-8</x:v>
-      </x:c>
-      <x:c r="M1410" s="3" t="b">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1411" ht="18" customHeight="1">
-      <x:c r="A1411" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1411" s="2" t="str">
-        <x:v>subsystem</x:v>
-      </x:c>
-      <x:c r="C1411" s="2" t="str">
-        <x:v>Xenobiotics metabolism</x:v>
-      </x:c>
-      <x:c r="D1411" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1411" s="2" t="n">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="F1411" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1411" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1411" s="2" t="n">
-        <x:v>7.644824391476459</x:v>
-      </x:c>
-      <x:c r="I1411" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J1411" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K1411" s="2"/>
-      <x:c r="L1411" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1411" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1412" ht="18" customHeight="1">
-      <x:c r="A1412" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1412" s="2" t="str">
-        <x:v>reviewer_aggregate</x:v>
-      </x:c>
-      <x:c r="C1412" s="2" t="str">
-        <x:v>Transport/exchange (annotation-defined)</x:v>
-      </x:c>
-      <x:c r="D1412" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1412" s="2" t="n">
-        <x:v>5589</x:v>
-      </x:c>
-      <x:c r="F1412" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1412" s="2" t="n">
-        <x:v>315</x:v>
-      </x:c>
-      <x:c r="H1412" s="2" t="n">
-        <x:v>307.38793902130885</x:v>
-      </x:c>
-      <x:c r="I1412" s="2" t="n">
-        <x:v>1.0247636943821776</x:v>
-      </x:c>
-      <x:c r="J1412" s="2" t="n">
-        <x:v>0.28297997425185806</x:v>
-      </x:c>
-      <x:c r="K1412" s="2" t="str">
-        <x:v>MAR00019;MAR00061;MAR00089;MAR00142;MAR00158;MAR00182;MAR00569;MAR00574;MAR00578;MAR00628;MAR00656;MAR00658;MAR00661;MAR00714;MAR01095;MAR01461;MAR01462;MAR01499;MAR01525;MAR01534;MAR01601;MAR01607;MAR01633;MAR01669;MAR01827;MAR01871;MAR01922;MAR01939;MAR02225;MAR02278;MAR02351;MAR02379;MAR02382;MAR03597;MAR03789;MAR03946;MAR03951;MAR03952;MAR03959;MAR04110;MAR04146;MAR04181;MAR04384;MAR04756;MAR04765;MAR04847;MAR04852;MAR04855;MAR04859;MAR04874;MAR04882;MAR04883;MAR04886;MAR04889;MAR04894;MAR04896;MAR04898;MAR04899;MAR04905;MAR04914;MAR04919;MAR04922;MAR04947;MAR04948;MAR04958;MAR04963;MAR04969;MAR04985;MAR04990;MAR05006;MAR05023;MAR05032;MAR05043;MAR05068;MAR05071;MAR05074;MAR05076;MAR05080;MAR05082;MAR05085;MAR05088;MAR05089;MAR05091;MAR05115;MAR05116;MAR05126;MAR05206;MAR05227;MAR05303;MAR05304;MAR05361;MAR05420;MAR05422;MAR05423;MAR05448;MAR05471;MAR05498;MAR05510;MAR05521;MAR05548;MAR05566;MAR05570;MAR05575;MAR05577;MAR05969;MAR05987;MAR06058;MAR06072;MAR06090;MAR06095;MAR06250;MAR06328;MAR06366;MAR06383;MAR06438;MAR06454;MAR06462;MAR06463;MAR06468;MAR06469;MAR06474;MAR06481;MAR06505;MAR06512;MAR06513;MAR06629;MAR07590;MAR07596;MAR07609;MAR07638;MAR07735;MAR07765;MAR07767;MAR07772;MAR07776;MAR07777;MAR07778;MAR07779;MAR07780;MAR07781;MAR07786;MAR07792;MAR07796;MAR07811;MAR07819;MAR07857;MAR07860;MAR07861;MAR07862;MAR08009;MAR08010;MAR08408;MAR08428;MAR08430;MAR08612;MAR08614;MAR08676;MAR08687;MAR08716;MAR08720;MAR08721;MAR08722;MAR08891;MAR08966;MAR08987;MAR08998;MAR09038;MAR09039;MAR09040;MAR09041;MAR09042;MAR09043;MAR09044;MAR09045;MAR09046;MAR09047;MAR09048;MAR09058;MAR09062;MAR09063;MAR09064;MAR09066;MAR09067;MAR09068;MAR09069;MAR09070;MAR09072;MAR09076;MAR09079;MAR09103;MAR09107;MAR09108;MAR09109;MAR09112;MAR09143;MAR09146;MAR09151;MAR09153;MAR09172;MAR09209;MAR09215;MAR09242;MAR09253;MAR09254;MAR09255;MAR09259;MAR09269;MAR09271;MAR09273;MAR09292;MAR09298;MAR09300;MAR09353;MAR09354;MAR09360;MAR09363;MAR09378;MAR09383;MAR09404;MAR09406;MAR09437;MAR09440;MAR09609;MAR09637;MAR09641;MAR09650;MAR09702;MAR09728;MAR09729;MAR09824;MAR09825;MAR09827;MAR09828;MAR09830;MAR09833;MAR09834;MAR09835;MAR09836;MAR09837;MAR09838;MAR09839;MAR09847;MAR09849;MAR09858;MAR09860;MAR09861;MAR09862;MAR09864;MAR09868;MAR09883;MAR09884;MAR09913;MAR09920;MAR09921;MAR09925;MAR09975;MAR09983;MAR09989;MAR09996;MAR10004;MAR10023;MAR10024;MAR10039;MAR10040;MAR10046;MAR10047;MAR10049;MAR10159;MAR10188;MAR10193;MAR10195;MAR10197;MAR10202;MAR10222;MAR10243;MAR10250;MAR10254;MAR10363;MAR10364;MAR10366;MAR10375;MAR10383;MAR10489;MAR10496;MAR11250;MAR11252;MAR11256;MAR11257;MAR11261;MAR11276;MAR11400;MAR11424;MAR11428;MAR11443;MAR11583;MAR11787;MAR11894;MAR11895;MAR11896;MAR11897;MAR11947;MAR11953;MAR11973;MAR11974;MAR12127;MAR12306;MAR12307;MAR13080;MAR13086;MAR20137;MAR20139;MAR20149;MAR20156;MAR20160;MAR20164</x:v>
-      </x:c>
-      <x:c r="L1412" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1412" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1413" ht="18" customHeight="1">
-      <x:c r="A1413" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1413" s="2" t="str">
-        <x:v>reviewer_aggregate</x:v>
-      </x:c>
-      <x:c r="C1413" s="2" t="str">
-        <x:v>Carnitine shuttles (all compartments)</x:v>
-      </x:c>
-      <x:c r="D1413" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1413" s="2" t="n">
-        <x:v>308</x:v>
-      </x:c>
-      <x:c r="F1413" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1413" s="2" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H1413" s="2" t="n">
-        <x:v>16.93961088183273</x:v>
-      </x:c>
-      <x:c r="I1413" s="2" t="n">
-        <x:v>0.9445317316680256</x:v>
-      </x:c>
-      <x:c r="J1413" s="2" t="n">
-        <x:v>0.6304168324439183</x:v>
-      </x:c>
-      <x:c r="K1413" s="2" t="str">
-        <x:v>MAR00159;MAR02591;MAR02594;MAR02599;MAR02626;MAR02730;MAR02732;MAR02742;MAR02746;MAR02748;MAR02750;MAR02759;MAR02869;MAR02870;MAR02896;MAR02897</x:v>
-      </x:c>
-      <x:c r="L1413" s="2" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M1413" s="3" t="b">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="1414" ht="18" customHeight="1">
-      <x:c r="A1414" s="2" t="str">
-        <x:v>L4union</x:v>
-      </x:c>
-      <x:c r="B1414" s="2" t="str">
-        <x:v>reviewer_aggregate</x:v>
-      </x:c>
-      <x:c r="C1414" s="2" t="str">
-        <x:v>Beta-oxidation (all annotated types)</x:v>
-      </x:c>
-      <x:c r="D1414" s="2" t="n">
-        <x:v>11873</x:v>
-      </x:c>
-      <x:c r="E1414" s="2" t="n">
-        <x:v>322</x:v>
-      </x:c>
-      <x:c r="F1414" s="2" t="n">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="G1414" s="2" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="H1414" s="2" t="n">
-        <x:v>17.709593194643308</x:v>
-      </x:c>
-      <x:c r="I1414" s="2" t="n">
-        <x:v>1.5245974147032806</x:v>
-      </x:c>
-      <x:c r="J1414" s="2" t="n">
-        <x:v>0.019080109499143152</x:v>
-      </x:c>
-      <x:c r="K1414" s="2" t="str">
-        <x:v>MAR03136;MAR03137;MAR03139;MAR03150;MAR03151;MAR03153;MAR03250;MAR03252;MAR03254;MAR03256;MAR03258;MAR03260;MAR03262;MAR03264;MAR03272;MAR03281;MAR03282;MAR03283;MAR03285;MAR03286;MAR03287;MAR03288;MAR03290;MAR03292;MAR03293;MAR03298;MAR03430</x:v>
-      </x:c>
-      <x:c r="L1414" s="2" t="n">
-        <x:v>0.14041768084525663</x:v>
-      </x:c>
-      <x:c r="M1414" s="3" t="b">
         <x:v>0</x:v>
       </x:c>
     </x:row>
